--- a/Marathon_programme.xlsx
+++ b/Marathon_programme.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="698">
   <si>
     <t xml:space="preserve">  S01 — 31/08/2026 → 06/09/2026   |     S1 — Transition post-vacances (Z2 pur 70%)</t>
   </si>
@@ -401,14 +401,11 @@
     <t xml:space="preserve">  S06 — 05/10/2026 → 11/10/2026   |     Phase 1 — Base</t>
   </si>
   <si>
-    <t xml:space="preserve">Tempo — Jog progressif 34' (version courte)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objectif : endurance aérobie active, allure progressive (70 → 80% FC max)
-11' à 70-72% FC max (136-140 bpm)
-11' à 74-77% (144-149 bpm)
-12' à 78-80% (151-155 bpm)
-(un seul bloc continu, la progression se fait à la FC)</t>
+    <t xml:space="preserve">Objectif : économie de course et relance (alternance lent / rapide)
+13' EF Z2 (127-140 bpm)
+2 x [1 km à 80% FC max (155 bpm) — 1'15 de repos — 1 km à 87% (169 bpm)]
+1'40 de repos entre chaque série
+9' EF Z2 (127-140 bpm)</t>
   </si>
   <si>
     <t xml:space="preserve">43' Z2 très facile (127-140 bpm) — récupération active
@@ -432,7 +429,7 @@
 Total : 1600 m</t>
   </si>
   <si>
-    <t xml:space="preserve">37' EF Z2 (127-140 bpm)
+    <t xml:space="preserve">25' EF Z2 (127-140 bpm)
 6x20'' accélérations en fin — allure libre
 Très facile, aucune pression chrono</t>
   </si>
@@ -485,16 +482,14 @@
     <t xml:space="preserve">  S07 — 12/10/2026 → 18/10/2026   |     Phase 1 — Base</t>
   </si>
   <si>
-    <t xml:space="preserve">Tempo — Progressif 3x8' (80/85/90%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objectif : progression SV1 → SV2, endurance de seuil
-8' EF Z2 (127-140 bpm) + 2-4 lignes droites
-8' à 80% FC max (155 bpm)
-8' à 85% FC max (165 bpm)
-8' à 90% FC max (175 bpm)
-(enchaînés, sans repos)
-6' EF Z2 (127-140 bpm)</t>
+    <t xml:space="preserve">Qualité — 2x(9' + 5') @ 83/87%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objectif : seuil, allure marathon vers semi
+14' EF Z2 (127-140 bpm)
+2 x [9' à 83% FC max (161 bpm) — 1'30 de repos — 5' à 87% (169 bpm)]
+3'30 de repos entre séries
+9' EF Z2 (127-140 bpm)</t>
   </si>
   <si>
     <t xml:space="preserve">Vélo clé — Over-unders 3x12' — r=5'</t>
@@ -512,6 +507,11 @@
 Retour au calme : 200 m souple (110-126 bpm)
 Consigne : allure constante sur chaque répétition ; sighting toutes les 6-8 cycles de bras
 Total : 1750 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18' EF Z2 (127-140 bpm)
+6x20'' accélérations en fin — allure libre
+Très facile, aucune pression chrono</t>
   </si>
   <si>
     <t xml:space="preserve">55' EF (127-140 bpm) | 4x3' basse cadence (55-62 rpm) @ Z2 — r=3'
@@ -553,11 +553,14 @@
     <t xml:space="preserve">  S08 — 19/10/2026 → 25/10/2026   |     Phase 1 — Base</t>
   </si>
   <si>
+    <t xml:space="preserve">Qualité — 1km lent/rapide x3 (80/87%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Objectif : économie de course et relance (alternance lent / rapide)
-11' EF Z2 (127-140 bpm)
-2 x [1 km à 80% FC max (155 bpm) — 1'15 de repos — 1 km à 87% (169 bpm)]
+9' EF Z2 (127-140 bpm)
+3 x [1 km à 80% FC max (155 bpm) — 1'15 de repos — 1 km à 87% (169 bpm)]
 1'40 de repos entre chaque série
-8' EF Z2 (127-140 bpm)</t>
+6' EF Z2 (127-140 bpm)</t>
   </si>
   <si>
     <t xml:space="preserve">Vélo clé — VO2 5x3' @ 96% FTP — r=3'</t>
@@ -580,7 +583,7 @@
 Total : 1850 m</t>
   </si>
   <si>
-    <t xml:space="preserve">43' EF Z2 (127-140 bpm)
+    <t xml:space="preserve">34' EF Z2 (127-140 bpm)
 6x20'' accélérations en fin — allure libre
 Très facile, aucune pression chrono</t>
   </si>
@@ -731,11 +734,6 @@
 Total : 1900 m</t>
   </si>
   <si>
-    <t xml:space="preserve">34' EF Z2 (127-140 bpm)
-6x20'' accélérations en fin — allure libre
-Très facile, aucune pression chrono</t>
-  </si>
-  <si>
     <t xml:space="preserve">27' EF Z1-Z2 (120-135 bpm) — COURT
 Vraie récup — pas de strides</t>
   </si>
@@ -811,6 +809,11 @@
 Retour au calme : 200 m souple (110-126 bpm)
 Consigne : allure constante sur chaque répétition ; sighting toutes les 6-8 cycles de bras
 Total : 1950 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37' EF Z2 (127-140 bpm)
+6x20'' accélérations en fin — allure libre
+Très facile, aucune pression chrono</t>
   </si>
   <si>
     <t xml:space="preserve">64' EF (127-140 bpm) | 4x4' basse cadence (55-62 rpm) @ Z2 — r=3'
@@ -885,6 +888,11 @@
 Total : 2050 m</t>
   </si>
   <si>
+    <t xml:space="preserve">43' EF Z2 (127-140 bpm)
+6x20'' accélérations en fin — allure libre
+Très facile, aucune pression chrono</t>
+  </si>
+  <si>
     <t xml:space="preserve">70' EF (127-140 bpm) | 4x4' basse cadence (55-62 rpm) @ Z2 — r=3'
 Objectif : force musculaire spécifique, économie de pédalage
 FC : 131-155 bpm | RPE 6-7/10
@@ -1062,9 +1070,6 @@
   </si>
   <si>
     <t xml:space="preserve">  S15 — 07/12/2026 → 13/12/2026   |     Phase 2 — Build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualité — 2x(9' + 5') @ 83/87%</t>
   </si>
   <si>
     <t xml:space="preserve">Objectif : seuil, allure marathon vers semi
@@ -1254,6 +1259,13 @@
   </si>
   <si>
     <t xml:space="preserve">  S18 — 28/12/2026 → 03/01/2027   |     Semaine spé CAP — Dimanche vélo seul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objectif : économie de course et relance (alternance lent / rapide)
+11' EF Z2 (127-140 bpm)
+2 x [1 km à 80% FC max (155 bpm) — 1'15 de repos — 1 km à 87% (169 bpm)]
+1'40 de repos entre chaque série
+8' EF Z2 (127-140 bpm)</t>
   </si>
   <si>
     <t xml:space="preserve">Tempo — Jog progressif 37' (version courte)</t>
@@ -5705,10 +5717,10 @@
         <v>7</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>47</v>
@@ -5717,10 +5729,10 @@
         <v>5</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
@@ -5751,7 +5763,7 @@
         <v>2</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I62" s="4"/>
       <c r="J62" s="4" t="n">
@@ -5773,7 +5785,7 @@
         <v>11</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>101</v>
@@ -5785,7 +5797,7 @@
         <v>6</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4" t="n">
@@ -5819,7 +5831,7 @@
         <v>4</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
@@ -5842,7 +5854,7 @@
         <v>75</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>19</v>
@@ -5851,10 +5863,10 @@
         <v>2</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
@@ -5885,7 +5897,7 @@
         <v>5</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4" t="n">
@@ -5907,7 +5919,7 @@
         <v>27</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E67" s="4" t="n">
         <v>80</v>
@@ -5919,7 +5931,7 @@
         <v>4</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
@@ -5939,7 +5951,7 @@
         <v>7</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>62</v>
@@ -5951,7 +5963,7 @@
         <v>5</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>10</v>
@@ -5973,7 +5985,7 @@
         <v>11</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E69" s="4" t="n">
         <v>214</v>
@@ -5985,7 +5997,7 @@
         <v>6</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I69" s="4"/>
       <c r="J69" s="4" t="n">
@@ -6007,7 +6019,7 @@
         <v>27</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E70" s="4" t="n">
         <v>57</v>
@@ -6019,7 +6031,7 @@
         <v>7</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
@@ -6055,7 +6067,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -6110,10 +6122,10 @@
         <v>7</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>39</v>
@@ -6122,10 +6134,10 @@
         <v>6</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
@@ -6156,7 +6168,7 @@
         <v>2</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4" t="n">
@@ -6178,7 +6190,7 @@
         <v>11</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E76" s="4" t="n">
         <v>107</v>
@@ -6190,7 +6202,7 @@
         <v>7</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4" t="n">
@@ -6224,7 +6236,7 @@
         <v>4</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
@@ -6247,7 +6259,7 @@
         <v>75</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>19</v>
@@ -6256,10 +6268,10 @@
         <v>2</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
@@ -6312,7 +6324,7 @@
         <v>27</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E80" s="4" t="n">
         <v>83</v>
@@ -6515,10 +6527,10 @@
         <v>7</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>39</v>
@@ -6527,10 +6539,10 @@
         <v>6</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
@@ -6561,7 +6573,7 @@
         <v>2</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="n">
@@ -6583,19 +6595,19 @@
         <v>11</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>111</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G89" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I89" s="4"/>
       <c r="J89" s="4" t="n">
@@ -6629,7 +6641,7 @@
         <v>4</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
@@ -6652,7 +6664,7 @@
         <v>75</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>19</v>
@@ -6661,10 +6673,10 @@
         <v>2</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
@@ -6695,7 +6707,7 @@
         <v>5</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I92" s="4"/>
       <c r="J92" s="4" t="n">
@@ -6717,7 +6729,7 @@
         <v>27</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>87</v>
@@ -6729,7 +6741,7 @@
         <v>4</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
@@ -6749,7 +6761,7 @@
         <v>7</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>74</v>
@@ -6761,7 +6773,7 @@
         <v>5</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I94" s="4" t="n">
         <v>12</v>
@@ -6783,7 +6795,7 @@
         <v>11</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>236</v>
@@ -6795,7 +6807,7 @@
         <v>6</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I95" s="4"/>
       <c r="J95" s="4" t="n">
@@ -6829,7 +6841,7 @@
         <v>4</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
@@ -6865,7 +6877,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -6932,7 +6944,7 @@
         <v>6</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I100" s="4" t="n">
         <v>5</v>
@@ -6966,7 +6978,7 @@
         <v>2</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I101" s="4"/>
       <c r="J101" s="4" t="n">
@@ -6988,7 +7000,7 @@
         <v>11</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E102" s="4" t="n">
         <v>77</v>
@@ -7000,7 +7012,7 @@
         <v>5</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I102" s="4"/>
       <c r="J102" s="4" t="n">
@@ -7034,7 +7046,7 @@
         <v>4</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
@@ -7066,7 +7078,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I104" s="4" t="n">
         <v>5</v>
@@ -7100,7 +7112,7 @@
         <v>3</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I105" s="4"/>
       <c r="J105" s="4" t="n">
@@ -7122,7 +7134,7 @@
         <v>27</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E106" s="4" t="n">
         <v>64</v>
@@ -7134,7 +7146,7 @@
         <v>4</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
@@ -7154,7 +7166,7 @@
         <v>7</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E107" s="4" t="n">
         <v>49</v>
@@ -7166,7 +7178,7 @@
         <v>5</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I107" s="4" t="n">
         <v>8</v>
@@ -7188,7 +7200,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E108" s="4" t="n">
         <v>150</v>
@@ -7200,7 +7212,7 @@
         <v>4</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I108" s="4"/>
       <c r="J108" s="4" t="n">
@@ -7234,7 +7246,7 @@
         <v>4</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
@@ -7270,7 +7282,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B111" s="16"/>
       <c r="C111" s="16"/>
@@ -7325,7 +7337,7 @@
         <v>7</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E113" s="4" t="n">
         <v>31</v>
@@ -7337,7 +7349,7 @@
         <v>7</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I113" s="4" t="n">
         <v>5.5</v>
@@ -7371,7 +7383,7 @@
         <v>2</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I114" s="4"/>
       <c r="J114" s="4" t="n">
@@ -7393,7 +7405,7 @@
         <v>11</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E115" s="4" t="n">
         <v>116</v>
@@ -7405,7 +7417,7 @@
         <v>6</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I115" s="4"/>
       <c r="J115" s="4" t="n">
@@ -7439,7 +7451,7 @@
         <v>4</v>
       </c>
       <c r="H116" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
@@ -7471,7 +7483,7 @@
         <v>2</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="I117" s="4" t="n">
         <v>5.5</v>
@@ -7561,7 +7573,7 @@
         <v>27</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E120" s="4" t="n">
         <v>89</v>
@@ -7810,7 +7822,7 @@
         <v>2</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I128" s="4"/>
       <c r="J128" s="4" t="n">
@@ -7910,7 +7922,7 @@
         <v>2</v>
       </c>
       <c r="H131" s="7" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="I131" s="4" t="n">
         <v>6</v>
@@ -7978,7 +7990,7 @@
         <v>5</v>
       </c>
       <c r="H133" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I133" s="4"/>
       <c r="J133" s="4" t="n">
@@ -8000,7 +8012,7 @@
         <v>27</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E134" s="4" t="n">
         <v>91</v>
@@ -8012,7 +8024,7 @@
         <v>4</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
@@ -8032,7 +8044,7 @@
         <v>7</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E135" s="4" t="n">
         <v>86</v>
@@ -8044,7 +8056,7 @@
         <v>6</v>
       </c>
       <c r="H135" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I135" s="4" t="n">
         <v>14</v>
@@ -8066,7 +8078,7 @@
         <v>11</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E136" s="4" t="n">
         <v>251</v>
@@ -8078,7 +8090,7 @@
         <v>6</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I136" s="4"/>
       <c r="J136" s="4" t="n">
@@ -8112,7 +8124,7 @@
         <v>4</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
@@ -8148,7 +8160,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B139" s="16"/>
       <c r="C139" s="16"/>
@@ -8203,7 +8215,7 @@
         <v>7</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E141" s="4" t="n">
         <v>44</v>
@@ -8215,7 +8227,7 @@
         <v>6</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I141" s="4" t="n">
         <v>8</v>
@@ -8249,7 +8261,7 @@
         <v>2</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I142" s="4"/>
       <c r="J142" s="4" t="n">
@@ -8271,7 +8283,7 @@
         <v>11</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E143" s="4" t="n">
         <v>126</v>
@@ -8283,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I143" s="4"/>
       <c r="J143" s="4" t="n">
@@ -8317,7 +8329,7 @@
         <v>4</v>
       </c>
       <c r="H144" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
@@ -8349,7 +8361,7 @@
         <v>2</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="I145" s="4" t="n">
         <v>7</v>
@@ -8417,7 +8429,7 @@
         <v>5</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I147" s="4"/>
       <c r="J147" s="4" t="n">
@@ -8439,7 +8451,7 @@
         <v>27</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E148" s="4" t="n">
         <v>93</v>
@@ -8451,7 +8463,7 @@
         <v>4</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
@@ -8471,7 +8483,7 @@
         <v>7</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E149" s="4" t="n">
         <v>92</v>
@@ -8483,7 +8495,7 @@
         <v>6</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I149" s="4" t="n">
         <v>15</v>
@@ -8505,7 +8517,7 @@
         <v>11</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E150" s="4" t="n">
         <v>261</v>
@@ -8517,7 +8529,7 @@
         <v>6</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I150" s="4"/>
       <c r="J150" s="4" t="n">
@@ -8551,7 +8563,7 @@
         <v>4</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
@@ -8587,7 +8599,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -8642,7 +8654,7 @@
         <v>7</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E155" s="4" t="n">
         <v>30</v>
@@ -8654,7 +8666,7 @@
         <v>6</v>
       </c>
       <c r="H155" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I155" s="4" t="n">
         <v>5</v>
@@ -8688,7 +8700,7 @@
         <v>2</v>
       </c>
       <c r="H156" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I156" s="4"/>
       <c r="J156" s="4" t="n">
@@ -8710,7 +8722,7 @@
         <v>11</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E157" s="4" t="n">
         <v>81</v>
@@ -8722,7 +8734,7 @@
         <v>5</v>
       </c>
       <c r="H157" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I157" s="4"/>
       <c r="J157" s="4" t="n">
@@ -8756,7 +8768,7 @@
         <v>4</v>
       </c>
       <c r="H158" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
@@ -8788,7 +8800,7 @@
         <v>2</v>
       </c>
       <c r="H159" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I159" s="4" t="n">
         <v>5</v>
@@ -8822,7 +8834,7 @@
         <v>2</v>
       </c>
       <c r="H160" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I160" s="4" t="n">
         <v>3</v>
@@ -8856,7 +8868,7 @@
         <v>3</v>
       </c>
       <c r="H161" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I161" s="4"/>
       <c r="J161" s="4" t="n">
@@ -8878,7 +8890,7 @@
         <v>27</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E162" s="4" t="n">
         <v>68</v>
@@ -8890,7 +8902,7 @@
         <v>4</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
@@ -8910,7 +8922,7 @@
         <v>7</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E163" s="4" t="n">
         <v>62</v>
@@ -8922,7 +8934,7 @@
         <v>5</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I163" s="4" t="n">
         <v>10</v>
@@ -8944,7 +8956,7 @@
         <v>11</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E164" s="4" t="n">
         <v>171</v>
@@ -8956,7 +8968,7 @@
         <v>4</v>
       </c>
       <c r="H164" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I164" s="4"/>
       <c r="J164" s="4" t="n">
@@ -8990,7 +9002,7 @@
         <v>4</v>
       </c>
       <c r="H165" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
@@ -9026,7 +9038,7 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B167" s="16"/>
       <c r="C167" s="16"/>
@@ -9081,7 +9093,7 @@
         <v>7</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E169" s="4" t="n">
         <v>52</v>
@@ -9093,7 +9105,7 @@
         <v>7</v>
       </c>
       <c r="H169" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I169" s="4" t="n">
         <v>8.5</v>
@@ -9127,7 +9139,7 @@
         <v>2</v>
       </c>
       <c r="H170" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I170" s="4"/>
       <c r="J170" s="4" t="n">
@@ -9149,7 +9161,7 @@
         <v>11</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E171" s="4" t="n">
         <v>126</v>
@@ -9161,7 +9173,7 @@
         <v>6</v>
       </c>
       <c r="H171" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I171" s="4"/>
       <c r="J171" s="4" t="n">
@@ -9195,7 +9207,7 @@
         <v>4</v>
       </c>
       <c r="H172" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I172" s="4"/>
       <c r="J172" s="4"/>
@@ -9227,7 +9239,7 @@
         <v>2</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I173" s="4" t="n">
         <v>7.5</v>
@@ -9295,7 +9307,7 @@
         <v>5</v>
       </c>
       <c r="H175" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I175" s="4"/>
       <c r="J175" s="4" t="n">
@@ -9317,7 +9329,7 @@
         <v>27</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E176" s="4" t="n">
         <v>96</v>
@@ -9329,7 +9341,7 @@
         <v>5</v>
       </c>
       <c r="H176" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
@@ -9349,7 +9361,7 @@
         <v>7</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E177" s="4" t="n">
         <v>99</v>
@@ -9361,7 +9373,7 @@
         <v>6</v>
       </c>
       <c r="H177" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I177" s="4" t="n">
         <v>16</v>
@@ -9383,7 +9395,7 @@
         <v>11</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E178" s="4" t="n">
         <v>268</v>
@@ -9395,7 +9407,7 @@
         <v>6</v>
       </c>
       <c r="H178" s="7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4" t="n">
@@ -9429,7 +9441,7 @@
         <v>6</v>
       </c>
       <c r="H179" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
@@ -9465,7 +9477,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B181" s="17"/>
       <c r="C181" s="17"/>
@@ -9520,7 +9532,7 @@
         <v>7</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="E183" s="4" t="n">
         <v>54</v>
@@ -9532,7 +9544,7 @@
         <v>7</v>
       </c>
       <c r="H183" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I183" s="4" t="n">
         <v>9.5</v>
@@ -9566,7 +9578,7 @@
         <v>2</v>
       </c>
       <c r="H184" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I184" s="4"/>
       <c r="J184" s="4" t="n">
@@ -9588,19 +9600,19 @@
         <v>11</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E185" s="4" t="n">
         <v>137</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G185" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H185" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I185" s="4"/>
       <c r="J185" s="4" t="n">
@@ -9634,7 +9646,7 @@
         <v>4</v>
       </c>
       <c r="H186" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
@@ -9666,7 +9678,7 @@
         <v>2</v>
       </c>
       <c r="H187" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I187" s="4" t="n">
         <v>9</v>
@@ -9734,7 +9746,7 @@
         <v>5</v>
       </c>
       <c r="H189" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I189" s="4"/>
       <c r="J189" s="4" t="n">
@@ -9756,7 +9768,7 @@
         <v>27</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E190" s="4" t="n">
         <v>98</v>
@@ -9768,7 +9780,7 @@
         <v>5</v>
       </c>
       <c r="H190" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
@@ -9788,7 +9800,7 @@
         <v>7</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E191" s="4" t="n">
         <v>105</v>
@@ -9800,7 +9812,7 @@
         <v>6</v>
       </c>
       <c r="H191" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I191" s="4" t="n">
         <v>17</v>
@@ -9822,7 +9834,7 @@
         <v>11</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E192" s="4" t="n">
         <v>279</v>
@@ -9834,7 +9846,7 @@
         <v>6</v>
       </c>
       <c r="H192" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I192" s="4"/>
       <c r="J192" s="4" t="n">
@@ -9868,7 +9880,7 @@
         <v>4</v>
       </c>
       <c r="H193" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
@@ -9904,7 +9916,7 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B195" s="17"/>
       <c r="C195" s="17"/>
@@ -9959,7 +9971,7 @@
         <v>7</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E197" s="4" t="n">
         <v>65</v>
@@ -9971,7 +9983,7 @@
         <v>6</v>
       </c>
       <c r="H197" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I197" s="4" t="n">
         <v>11</v>
@@ -10005,7 +10017,7 @@
         <v>2</v>
       </c>
       <c r="H198" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I198" s="4"/>
       <c r="J198" s="4" t="n">
@@ -10027,7 +10039,7 @@
         <v>11</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E199" s="4" t="n">
         <v>146</v>
@@ -10039,7 +10051,7 @@
         <v>6</v>
       </c>
       <c r="H199" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I199" s="4"/>
       <c r="J199" s="4" t="n">
@@ -10073,7 +10085,7 @@
         <v>4</v>
       </c>
       <c r="H200" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
@@ -10105,7 +10117,7 @@
         <v>2</v>
       </c>
       <c r="H201" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I201" s="4" t="n">
         <v>10</v>
@@ -10173,7 +10185,7 @@
         <v>5</v>
       </c>
       <c r="H203" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I203" s="4"/>
       <c r="J203" s="4" t="n">
@@ -10195,7 +10207,7 @@
         <v>27</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E204" s="4" t="n">
         <v>100</v>
@@ -10207,7 +10219,7 @@
         <v>5</v>
       </c>
       <c r="H204" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
@@ -10227,7 +10239,7 @@
         <v>7</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E205" s="4" t="n">
         <v>111</v>
@@ -10239,7 +10251,7 @@
         <v>6</v>
       </c>
       <c r="H205" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I205" s="4" t="n">
         <v>18</v>
@@ -10261,7 +10273,7 @@
         <v>11</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E206" s="4" t="n">
         <v>289</v>
@@ -10273,7 +10285,7 @@
         <v>6</v>
       </c>
       <c r="H206" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I206" s="4"/>
       <c r="J206" s="4" t="n">
@@ -10307,7 +10319,7 @@
         <v>4</v>
       </c>
       <c r="H207" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I207" s="4"/>
       <c r="J207" s="4"/>
@@ -10343,7 +10355,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -10368,7 +10380,7 @@
         <v>2</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="6"/>
@@ -10392,7 +10404,7 @@
         <v>11</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E211" s="4" t="n">
         <v>136</v>
@@ -10404,7 +10416,7 @@
         <v>5</v>
       </c>
       <c r="H211" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I211" s="4"/>
       <c r="J211" s="4" t="n">
@@ -10426,7 +10438,7 @@
         <v>27</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E212" s="4" t="n">
         <v>88</v>
@@ -10438,7 +10450,7 @@
         <v>4</v>
       </c>
       <c r="H212" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I212" s="4"/>
       <c r="J212" s="4"/>
@@ -10458,7 +10470,7 @@
         <v>11</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E213" s="4" t="n">
         <v>100</v>
@@ -10470,7 +10482,7 @@
         <v>3</v>
       </c>
       <c r="H213" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I213" s="4"/>
       <c r="J213" s="4" t="n">
@@ -10492,7 +10504,7 @@
         <v>7</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E214" s="4" t="n">
         <v>65</v>
@@ -10504,7 +10516,7 @@
         <v>6</v>
       </c>
       <c r="H214" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I214" s="4" t="n">
         <v>11.5</v>
@@ -10526,7 +10538,7 @@
         <v>7</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E215" s="4" t="n">
         <v>65</v>
@@ -10538,7 +10550,7 @@
         <v>2</v>
       </c>
       <c r="H215" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I215" s="4" t="n">
         <v>10.5</v>
@@ -10560,7 +10572,7 @@
         <v>2</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="6"/>
@@ -10584,7 +10596,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E217" s="4" t="n">
         <v>111</v>
@@ -10596,7 +10608,7 @@
         <v>6</v>
       </c>
       <c r="H217" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I217" s="4" t="n">
         <v>18</v>
@@ -10634,7 +10646,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -10695,7 +10707,7 @@
         <v>6</v>
       </c>
       <c r="H221" s="7" t="s">
-        <v>125</v>
+        <v>263</v>
       </c>
       <c r="I221" s="4" t="n">
         <v>7.5</v>
@@ -10717,7 +10729,7 @@
         <v>7</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E222" s="4" t="n">
         <v>37</v>
@@ -10729,7 +10741,7 @@
         <v>5</v>
       </c>
       <c r="H222" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I222" s="4" t="n">
         <v>6.5</v>
@@ -10751,7 +10763,7 @@
         <v>7</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E223" s="4" t="n">
         <v>43</v>
@@ -10763,7 +10775,7 @@
         <v>4</v>
       </c>
       <c r="H223" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I223" s="4" t="n">
         <v>7</v>
@@ -10797,7 +10809,7 @@
         <v>2</v>
       </c>
       <c r="H224" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I224" s="4" t="n">
         <v>5</v>
@@ -10819,7 +10831,7 @@
         <v>7</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E225" s="4" t="n">
         <v>117</v>
@@ -10831,7 +10843,7 @@
         <v>6</v>
       </c>
       <c r="H225" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I225" s="4" t="n">
         <v>19</v>
@@ -10853,7 +10865,7 @@
         <v>27</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E226" s="4" t="n">
         <v>99</v>
@@ -10865,7 +10877,7 @@
         <v>5</v>
       </c>
       <c r="H226" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I226" s="4"/>
       <c r="J226" s="4"/>
@@ -10885,7 +10897,7 @@
         <v>11</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E227" s="4" t="n">
         <v>150</v>
@@ -10897,7 +10909,7 @@
         <v>4</v>
       </c>
       <c r="H227" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I227" s="4"/>
       <c r="J227" s="4" t="n">
@@ -10935,7 +10947,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="16" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B229" s="16"/>
       <c r="C229" s="16"/>
@@ -10990,7 +11002,7 @@
         <v>7</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="E231" s="4" t="n">
         <v>60</v>
@@ -11002,7 +11014,7 @@
         <v>7</v>
       </c>
       <c r="H231" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I231" s="4" t="n">
         <v>10.5</v>
@@ -11036,7 +11048,7 @@
         <v>2</v>
       </c>
       <c r="H232" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I232" s="4"/>
       <c r="J232" s="4" t="n">
@@ -11058,7 +11070,7 @@
         <v>11</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E233" s="4" t="n">
         <v>124</v>
@@ -11070,7 +11082,7 @@
         <v>6</v>
       </c>
       <c r="H233" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I233" s="4"/>
       <c r="J233" s="4" t="n">
@@ -11104,7 +11116,7 @@
         <v>4</v>
       </c>
       <c r="H234" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I234" s="4" t="n">
         <v>10</v>
@@ -11126,7 +11138,7 @@
         <v>27</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E235" s="4" t="n">
         <v>58</v>
@@ -11138,7 +11150,7 @@
         <v>2</v>
       </c>
       <c r="H235" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I235" s="4"/>
       <c r="J235" s="4"/>
@@ -11170,7 +11182,7 @@
         <v>2</v>
       </c>
       <c r="H236" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I236" s="4" t="n">
         <v>5</v>
@@ -11204,7 +11216,7 @@
         <v>5</v>
       </c>
       <c r="H237" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I237" s="4"/>
       <c r="J237" s="4" t="n">
@@ -11226,7 +11238,7 @@
         <v>27</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E238" s="4" t="n">
         <v>86</v>
@@ -11238,7 +11250,7 @@
         <v>5</v>
       </c>
       <c r="H238" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I238" s="4"/>
       <c r="J238" s="4"/>
@@ -11258,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E239" s="4" t="n">
         <v>117</v>
@@ -11270,7 +11282,7 @@
         <v>6</v>
       </c>
       <c r="H239" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I239" s="4" t="n">
         <v>19</v>
@@ -11292,7 +11304,7 @@
         <v>11</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E240" s="4" t="n">
         <v>257</v>
@@ -11304,7 +11316,7 @@
         <v>6</v>
       </c>
       <c r="H240" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I240" s="4"/>
       <c r="J240" s="4" t="n">
@@ -11326,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E241" s="4" t="n">
         <v>15</v>
@@ -11338,7 +11350,7 @@
         <v>4</v>
       </c>
       <c r="H241" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I241" s="4" t="n">
         <v>2.5</v>
@@ -11358,7 +11370,7 @@
         <v>27</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E242" s="4" t="n">
         <v>63</v>
@@ -11370,7 +11382,7 @@
         <v>7</v>
       </c>
       <c r="H242" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I242" s="4"/>
       <c r="J242" s="4"/>
@@ -11406,7 +11418,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="18" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B244" s="18"/>
       <c r="C244" s="18"/>
@@ -11454,7 +11466,7 @@
         <v>7</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E246" s="4" t="n">
         <v>65</v>
@@ -11466,7 +11478,7 @@
         <v>6</v>
       </c>
       <c r="H246" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I246" s="4" t="n">
         <v>11</v>
@@ -11500,7 +11512,7 @@
         <v>2</v>
       </c>
       <c r="H247" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I247" s="4"/>
       <c r="J247" s="4" t="n">
@@ -11522,7 +11534,7 @@
         <v>11</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E248" s="4" t="n">
         <v>131</v>
@@ -11534,7 +11546,7 @@
         <v>6</v>
       </c>
       <c r="H248" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I248" s="4"/>
       <c r="J248" s="4" t="n">
@@ -11568,7 +11580,7 @@
         <v>4</v>
       </c>
       <c r="H249" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I249" s="4" t="n">
         <v>10.5</v>
@@ -11590,7 +11602,7 @@
         <v>27</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E250" s="4" t="n">
         <v>63</v>
@@ -11602,7 +11614,7 @@
         <v>2</v>
       </c>
       <c r="H250" s="7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I250" s="4"/>
       <c r="J250" s="4"/>
@@ -11634,7 +11646,7 @@
         <v>2</v>
       </c>
       <c r="H251" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I251" s="4" t="n">
         <v>5</v>
@@ -11668,7 +11680,7 @@
         <v>5</v>
       </c>
       <c r="H252" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I252" s="4"/>
       <c r="J252" s="4" t="n">
@@ -11690,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E253" s="4" t="n">
         <v>94</v>
@@ -11702,7 +11714,7 @@
         <v>5</v>
       </c>
       <c r="H253" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I253" s="4"/>
       <c r="J253" s="4"/>
@@ -11722,7 +11734,7 @@
         <v>7</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E254" s="4" t="n">
         <v>123</v>
@@ -11734,7 +11746,7 @@
         <v>6</v>
       </c>
       <c r="H254" s="7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I254" s="4" t="n">
         <v>20</v>
@@ -11756,7 +11768,7 @@
         <v>11</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E255" s="4" t="n">
         <v>279</v>
@@ -11768,7 +11780,7 @@
         <v>6</v>
       </c>
       <c r="H255" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I255" s="4"/>
       <c r="J255" s="4" t="n">
@@ -11790,7 +11802,7 @@
         <v>7</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E256" s="4" t="n">
         <v>20</v>
@@ -11802,7 +11814,7 @@
         <v>4</v>
       </c>
       <c r="H256" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I256" s="4" t="n">
         <v>3.5</v>
@@ -11834,7 +11846,7 @@
         <v>4</v>
       </c>
       <c r="H257" s="7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I257" s="4"/>
       <c r="J257" s="4"/>
@@ -11870,7 +11882,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B259" s="16"/>
       <c r="C259" s="16"/>
@@ -11925,7 +11937,7 @@
         <v>7</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E261" s="4" t="n">
         <v>70</v>
@@ -11937,7 +11949,7 @@
         <v>6</v>
       </c>
       <c r="H261" s="7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I261" s="4" t="n">
         <v>12</v>
@@ -11971,7 +11983,7 @@
         <v>2</v>
       </c>
       <c r="H262" s="7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I262" s="4"/>
       <c r="J262" s="4" t="n">
@@ -11993,7 +12005,7 @@
         <v>11</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E263" s="4" t="n">
         <v>137</v>
@@ -12005,7 +12017,7 @@
         <v>6</v>
       </c>
       <c r="H263" s="7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I263" s="4"/>
       <c r="J263" s="4" t="n">
@@ -12039,7 +12051,7 @@
         <v>4</v>
       </c>
       <c r="H264" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I264" s="4" t="n">
         <v>11.5</v>
@@ -12061,7 +12073,7 @@
         <v>27</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E265" s="4" t="n">
         <v>67</v>
@@ -12073,7 +12085,7 @@
         <v>2</v>
       </c>
       <c r="H265" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I265" s="4"/>
       <c r="J265" s="4"/>
@@ -12105,7 +12117,7 @@
         <v>2</v>
       </c>
       <c r="H266" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I266" s="4" t="n">
         <v>5</v>
@@ -12139,7 +12151,7 @@
         <v>5</v>
       </c>
       <c r="H267" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I267" s="4"/>
       <c r="J267" s="4" t="n">
@@ -12161,7 +12173,7 @@
         <v>27</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E268" s="4" t="n">
         <v>98</v>
@@ -12173,7 +12185,7 @@
         <v>5</v>
       </c>
       <c r="H268" s="7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I268" s="4"/>
       <c r="J268" s="4"/>
@@ -12193,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E269" s="4" t="n">
         <v>130</v>
@@ -12205,7 +12217,7 @@
         <v>6</v>
       </c>
       <c r="H269" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I269" s="4" t="n">
         <v>21</v>
@@ -12227,7 +12239,7 @@
         <v>11</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E270" s="4" t="n">
         <v>296</v>
@@ -12239,7 +12251,7 @@
         <v>6</v>
       </c>
       <c r="H270" s="7" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I270" s="4"/>
       <c r="J270" s="4" t="n">
@@ -12261,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E271" s="4" t="n">
         <v>20</v>
@@ -12273,7 +12285,7 @@
         <v>4</v>
       </c>
       <c r="H271" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I271" s="4" t="n">
         <v>3.5</v>
@@ -12305,7 +12317,7 @@
         <v>6</v>
       </c>
       <c r="H272" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I272" s="4"/>
       <c r="J272" s="4"/>
@@ -12341,7 +12353,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -12396,7 +12408,7 @@
         <v>7</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E276" s="4" t="n">
         <v>46</v>
@@ -12408,7 +12420,7 @@
         <v>6</v>
       </c>
       <c r="H276" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I276" s="4" t="n">
         <v>8</v>
@@ -12442,7 +12454,7 @@
         <v>2</v>
       </c>
       <c r="H277" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I277" s="4"/>
       <c r="J277" s="4" t="n">
@@ -12464,7 +12476,7 @@
         <v>11</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E278" s="4" t="n">
         <v>90</v>
@@ -12476,7 +12488,7 @@
         <v>5</v>
       </c>
       <c r="H278" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I278" s="4"/>
       <c r="J278" s="4" t="n">
@@ -12510,7 +12522,7 @@
         <v>2</v>
       </c>
       <c r="H279" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I279" s="4" t="n">
         <v>7.5</v>
@@ -12532,7 +12544,7 @@
         <v>27</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E280" s="4" t="n">
         <v>71</v>
@@ -12544,7 +12556,7 @@
         <v>2</v>
       </c>
       <c r="H280" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I280" s="4"/>
       <c r="J280" s="4"/>
@@ -12610,7 +12622,7 @@
         <v>3</v>
       </c>
       <c r="H282" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I282" s="4"/>
       <c r="J282" s="4" t="n">
@@ -12632,7 +12644,7 @@
         <v>27</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E283" s="4" t="n">
         <v>86</v>
@@ -12644,7 +12656,7 @@
         <v>5</v>
       </c>
       <c r="H283" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I283" s="4"/>
       <c r="J283" s="4"/>
@@ -12664,7 +12676,7 @@
         <v>7</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E284" s="4" t="n">
         <v>86</v>
@@ -12676,7 +12688,7 @@
         <v>6</v>
       </c>
       <c r="H284" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I284" s="4" t="n">
         <v>14</v>
@@ -12698,7 +12710,7 @@
         <v>11</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E285" s="4" t="n">
         <v>193</v>
@@ -12710,7 +12722,7 @@
         <v>4</v>
       </c>
       <c r="H285" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I285" s="4"/>
       <c r="J285" s="4" t="n">
@@ -12732,7 +12744,7 @@
         <v>7</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E286" s="4" t="n">
         <v>15</v>
@@ -12744,7 +12756,7 @@
         <v>4</v>
       </c>
       <c r="H286" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I286" s="4" t="n">
         <v>2.5</v>
@@ -12780,7 +12792,7 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="16" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B288" s="16"/>
       <c r="C288" s="16"/>
@@ -12828,7 +12840,7 @@
         <v>7</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E290" s="4" t="n">
         <v>66</v>
@@ -12840,7 +12852,7 @@
         <v>7</v>
       </c>
       <c r="H290" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I290" s="4" t="n">
         <v>12.5</v>
@@ -12874,7 +12886,7 @@
         <v>2</v>
       </c>
       <c r="H291" s="7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I291" s="4"/>
       <c r="J291" s="4" t="n">
@@ -12896,7 +12908,7 @@
         <v>11</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E292" s="4" t="n">
         <v>141</v>
@@ -12908,7 +12920,7 @@
         <v>8</v>
       </c>
       <c r="H292" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I292" s="4"/>
       <c r="J292" s="4" t="n">
@@ -12942,7 +12954,7 @@
         <v>4</v>
       </c>
       <c r="H293" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I293" s="4" t="n">
         <v>12</v>
@@ -12964,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E294" s="4" t="n">
         <v>67</v>
@@ -12976,7 +12988,7 @@
         <v>2</v>
       </c>
       <c r="H294" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I294" s="4"/>
       <c r="J294" s="4"/>
@@ -13008,7 +13020,7 @@
         <v>2</v>
       </c>
       <c r="H295" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I295" s="4" t="n">
         <v>5</v>
@@ -13042,7 +13054,7 @@
         <v>5</v>
       </c>
       <c r="H296" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I296" s="4"/>
       <c r="J296" s="4" t="n">
@@ -13064,7 +13076,7 @@
         <v>27</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E297" s="4" t="n">
         <v>99</v>
@@ -13076,7 +13088,7 @@
         <v>5</v>
       </c>
       <c r="H297" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I297" s="4"/>
       <c r="J297" s="4"/>
@@ -13096,7 +13108,7 @@
         <v>7</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E298" s="4" t="n">
         <v>136</v>
@@ -13108,7 +13120,7 @@
         <v>6</v>
       </c>
       <c r="H298" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I298" s="4" t="n">
         <v>22</v>
@@ -13130,7 +13142,7 @@
         <v>11</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E299" s="4" t="n">
         <v>300</v>
@@ -13142,7 +13154,7 @@
         <v>6</v>
       </c>
       <c r="H299" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I299" s="4"/>
       <c r="J299" s="4" t="n">
@@ -13164,7 +13176,7 @@
         <v>7</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E300" s="4" t="n">
         <v>20</v>
@@ -13176,7 +13188,7 @@
         <v>4</v>
       </c>
       <c r="H300" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I300" s="4" t="n">
         <v>3.5</v>
@@ -13208,7 +13220,7 @@
         <v>4</v>
       </c>
       <c r="H301" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I301" s="4"/>
       <c r="J301" s="4"/>
@@ -13244,7 +13256,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B303" s="16"/>
       <c r="C303" s="16"/>
@@ -13299,7 +13311,7 @@
         <v>7</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E305" s="4" t="n">
         <v>81</v>
@@ -13311,7 +13323,7 @@
         <v>7</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I305" s="4" t="n">
         <v>15.5</v>
@@ -13345,7 +13357,7 @@
         <v>2</v>
       </c>
       <c r="H306" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I306" s="4"/>
       <c r="J306" s="4" t="n">
@@ -13367,7 +13379,7 @@
         <v>27</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E307" s="4" t="n">
         <v>65</v>
@@ -13379,7 +13391,7 @@
         <v>4</v>
       </c>
       <c r="H307" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I307" s="4"/>
       <c r="J307" s="4"/>
@@ -13399,19 +13411,19 @@
         <v>11</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E308" s="4" t="n">
         <v>150</v>
       </c>
       <c r="F308" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G308" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H308" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I308" s="4"/>
       <c r="J308" s="4" t="n">
@@ -13445,7 +13457,7 @@
         <v>4</v>
       </c>
       <c r="H309" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I309" s="4" t="n">
         <v>14.5</v>
@@ -13467,7 +13479,7 @@
         <v>27</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E310" s="4" t="n">
         <v>74</v>
@@ -13479,7 +13491,7 @@
         <v>2</v>
       </c>
       <c r="H310" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I310" s="4"/>
       <c r="J310" s="4"/>
@@ -13511,7 +13523,7 @@
         <v>2</v>
       </c>
       <c r="H311" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I311" s="4" t="n">
         <v>5</v>
@@ -13545,7 +13557,7 @@
         <v>5</v>
       </c>
       <c r="H312" s="7" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I312" s="4"/>
       <c r="J312" s="4" t="n">
@@ -13567,7 +13579,7 @@
         <v>7</v>
       </c>
       <c r="D313" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E313" s="4" t="n">
         <v>142</v>
@@ -13579,7 +13591,7 @@
         <v>6</v>
       </c>
       <c r="H313" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I313" s="4" t="n">
         <v>23</v>
@@ -13601,7 +13613,7 @@
         <v>11</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E314" s="4" t="n">
         <v>311</v>
@@ -13613,7 +13625,7 @@
         <v>6</v>
       </c>
       <c r="H314" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I314" s="4"/>
       <c r="J314" s="4" t="n">
@@ -13651,7 +13663,7 @@
     </row>
     <row r="316" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="20" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>
@@ -13706,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D318" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E318" s="4" t="n">
         <v>86</v>
@@ -13718,7 +13730,7 @@
         <v>7</v>
       </c>
       <c r="H318" s="7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I318" s="4" t="n">
         <v>15</v>
@@ -13752,7 +13764,7 @@
         <v>2</v>
       </c>
       <c r="H319" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I319" s="4"/>
       <c r="J319" s="4" t="n">
@@ -13774,7 +13786,7 @@
         <v>11</v>
       </c>
       <c r="D320" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E320" s="4" t="n">
         <v>159</v>
@@ -13786,7 +13798,7 @@
         <v>6</v>
       </c>
       <c r="H320" s="7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I320" s="4"/>
       <c r="J320" s="4" t="n">
@@ -13820,7 +13832,7 @@
         <v>4</v>
       </c>
       <c r="H321" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I321" s="4" t="n">
         <v>13.5</v>
@@ -13842,7 +13854,7 @@
         <v>27</v>
       </c>
       <c r="D322" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E322" s="4" t="n">
         <v>68</v>
@@ -13854,7 +13866,7 @@
         <v>2</v>
       </c>
       <c r="H322" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I322" s="4"/>
       <c r="J322" s="4"/>
@@ -13886,7 +13898,7 @@
         <v>2</v>
       </c>
       <c r="H323" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I323" s="4" t="n">
         <v>5</v>
@@ -13920,7 +13932,7 @@
         <v>5</v>
       </c>
       <c r="H324" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I324" s="4"/>
       <c r="J324" s="4" t="n">
@@ -13942,7 +13954,7 @@
         <v>27</v>
       </c>
       <c r="D325" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E325" s="4" t="n">
         <v>101</v>
@@ -13954,7 +13966,7 @@
         <v>5</v>
       </c>
       <c r="H325" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I325" s="4"/>
       <c r="J325" s="4"/>
@@ -13974,7 +13986,7 @@
         <v>7</v>
       </c>
       <c r="D326" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E326" s="4" t="n">
         <v>148</v>
@@ -13986,7 +13998,7 @@
         <v>6</v>
       </c>
       <c r="H326" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I326" s="4" t="n">
         <v>24</v>
@@ -14008,7 +14020,7 @@
         <v>11</v>
       </c>
       <c r="D327" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E327" s="4" t="n">
         <v>321</v>
@@ -14020,7 +14032,7 @@
         <v>6</v>
       </c>
       <c r="H327" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I327" s="4"/>
       <c r="J327" s="4" t="n">
@@ -14042,7 +14054,7 @@
         <v>7</v>
       </c>
       <c r="D328" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E328" s="4" t="n">
         <v>25</v>
@@ -14054,7 +14066,7 @@
         <v>4</v>
       </c>
       <c r="H328" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I328" s="4" t="n">
         <v>4.5</v>
@@ -14086,7 +14098,7 @@
         <v>6</v>
       </c>
       <c r="H329" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I329" s="4"/>
       <c r="J329" s="4"/>
@@ -14122,7 +14134,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -14177,7 +14189,7 @@
         <v>7</v>
       </c>
       <c r="D333" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E333" s="4" t="n">
         <v>92</v>
@@ -14189,7 +14201,7 @@
         <v>7</v>
       </c>
       <c r="H333" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I333" s="4" t="n">
         <v>16.5</v>
@@ -14223,7 +14235,7 @@
         <v>2</v>
       </c>
       <c r="H334" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I334" s="4"/>
       <c r="J334" s="4" t="n">
@@ -14245,7 +14257,7 @@
         <v>11</v>
       </c>
       <c r="D335" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E335" s="4" t="n">
         <v>167</v>
@@ -14257,7 +14269,7 @@
         <v>6</v>
       </c>
       <c r="H335" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I335" s="4"/>
       <c r="J335" s="4" t="n">
@@ -14291,7 +14303,7 @@
         <v>4</v>
       </c>
       <c r="H336" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I336" s="4" t="n">
         <v>15</v>
@@ -14313,7 +14325,7 @@
         <v>27</v>
       </c>
       <c r="D337" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E337" s="4" t="n">
         <v>72</v>
@@ -14325,7 +14337,7 @@
         <v>2</v>
       </c>
       <c r="H337" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I337" s="4"/>
       <c r="J337" s="4"/>
@@ -14357,7 +14369,7 @@
         <v>2</v>
       </c>
       <c r="H338" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I338" s="4" t="n">
         <v>5</v>
@@ -14391,7 +14403,7 @@
         <v>5</v>
       </c>
       <c r="H339" s="7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I339" s="4"/>
       <c r="J339" s="4" t="n">
@@ -14413,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="D340" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E340" s="4" t="n">
         <v>103</v>
@@ -14425,7 +14437,7 @@
         <v>5</v>
       </c>
       <c r="H340" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I340" s="4"/>
       <c r="J340" s="4"/>
@@ -14445,7 +14457,7 @@
         <v>7</v>
       </c>
       <c r="D341" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E341" s="4" t="n">
         <v>154</v>
@@ -14457,7 +14469,7 @@
         <v>6</v>
       </c>
       <c r="H341" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I341" s="4" t="n">
         <v>25</v>
@@ -14479,7 +14491,7 @@
         <v>11</v>
       </c>
       <c r="D342" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E342" s="4" t="n">
         <v>332</v>
@@ -14491,7 +14503,7 @@
         <v>6</v>
       </c>
       <c r="H342" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I342" s="4"/>
       <c r="J342" s="4" t="n">
@@ -14513,7 +14525,7 @@
         <v>7</v>
       </c>
       <c r="D343" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E343" s="4" t="n">
         <v>25</v>
@@ -14525,7 +14537,7 @@
         <v>4</v>
       </c>
       <c r="H343" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I343" s="4" t="n">
         <v>4.5</v>
@@ -14557,7 +14569,7 @@
         <v>4</v>
       </c>
       <c r="H344" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I344" s="4"/>
       <c r="J344" s="4"/>
@@ -14593,7 +14605,7 @@
     </row>
     <row r="346" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="16" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B346" s="16"/>
       <c r="C346" s="16"/>
@@ -14618,7 +14630,7 @@
         <v>2</v>
       </c>
       <c r="D347" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E347" s="4" t="s">
         <v>4</v>
@@ -14630,7 +14642,7 @@
         <v>1</v>
       </c>
       <c r="H347" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I347" s="4"/>
       <c r="J347" s="4"/>
@@ -14645,22 +14657,22 @@
         <v>6</v>
       </c>
       <c r="C348" s="21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D348" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E348" s="4" t="n">
         <v>360</v>
       </c>
       <c r="F348" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G348" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H348" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I348" s="4"/>
       <c r="J348" s="4"/>
@@ -14677,22 +14689,22 @@
         <v>14</v>
       </c>
       <c r="C349" s="21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D349" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E349" s="4" t="n">
         <v>360</v>
       </c>
       <c r="F349" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G349" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H349" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I349" s="4"/>
       <c r="J349" s="4"/>
@@ -14709,22 +14721,22 @@
         <v>17</v>
       </c>
       <c r="C350" s="21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D350" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E350" s="4" t="n">
         <v>360</v>
       </c>
       <c r="F350" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G350" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H350" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I350" s="4"/>
       <c r="J350" s="4"/>
@@ -14741,22 +14753,22 @@
         <v>21</v>
       </c>
       <c r="C351" s="21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D351" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E351" s="4" t="n">
         <v>360</v>
       </c>
       <c r="F351" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G351" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H351" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I351" s="4"/>
       <c r="J351" s="4"/>
@@ -14773,22 +14785,22 @@
         <v>26</v>
       </c>
       <c r="C352" s="21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D352" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E352" s="4" t="n">
         <v>360</v>
       </c>
       <c r="F352" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G352" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H352" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I352" s="4"/>
       <c r="J352" s="4"/>
@@ -14808,7 +14820,7 @@
         <v>2</v>
       </c>
       <c r="D353" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E353" s="4" t="s">
         <v>4</v>
@@ -14820,7 +14832,7 @@
         <v>1</v>
       </c>
       <c r="H353" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I353" s="4"/>
       <c r="J353" s="4"/>
@@ -14854,7 +14866,7 @@
     </row>
     <row r="355" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="16" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B355" s="16"/>
       <c r="C355" s="16"/>
@@ -14909,7 +14921,7 @@
         <v>7</v>
       </c>
       <c r="D357" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E357" s="4" t="n">
         <v>66</v>
@@ -14921,7 +14933,7 @@
         <v>5</v>
       </c>
       <c r="H357" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I357" s="4" t="n">
         <v>11.5</v>
@@ -14955,7 +14967,7 @@
         <v>2</v>
       </c>
       <c r="H358" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I358" s="4"/>
       <c r="J358" s="4" t="n">
@@ -14977,7 +14989,7 @@
         <v>11</v>
       </c>
       <c r="D359" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E359" s="4" t="n">
         <v>124</v>
@@ -14989,7 +15001,7 @@
         <v>3</v>
       </c>
       <c r="H359" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I359" s="4"/>
       <c r="J359" s="4" t="n">
@@ -15023,7 +15035,7 @@
         <v>4</v>
       </c>
       <c r="H360" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I360" s="4" t="n">
         <v>11</v>
@@ -15045,7 +15057,7 @@
         <v>27</v>
       </c>
       <c r="D361" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E361" s="4" t="n">
         <v>57</v>
@@ -15057,7 +15069,7 @@
         <v>2</v>
       </c>
       <c r="H361" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I361" s="4"/>
       <c r="J361" s="4"/>
@@ -15089,7 +15101,7 @@
         <v>2</v>
       </c>
       <c r="H362" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I362" s="4" t="n">
         <v>5</v>
@@ -15111,7 +15123,7 @@
         <v>11</v>
       </c>
       <c r="D363" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E363" s="4" t="n">
         <v>103</v>
@@ -15123,7 +15135,7 @@
         <v>2</v>
       </c>
       <c r="H363" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I363" s="4"/>
       <c r="J363" s="4" t="n">
@@ -15145,7 +15157,7 @@
         <v>27</v>
       </c>
       <c r="D364" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E364" s="4" t="n">
         <v>84</v>
@@ -15157,7 +15169,7 @@
         <v>5</v>
       </c>
       <c r="H364" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I364" s="4"/>
       <c r="J364" s="4"/>
@@ -15177,7 +15189,7 @@
         <v>7</v>
       </c>
       <c r="D365" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E365" s="4" t="n">
         <v>123</v>
@@ -15189,7 +15201,7 @@
         <v>6</v>
       </c>
       <c r="H365" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I365" s="4" t="n">
         <v>20</v>
@@ -15211,7 +15223,7 @@
         <v>11</v>
       </c>
       <c r="D366" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E366" s="4" t="n">
         <v>257</v>
@@ -15223,7 +15235,7 @@
         <v>6</v>
       </c>
       <c r="H366" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I366" s="4"/>
       <c r="J366" s="4" t="n">
@@ -15245,7 +15257,7 @@
         <v>7</v>
       </c>
       <c r="D367" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E367" s="4" t="n">
         <v>15</v>
@@ -15257,7 +15269,7 @@
         <v>4</v>
       </c>
       <c r="H367" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I367" s="4" t="n">
         <v>2.5</v>
@@ -15289,7 +15301,7 @@
         <v>4</v>
       </c>
       <c r="H368" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I368" s="4"/>
       <c r="J368" s="4"/>
@@ -15325,7 +15337,7 @@
     </row>
     <row r="370" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="16" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B370" s="16"/>
       <c r="C370" s="16"/>
@@ -15380,7 +15392,7 @@
         <v>7</v>
       </c>
       <c r="D372" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E372" s="4" t="n">
         <v>80</v>
@@ -15392,7 +15404,7 @@
         <v>6</v>
       </c>
       <c r="H372" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I372" s="4" t="n">
         <v>14.5</v>
@@ -15426,7 +15438,7 @@
         <v>2</v>
       </c>
       <c r="H373" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I373" s="4"/>
       <c r="J373" s="4" t="n">
@@ -15448,7 +15460,7 @@
         <v>11</v>
       </c>
       <c r="D374" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E374" s="4" t="n">
         <v>146</v>
@@ -15460,7 +15472,7 @@
         <v>6</v>
       </c>
       <c r="H374" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I374" s="4"/>
       <c r="J374" s="4" t="n">
@@ -15494,7 +15506,7 @@
         <v>4</v>
       </c>
       <c r="H375" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I375" s="4" t="n">
         <v>13</v>
@@ -15516,7 +15528,7 @@
         <v>27</v>
       </c>
       <c r="D376" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E376" s="4" t="n">
         <v>65</v>
@@ -15528,7 +15540,7 @@
         <v>2</v>
       </c>
       <c r="H376" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I376" s="4"/>
       <c r="J376" s="4"/>
@@ -15560,7 +15572,7 @@
         <v>2</v>
       </c>
       <c r="H377" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I377" s="4" t="n">
         <v>6</v>
@@ -15594,7 +15606,7 @@
         <v>5</v>
       </c>
       <c r="H378" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I378" s="4"/>
       <c r="J378" s="4" t="n">
@@ -15616,7 +15628,7 @@
         <v>27</v>
       </c>
       <c r="D379" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E379" s="4" t="n">
         <v>96</v>
@@ -15628,7 +15640,7 @@
         <v>5</v>
       </c>
       <c r="H379" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I379" s="4"/>
       <c r="J379" s="4"/>
@@ -15648,7 +15660,7 @@
         <v>7</v>
       </c>
       <c r="D380" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E380" s="4" t="n">
         <v>142</v>
@@ -15660,7 +15672,7 @@
         <v>7</v>
       </c>
       <c r="H380" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="I380" s="4" t="n">
         <v>23</v>
@@ -15682,7 +15694,7 @@
         <v>11</v>
       </c>
       <c r="D381" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E381" s="4" t="n">
         <v>300</v>
@@ -15694,7 +15706,7 @@
         <v>6</v>
       </c>
       <c r="H381" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I381" s="4"/>
       <c r="J381" s="4" t="n">
@@ -15716,7 +15728,7 @@
         <v>7</v>
       </c>
       <c r="D382" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E382" s="4" t="n">
         <v>20</v>
@@ -15728,7 +15740,7 @@
         <v>4</v>
       </c>
       <c r="H382" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I382" s="4" t="n">
         <v>3.5</v>
@@ -15748,7 +15760,7 @@
         <v>27</v>
       </c>
       <c r="D383" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E383" s="4" t="n">
         <v>71</v>
@@ -15760,7 +15772,7 @@
         <v>7</v>
       </c>
       <c r="H383" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I383" s="4"/>
       <c r="J383" s="4"/>
@@ -15796,7 +15808,7 @@
     </row>
     <row r="385" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -15851,7 +15863,7 @@
         <v>7</v>
       </c>
       <c r="D387" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E387" s="4" t="n">
         <v>60</v>
@@ -15863,7 +15875,7 @@
         <v>6</v>
       </c>
       <c r="H387" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I387" s="4" t="n">
         <v>10.5</v>
@@ -15897,7 +15909,7 @@
         <v>2</v>
       </c>
       <c r="H388" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I388" s="4"/>
       <c r="J388" s="4" t="n">
@@ -15919,7 +15931,7 @@
         <v>11</v>
       </c>
       <c r="D389" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E389" s="4" t="n">
         <v>94</v>
@@ -15931,7 +15943,7 @@
         <v>5</v>
       </c>
       <c r="H389" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I389" s="4"/>
       <c r="J389" s="4" t="n">
@@ -15965,7 +15977,7 @@
         <v>2</v>
       </c>
       <c r="H390" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I390" s="4" t="n">
         <v>9.5</v>
@@ -15987,7 +15999,7 @@
         <v>27</v>
       </c>
       <c r="D391" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E391" s="4" t="n">
         <v>47</v>
@@ -15999,7 +16011,7 @@
         <v>2</v>
       </c>
       <c r="H391" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I391" s="4"/>
       <c r="J391" s="4"/>
@@ -16031,7 +16043,7 @@
         <v>2</v>
       </c>
       <c r="H392" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I392" s="4" t="n">
         <v>5</v>
@@ -16065,7 +16077,7 @@
         <v>3</v>
       </c>
       <c r="H393" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I393" s="4"/>
       <c r="J393" s="4" t="n">
@@ -16087,7 +16099,7 @@
         <v>27</v>
       </c>
       <c r="D394" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E394" s="4" t="n">
         <v>73</v>
@@ -16099,7 +16111,7 @@
         <v>5</v>
       </c>
       <c r="H394" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I394" s="4"/>
       <c r="J394" s="4"/>
@@ -16119,7 +16131,7 @@
         <v>7</v>
       </c>
       <c r="D395" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E395" s="4" t="n">
         <v>105</v>
@@ -16131,7 +16143,7 @@
         <v>6</v>
       </c>
       <c r="H395" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="I395" s="4" t="n">
         <v>17</v>
@@ -16153,7 +16165,7 @@
         <v>11</v>
       </c>
       <c r="D396" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E396" s="4" t="n">
         <v>214</v>
@@ -16165,7 +16177,7 @@
         <v>4</v>
       </c>
       <c r="H396" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I396" s="4"/>
       <c r="J396" s="4" t="n">
@@ -16199,7 +16211,7 @@
         <v>4</v>
       </c>
       <c r="H397" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I397" s="4"/>
       <c r="J397" s="4"/>
@@ -16235,7 +16247,7 @@
     </row>
     <row r="399" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="16" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B399" s="16"/>
       <c r="C399" s="16"/>
@@ -16290,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D401" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E401" s="4" t="n">
         <v>78</v>
@@ -16302,7 +16314,7 @@
         <v>7</v>
       </c>
       <c r="H401" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="I401" s="4" t="n">
         <v>15</v>
@@ -16336,7 +16348,7 @@
         <v>2</v>
       </c>
       <c r="H402" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I402" s="4"/>
       <c r="J402" s="4" t="n">
@@ -16358,7 +16370,7 @@
         <v>11</v>
       </c>
       <c r="D403" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E403" s="4" t="n">
         <v>150</v>
@@ -16370,7 +16382,7 @@
         <v>6</v>
       </c>
       <c r="H403" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I403" s="4"/>
       <c r="J403" s="4" t="n">
@@ -16404,7 +16416,7 @@
         <v>4</v>
       </c>
       <c r="H404" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I404" s="4" t="n">
         <v>13.5</v>
@@ -16426,7 +16438,7 @@
         <v>27</v>
       </c>
       <c r="D405" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E405" s="4" t="n">
         <v>68</v>
@@ -16438,7 +16450,7 @@
         <v>2</v>
       </c>
       <c r="H405" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I405" s="4"/>
       <c r="J405" s="4"/>
@@ -16470,7 +16482,7 @@
         <v>2</v>
       </c>
       <c r="H406" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I406" s="4" t="n">
         <v>6</v>
@@ -16504,7 +16516,7 @@
         <v>5</v>
       </c>
       <c r="H407" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I407" s="4"/>
       <c r="J407" s="4" t="n">
@@ -16526,7 +16538,7 @@
         <v>27</v>
       </c>
       <c r="D408" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E408" s="4" t="n">
         <v>99</v>
@@ -16538,7 +16550,7 @@
         <v>5</v>
       </c>
       <c r="H408" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I408" s="4"/>
       <c r="J408" s="4"/>
@@ -16558,7 +16570,7 @@
         <v>7</v>
       </c>
       <c r="D409" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E409" s="4" t="n">
         <v>154</v>
@@ -16570,7 +16582,7 @@
         <v>7</v>
       </c>
       <c r="H409" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I409" s="4" t="n">
         <v>25</v>
@@ -16592,7 +16604,7 @@
         <v>11</v>
       </c>
       <c r="D410" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E410" s="4" t="n">
         <v>321</v>
@@ -16604,7 +16616,7 @@
         <v>6</v>
       </c>
       <c r="H410" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I410" s="4"/>
       <c r="J410" s="4" t="n">
@@ -16626,7 +16638,7 @@
         <v>7</v>
       </c>
       <c r="D411" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E411" s="4" t="n">
         <v>25</v>
@@ -16638,7 +16650,7 @@
         <v>4</v>
       </c>
       <c r="H411" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I411" s="4" t="n">
         <v>4.5</v>
@@ -16670,7 +16682,7 @@
         <v>6</v>
       </c>
       <c r="H412" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I412" s="4"/>
       <c r="J412" s="4"/>
@@ -16706,7 +16718,7 @@
     </row>
     <row r="414" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="16" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B414" s="16"/>
       <c r="C414" s="16"/>
@@ -16761,7 +16773,7 @@
         <v>7</v>
       </c>
       <c r="D416" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E416" s="4" t="n">
         <v>80</v>
@@ -16773,7 +16785,7 @@
         <v>6</v>
       </c>
       <c r="H416" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I416" s="4" t="n">
         <v>14</v>
@@ -16807,7 +16819,7 @@
         <v>2</v>
       </c>
       <c r="H417" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I417" s="4"/>
       <c r="J417" s="4" t="n">
@@ -16829,7 +16841,7 @@
         <v>11</v>
       </c>
       <c r="D418" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E418" s="4" t="n">
         <v>163</v>
@@ -16841,7 +16853,7 @@
         <v>6</v>
       </c>
       <c r="H418" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I418" s="4"/>
       <c r="J418" s="4" t="n">
@@ -16875,7 +16887,7 @@
         <v>4</v>
       </c>
       <c r="H419" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I419" s="4" t="n">
         <v>13</v>
@@ -16897,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="D420" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E420" s="4" t="n">
         <v>81</v>
@@ -16909,7 +16921,7 @@
         <v>2</v>
       </c>
       <c r="H420" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I420" s="4"/>
       <c r="J420" s="4"/>
@@ -16941,7 +16953,7 @@
         <v>2</v>
       </c>
       <c r="H421" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I421" s="4" t="n">
         <v>6</v>
@@ -16975,7 +16987,7 @@
         <v>5</v>
       </c>
       <c r="H422" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I422" s="4"/>
       <c r="J422" s="4" t="n">
@@ -16997,7 +17009,7 @@
         <v>27</v>
       </c>
       <c r="D423" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E423" s="4" t="n">
         <v>70</v>
@@ -17009,7 +17021,7 @@
         <v>4</v>
       </c>
       <c r="H423" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I423" s="4"/>
       <c r="J423" s="4"/>
@@ -17029,7 +17041,7 @@
         <v>11</v>
       </c>
       <c r="D424" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E424" s="4" t="n">
         <v>300</v>
@@ -17041,7 +17053,7 @@
         <v>7</v>
       </c>
       <c r="H424" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I424" s="4"/>
       <c r="J424" s="4" t="n">
@@ -17063,7 +17075,7 @@
         <v>7</v>
       </c>
       <c r="D425" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E425" s="4" t="n">
         <v>76</v>
@@ -17075,7 +17087,7 @@
         <v>6</v>
       </c>
       <c r="H425" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I425" s="4" t="n">
         <v>13</v>
@@ -17097,7 +17109,7 @@
         <v>27</v>
       </c>
       <c r="D426" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E426" s="4" t="n">
         <v>81</v>
@@ -17109,7 +17121,7 @@
         <v>2</v>
       </c>
       <c r="H426" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I426" s="4"/>
       <c r="J426" s="4"/>
@@ -17145,7 +17157,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="16" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B428" s="16"/>
       <c r="C428" s="16"/>
@@ -17200,7 +17212,7 @@
         <v>7</v>
       </c>
       <c r="D430" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>80</v>
@@ -17212,7 +17224,7 @@
         <v>7</v>
       </c>
       <c r="H430" s="7" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I430" s="4" t="n">
         <v>14</v>
@@ -17246,7 +17258,7 @@
         <v>2</v>
       </c>
       <c r="H431" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I431" s="4"/>
       <c r="J431" s="4" t="n">
@@ -17268,7 +17280,7 @@
         <v>11</v>
       </c>
       <c r="D432" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>150</v>
@@ -17280,7 +17292,7 @@
         <v>6</v>
       </c>
       <c r="H432" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I432" s="4"/>
       <c r="J432" s="4" t="n">
@@ -17314,7 +17326,7 @@
         <v>4</v>
       </c>
       <c r="H433" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I433" s="4" t="n">
         <v>13</v>
@@ -17336,7 +17348,7 @@
         <v>27</v>
       </c>
       <c r="D434" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E434" s="4" t="n">
         <v>64</v>
@@ -17348,7 +17360,7 @@
         <v>2</v>
       </c>
       <c r="H434" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I434" s="4"/>
       <c r="J434" s="4"/>
@@ -17380,7 +17392,7 @@
         <v>2</v>
       </c>
       <c r="H435" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I435" s="4" t="n">
         <v>6</v>
@@ -17414,7 +17426,7 @@
         <v>5</v>
       </c>
       <c r="H436" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I436" s="4"/>
       <c r="J436" s="4" t="n">
@@ -17436,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D437" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E437" s="4" t="n">
         <v>94</v>
@@ -17448,7 +17460,7 @@
         <v>5</v>
       </c>
       <c r="H437" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I437" s="4"/>
       <c r="J437" s="4"/>
@@ -17468,7 +17480,7 @@
         <v>7</v>
       </c>
       <c r="D438" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E438" s="4" t="n">
         <v>136</v>
@@ -17480,7 +17492,7 @@
         <v>6</v>
       </c>
       <c r="H438" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I438" s="4" t="n">
         <v>22</v>
@@ -17502,7 +17514,7 @@
         <v>11</v>
       </c>
       <c r="D439" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E439" s="4" t="n">
         <v>279</v>
@@ -17514,7 +17526,7 @@
         <v>6</v>
       </c>
       <c r="H439" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I439" s="4"/>
       <c r="J439" s="4" t="n">
@@ -17536,7 +17548,7 @@
         <v>7</v>
       </c>
       <c r="D440" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E440" s="4" t="n">
         <v>30</v>
@@ -17548,7 +17560,7 @@
         <v>4</v>
       </c>
       <c r="H440" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="I440" s="4" t="n">
         <v>5</v>
@@ -17580,7 +17592,7 @@
         <v>4</v>
       </c>
       <c r="H441" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I441" s="4"/>
       <c r="J441" s="4"/>
@@ -17616,7 +17628,7 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="22" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B443" s="22"/>
       <c r="C443" s="22"/>
@@ -17671,7 +17683,7 @@
         <v>7</v>
       </c>
       <c r="D445" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E445" s="4" t="n">
         <v>69</v>
@@ -17683,7 +17695,7 @@
         <v>7</v>
       </c>
       <c r="H445" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I445" s="4" t="n">
         <v>13</v>
@@ -17717,7 +17729,7 @@
         <v>2</v>
       </c>
       <c r="H446" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I446" s="4"/>
       <c r="J446" s="4" t="n">
@@ -17739,7 +17751,7 @@
         <v>11</v>
       </c>
       <c r="D447" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E447" s="4" t="n">
         <v>132</v>
@@ -17751,7 +17763,7 @@
         <v>6</v>
       </c>
       <c r="H447" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I447" s="4"/>
       <c r="J447" s="4" t="n">
@@ -17773,7 +17785,7 @@
         <v>27</v>
       </c>
       <c r="D448" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E448" s="4" t="n">
         <v>73</v>
@@ -17785,7 +17797,7 @@
         <v>2</v>
       </c>
       <c r="H448" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I448" s="4"/>
       <c r="J448" s="4"/>
@@ -17817,7 +17829,7 @@
         <v>2</v>
       </c>
       <c r="H449" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I449" s="4" t="n">
         <v>10</v>
@@ -17851,7 +17863,7 @@
         <v>2</v>
       </c>
       <c r="H450" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I450" s="4" t="n">
         <v>3</v>
@@ -17885,7 +17897,7 @@
         <v>3</v>
       </c>
       <c r="H451" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I451" s="4"/>
       <c r="J451" s="4" t="n">
@@ -17907,7 +17919,7 @@
         <v>27</v>
       </c>
       <c r="D452" s="6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E452" s="4" t="n">
         <v>44</v>
@@ -17919,7 +17931,7 @@
         <v>3</v>
       </c>
       <c r="H452" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I452" s="4"/>
       <c r="J452" s="4"/>
@@ -17939,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D453" s="6" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E453" s="4" t="n">
         <v>15</v>
@@ -17951,7 +17963,7 @@
         <v>2</v>
       </c>
       <c r="H453" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I453" s="4" t="n">
         <v>2.5</v>
@@ -17973,7 +17985,7 @@
         <v>11</v>
       </c>
       <c r="D454" s="6" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E454" s="4" t="n">
         <v>15</v>
@@ -17985,7 +17997,7 @@
         <v>2</v>
       </c>
       <c r="H454" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I454" s="4"/>
       <c r="J454" s="4" t="n">
@@ -18007,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D455" s="19" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E455" s="19" t="s">
         <v>4</v>
@@ -18019,7 +18031,7 @@
         <v>3</v>
       </c>
       <c r="H455" s="24" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I455" s="19" t="n">
         <v>21</v>
@@ -18058,7 +18070,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="25" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B457" s="25"/>
       <c r="C457" s="25"/>
@@ -18095,7 +18107,7 @@
         <v>1</v>
       </c>
       <c r="H458" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I458" s="4"/>
       <c r="J458" s="4"/>
@@ -18113,7 +18125,7 @@
         <v>7</v>
       </c>
       <c r="D459" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E459" s="4" t="n">
         <v>46</v>
@@ -18125,7 +18137,7 @@
         <v>2</v>
       </c>
       <c r="H459" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I459" s="4" t="n">
         <v>7.5</v>
@@ -18159,7 +18171,7 @@
         <v>2</v>
       </c>
       <c r="H460" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I460" s="4"/>
       <c r="J460" s="4" t="n">
@@ -18181,7 +18193,7 @@
         <v>27</v>
       </c>
       <c r="D461" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E461" s="4" t="n">
         <v>46</v>
@@ -18193,7 +18205,7 @@
         <v>2</v>
       </c>
       <c r="H461" s="7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I461" s="4"/>
       <c r="J461" s="4"/>
@@ -18225,7 +18237,7 @@
         <v>2</v>
       </c>
       <c r="H462" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I462" s="4" t="n">
         <v>6.5</v>
@@ -18281,7 +18293,7 @@
         <v>11</v>
       </c>
       <c r="D464" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E464" s="4" t="n">
         <v>59</v>
@@ -18293,7 +18305,7 @@
         <v>2</v>
       </c>
       <c r="H464" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I464" s="4"/>
       <c r="J464" s="4" t="n">
@@ -18327,7 +18339,7 @@
         <v>3</v>
       </c>
       <c r="H465" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I465" s="4"/>
       <c r="J465" s="4"/>
@@ -18347,7 +18359,7 @@
         <v>11</v>
       </c>
       <c r="D466" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E466" s="4" t="n">
         <v>118</v>
@@ -18359,7 +18371,7 @@
         <v>2</v>
       </c>
       <c r="H466" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I466" s="4"/>
       <c r="J466" s="4" t="n">
@@ -18381,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D467" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E467" s="4" t="n">
         <v>62</v>
@@ -18393,7 +18405,7 @@
         <v>5</v>
       </c>
       <c r="H467" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I467" s="4" t="n">
         <v>10</v>
@@ -18427,7 +18439,7 @@
         <v>4</v>
       </c>
       <c r="H468" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I468" s="4"/>
       <c r="J468" s="4"/>
@@ -18463,7 +18475,7 @@
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="25" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B470" s="25"/>
       <c r="C470" s="25"/>
@@ -18518,7 +18530,7 @@
         <v>7</v>
       </c>
       <c r="D472" s="6" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E472" s="4" t="n">
         <v>60</v>
@@ -18530,7 +18542,7 @@
         <v>5</v>
       </c>
       <c r="H472" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I472" s="4" t="n">
         <v>10.5</v>
@@ -18564,7 +18576,7 @@
         <v>2</v>
       </c>
       <c r="H473" s="7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I473" s="4"/>
       <c r="J473" s="4" t="n">
@@ -18586,7 +18598,7 @@
         <v>11</v>
       </c>
       <c r="D474" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E474" s="4" t="n">
         <v>124</v>
@@ -18598,7 +18610,7 @@
         <v>5</v>
       </c>
       <c r="H474" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I474" s="4"/>
       <c r="J474" s="4" t="n">
@@ -18632,7 +18644,7 @@
         <v>4</v>
       </c>
       <c r="H475" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I475" s="4" t="n">
         <v>10</v>
@@ -18654,7 +18666,7 @@
         <v>27</v>
       </c>
       <c r="D476" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E476" s="4" t="n">
         <v>61</v>
@@ -18666,7 +18678,7 @@
         <v>2</v>
       </c>
       <c r="H476" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I476" s="4"/>
       <c r="J476" s="4"/>
@@ -18698,7 +18710,7 @@
         <v>2</v>
       </c>
       <c r="H477" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I477" s="4" t="n">
         <v>6</v>
@@ -18732,7 +18744,7 @@
         <v>5</v>
       </c>
       <c r="H478" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I478" s="4"/>
       <c r="J478" s="4" t="n">
@@ -18754,7 +18766,7 @@
         <v>27</v>
       </c>
       <c r="D479" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E479" s="4" t="n">
         <v>88</v>
@@ -18766,7 +18778,7 @@
         <v>5</v>
       </c>
       <c r="H479" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I479" s="4"/>
       <c r="J479" s="4"/>
@@ -18786,7 +18798,7 @@
         <v>7</v>
       </c>
       <c r="D480" s="6" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E480" s="4" t="n">
         <v>136</v>
@@ -18798,7 +18810,7 @@
         <v>6</v>
       </c>
       <c r="H480" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I480" s="4" t="n">
         <v>22</v>
@@ -18820,7 +18832,7 @@
         <v>11</v>
       </c>
       <c r="D481" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E481" s="4" t="n">
         <v>257</v>
@@ -18832,7 +18844,7 @@
         <v>6</v>
       </c>
       <c r="H481" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I481" s="4"/>
       <c r="J481" s="4" t="n">
@@ -18854,7 +18866,7 @@
         <v>7</v>
       </c>
       <c r="D482" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E482" s="4" t="n">
         <v>20</v>
@@ -18866,7 +18878,7 @@
         <v>4</v>
       </c>
       <c r="H482" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I482" s="4" t="n">
         <v>3.5</v>
@@ -18898,7 +18910,7 @@
         <v>4</v>
       </c>
       <c r="H483" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I483" s="4"/>
       <c r="J483" s="4"/>
@@ -18934,7 +18946,7 @@
     </row>
     <row r="485" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="25" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B485" s="25"/>
       <c r="C485" s="25"/>
@@ -18989,7 +19001,7 @@
         <v>7</v>
       </c>
       <c r="D487" s="6" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E487" s="4" t="n">
         <v>82</v>
@@ -19001,7 +19013,7 @@
         <v>7</v>
       </c>
       <c r="H487" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I487" s="4" t="n">
         <v>14</v>
@@ -19035,7 +19047,7 @@
         <v>2</v>
       </c>
       <c r="H488" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I488" s="4"/>
       <c r="J488" s="4" t="n">
@@ -19057,7 +19069,7 @@
         <v>11</v>
       </c>
       <c r="D489" s="6" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E489" s="4" t="n">
         <v>144</v>
@@ -19069,7 +19081,7 @@
         <v>6</v>
       </c>
       <c r="H489" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I489" s="4"/>
       <c r="J489" s="4" t="n">
@@ -19103,7 +19115,7 @@
         <v>4</v>
       </c>
       <c r="H490" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="I490" s="4" t="n">
         <v>12.5</v>
@@ -19125,7 +19137,7 @@
         <v>27</v>
       </c>
       <c r="D491" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E491" s="4" t="n">
         <v>68</v>
@@ -19137,7 +19149,7 @@
         <v>2</v>
       </c>
       <c r="H491" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I491" s="4"/>
       <c r="J491" s="4"/>
@@ -19169,7 +19181,7 @@
         <v>2</v>
       </c>
       <c r="H492" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I492" s="4" t="n">
         <v>6</v>
@@ -19203,7 +19215,7 @@
         <v>5</v>
       </c>
       <c r="H493" s="7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I493" s="4"/>
       <c r="J493" s="4" t="n">
@@ -19225,7 +19237,7 @@
         <v>27</v>
       </c>
       <c r="D494" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E494" s="4" t="n">
         <v>99</v>
@@ -19237,7 +19249,7 @@
         <v>5</v>
       </c>
       <c r="H494" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I494" s="4"/>
       <c r="J494" s="4"/>
@@ -19257,7 +19269,7 @@
         <v>7</v>
       </c>
       <c r="D495" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E495" s="4" t="n">
         <v>154</v>
@@ -19269,7 +19281,7 @@
         <v>7</v>
       </c>
       <c r="H495" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I495" s="4" t="n">
         <v>25</v>
@@ -19291,7 +19303,7 @@
         <v>11</v>
       </c>
       <c r="D496" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E496" s="4" t="n">
         <v>321</v>
@@ -19303,7 +19315,7 @@
         <v>6</v>
       </c>
       <c r="H496" s="7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I496" s="4"/>
       <c r="J496" s="4" t="n">
@@ -19325,7 +19337,7 @@
         <v>7</v>
       </c>
       <c r="D497" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E497" s="4" t="n">
         <v>25</v>
@@ -19337,7 +19349,7 @@
         <v>4</v>
       </c>
       <c r="H497" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I497" s="4" t="n">
         <v>4.5</v>
@@ -19369,7 +19381,7 @@
         <v>4</v>
       </c>
       <c r="H498" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I498" s="4"/>
       <c r="J498" s="4"/>
@@ -19405,7 +19417,7 @@
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="26" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B500" s="26"/>
       <c r="C500" s="26"/>
@@ -19459,7 +19471,7 @@
         <v>7</v>
       </c>
       <c r="D502" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E502" s="4" t="n">
         <v>64</v>
@@ -19471,7 +19483,7 @@
         <v>7</v>
       </c>
       <c r="H502" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I502" s="4" t="n">
         <v>11</v>
@@ -19505,7 +19517,7 @@
         <v>2</v>
       </c>
       <c r="H503" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I503" s="4"/>
       <c r="J503" s="4" t="n">
@@ -19527,7 +19539,7 @@
         <v>11</v>
       </c>
       <c r="D504" s="6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E504" s="4" t="n">
         <v>103</v>
@@ -19539,7 +19551,7 @@
         <v>5</v>
       </c>
       <c r="H504" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I504" s="4"/>
       <c r="J504" s="4" t="n">
@@ -19573,7 +19585,7 @@
         <v>2</v>
       </c>
       <c r="H505" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I505" s="4" t="n">
         <v>10</v>
@@ -19595,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D506" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E506" s="4" t="n">
         <v>49</v>
@@ -19607,7 +19619,7 @@
         <v>2</v>
       </c>
       <c r="H506" s="7" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I506" s="4"/>
       <c r="J506" s="4"/>
@@ -19639,7 +19651,7 @@
         <v>2</v>
       </c>
       <c r="H507" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I507" s="4" t="n">
         <v>5</v>
@@ -19673,7 +19685,7 @@
         <v>3</v>
       </c>
       <c r="H508" s="7" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I508" s="4"/>
       <c r="J508" s="4" t="n">
@@ -19695,7 +19707,7 @@
         <v>27</v>
       </c>
       <c r="D509" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E509" s="4" t="n">
         <v>75</v>
@@ -19707,7 +19719,7 @@
         <v>5</v>
       </c>
       <c r="H509" s="7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I509" s="4"/>
       <c r="J509" s="4"/>
@@ -19727,7 +19739,7 @@
         <v>7</v>
       </c>
       <c r="D510" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E510" s="4" t="n">
         <v>111</v>
@@ -19739,7 +19751,7 @@
         <v>6</v>
       </c>
       <c r="H510" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I510" s="4" t="n">
         <v>18</v>
@@ -19761,7 +19773,7 @@
         <v>11</v>
       </c>
       <c r="D511" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E511" s="4" t="n">
         <v>214</v>
@@ -19773,7 +19785,7 @@
         <v>4</v>
       </c>
       <c r="H511" s="7" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I511" s="4"/>
       <c r="J511" s="4" t="n">
@@ -19807,7 +19819,7 @@
         <v>4</v>
       </c>
       <c r="H512" s="7" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I512" s="4"/>
       <c r="J512" s="4"/>
@@ -19843,7 +19855,7 @@
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="16" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B514" s="16"/>
       <c r="C514" s="16"/>
@@ -19880,7 +19892,7 @@
         <v>4</v>
       </c>
       <c r="H515" s="7" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I515" s="4"/>
       <c r="J515" s="4"/>
@@ -19900,7 +19912,7 @@
         <v>7</v>
       </c>
       <c r="D516" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E516" s="4" t="n">
         <v>80</v>
@@ -19912,7 +19924,7 @@
         <v>6</v>
       </c>
       <c r="H516" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I516" s="4" t="n">
         <v>14.5</v>
@@ -19946,7 +19958,7 @@
         <v>2</v>
       </c>
       <c r="H517" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I517" s="4"/>
       <c r="J517" s="4" t="n">
@@ -19968,7 +19980,7 @@
         <v>11</v>
       </c>
       <c r="D518" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E518" s="4" t="n">
         <v>154</v>
@@ -19980,7 +19992,7 @@
         <v>6</v>
       </c>
       <c r="H518" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I518" s="4"/>
       <c r="J518" s="4" t="n">
@@ -20014,7 +20026,7 @@
         <v>4</v>
       </c>
       <c r="H519" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I519" s="4" t="n">
         <v>13.5</v>
@@ -20036,7 +20048,7 @@
         <v>27</v>
       </c>
       <c r="D520" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E520" s="4" t="n">
         <v>71</v>
@@ -20048,7 +20060,7 @@
         <v>2</v>
       </c>
       <c r="H520" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I520" s="4"/>
       <c r="J520" s="4"/>
@@ -20080,7 +20092,7 @@
         <v>2</v>
       </c>
       <c r="H521" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I521" s="4" t="n">
         <v>6</v>
@@ -20114,7 +20126,7 @@
         <v>5</v>
       </c>
       <c r="H522" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I522" s="4"/>
       <c r="J522" s="4" t="n">
@@ -20136,7 +20148,7 @@
         <v>27</v>
       </c>
       <c r="D523" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E523" s="4" t="n">
         <v>100</v>
@@ -20148,7 +20160,7 @@
         <v>5</v>
       </c>
       <c r="H523" s="7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I523" s="4"/>
       <c r="J523" s="4"/>
@@ -20168,7 +20180,7 @@
         <v>7</v>
       </c>
       <c r="D524" s="6" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E524" s="4" t="n">
         <v>173</v>
@@ -20180,7 +20192,7 @@
         <v>6</v>
       </c>
       <c r="H524" s="7" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I524" s="4" t="n">
         <v>28</v>
@@ -20202,7 +20214,7 @@
         <v>11</v>
       </c>
       <c r="D525" s="6" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E525" s="4" t="n">
         <v>343</v>
@@ -20214,7 +20226,7 @@
         <v>6</v>
       </c>
       <c r="H525" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I525" s="4"/>
       <c r="J525" s="4" t="n">
@@ -20236,7 +20248,7 @@
         <v>7</v>
       </c>
       <c r="D526" s="6" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E526" s="4" t="n">
         <v>35</v>
@@ -20248,7 +20260,7 @@
         <v>4</v>
       </c>
       <c r="H526" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I526" s="4" t="n">
         <v>6</v>
@@ -20284,7 +20296,7 @@
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="16" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B528" s="16"/>
       <c r="C528" s="16"/>
@@ -20321,7 +20333,7 @@
         <v>4</v>
       </c>
       <c r="H529" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I529" s="4"/>
       <c r="J529" s="4"/>
@@ -20341,7 +20353,7 @@
         <v>7</v>
       </c>
       <c r="D530" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E530" s="4" t="n">
         <v>84</v>
@@ -20353,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="H530" s="7" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I530" s="4" t="n">
         <v>16</v>
@@ -20387,7 +20399,7 @@
         <v>2</v>
       </c>
       <c r="H531" s="7" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I531" s="4"/>
       <c r="J531" s="4" t="n">
@@ -20409,7 +20421,7 @@
         <v>11</v>
       </c>
       <c r="D532" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E532" s="4" t="n">
         <v>165</v>
@@ -20421,7 +20433,7 @@
         <v>6</v>
       </c>
       <c r="H532" s="7" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I532" s="4"/>
       <c r="J532" s="4" t="n">
@@ -20455,7 +20467,7 @@
         <v>4</v>
       </c>
       <c r="H533" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I533" s="4" t="n">
         <v>15</v>
@@ -20477,7 +20489,7 @@
         <v>27</v>
       </c>
       <c r="D534" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E534" s="4" t="n">
         <v>74</v>
@@ -20489,7 +20501,7 @@
         <v>2</v>
       </c>
       <c r="H534" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I534" s="4"/>
       <c r="J534" s="4"/>
@@ -20521,7 +20533,7 @@
         <v>2</v>
       </c>
       <c r="H535" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I535" s="4" t="n">
         <v>6</v>
@@ -20555,7 +20567,7 @@
         <v>5</v>
       </c>
       <c r="H536" s="7" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I536" s="4"/>
       <c r="J536" s="4" t="n">
@@ -20577,7 +20589,7 @@
         <v>27</v>
       </c>
       <c r="D537" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E537" s="4" t="n">
         <v>106</v>
@@ -20589,7 +20601,7 @@
         <v>5</v>
       </c>
       <c r="H537" s="7" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I537" s="4"/>
       <c r="J537" s="4"/>
@@ -20609,7 +20621,7 @@
         <v>7</v>
       </c>
       <c r="D538" s="6" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E538" s="4" t="n">
         <v>185</v>
@@ -20621,7 +20633,7 @@
         <v>6</v>
       </c>
       <c r="H538" s="7" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I538" s="4" t="n">
         <v>30</v>
@@ -20643,7 +20655,7 @@
         <v>11</v>
       </c>
       <c r="D539" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E539" s="4" t="n">
         <v>364</v>
@@ -20655,7 +20667,7 @@
         <v>6</v>
       </c>
       <c r="H539" s="7" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I539" s="4"/>
       <c r="J539" s="4" t="n">
@@ -20677,7 +20689,7 @@
         <v>7</v>
       </c>
       <c r="D540" s="6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E540" s="4" t="n">
         <v>40</v>
@@ -20689,7 +20701,7 @@
         <v>4</v>
       </c>
       <c r="H540" s="7" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I540" s="4" t="n">
         <v>7</v>
@@ -20725,7 +20737,7 @@
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="16" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B542" s="16"/>
       <c r="C542" s="16"/>
@@ -20762,7 +20774,7 @@
         <v>4</v>
       </c>
       <c r="H543" s="7" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I543" s="4"/>
       <c r="J543" s="4"/>
@@ -20782,7 +20794,7 @@
         <v>7</v>
       </c>
       <c r="D544" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E544" s="4" t="n">
         <v>90</v>
@@ -20794,7 +20806,7 @@
         <v>7</v>
       </c>
       <c r="H544" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="I544" s="4" t="n">
         <v>17</v>
@@ -20828,7 +20840,7 @@
         <v>2</v>
       </c>
       <c r="H545" s="7" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I545" s="4"/>
       <c r="J545" s="4" t="n">
@@ -20850,7 +20862,7 @@
         <v>11</v>
       </c>
       <c r="D546" s="6" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E546" s="4" t="n">
         <v>174</v>
@@ -20862,7 +20874,7 @@
         <v>6</v>
       </c>
       <c r="H546" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I546" s="4"/>
       <c r="J546" s="4" t="n">
@@ -20896,7 +20908,7 @@
         <v>4</v>
       </c>
       <c r="H547" s="7" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I547" s="4" t="n">
         <v>15.5</v>
@@ -20918,7 +20930,7 @@
         <v>27</v>
       </c>
       <c r="D548" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E548" s="4" t="n">
         <v>78</v>
@@ -20930,7 +20942,7 @@
         <v>2</v>
       </c>
       <c r="H548" s="7" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I548" s="4"/>
       <c r="J548" s="4"/>
@@ -20962,7 +20974,7 @@
         <v>2</v>
       </c>
       <c r="H549" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I549" s="4" t="n">
         <v>6</v>
@@ -20996,7 +21008,7 @@
         <v>5</v>
       </c>
       <c r="H550" s="7" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I550" s="4"/>
       <c r="J550" s="4" t="n">
@@ -21018,7 +21030,7 @@
         <v>27</v>
       </c>
       <c r="D551" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E551" s="4" t="n">
         <v>110</v>
@@ -21030,7 +21042,7 @@
         <v>5</v>
       </c>
       <c r="H551" s="7" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I551" s="4"/>
       <c r="J551" s="4"/>
@@ -21050,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D552" s="6" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E552" s="4" t="n">
         <v>197</v>
@@ -21062,7 +21074,7 @@
         <v>6</v>
       </c>
       <c r="H552" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I552" s="4" t="n">
         <v>32</v>
@@ -21084,7 +21096,7 @@
         <v>11</v>
       </c>
       <c r="D553" s="6" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E553" s="4" t="n">
         <v>386</v>
@@ -21096,7 +21108,7 @@
         <v>6</v>
       </c>
       <c r="H553" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I553" s="4"/>
       <c r="J553" s="4" t="n">
@@ -21118,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D554" s="6" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E554" s="4" t="n">
         <v>45</v>
@@ -21130,7 +21142,7 @@
         <v>4</v>
       </c>
       <c r="H554" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="I554" s="4" t="n">
         <v>7.5</v>
@@ -21166,7 +21178,7 @@
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="22" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B556" s="22"/>
       <c r="C556" s="22"/>
@@ -21221,7 +21233,7 @@
         <v>7</v>
       </c>
       <c r="D558" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E558" s="4" t="n">
         <v>48</v>
@@ -21233,7 +21245,7 @@
         <v>5</v>
       </c>
       <c r="H558" s="7" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I558" s="4" t="n">
         <v>8.5</v>
@@ -21267,7 +21279,7 @@
         <v>2</v>
       </c>
       <c r="H559" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I559" s="4"/>
       <c r="J559" s="4" t="n">
@@ -21289,7 +21301,7 @@
         <v>11</v>
       </c>
       <c r="D560" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E560" s="4" t="n">
         <v>90</v>
@@ -21301,7 +21313,7 @@
         <v>5</v>
       </c>
       <c r="H560" s="7" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I560" s="4"/>
       <c r="J560" s="4" t="n">
@@ -21335,7 +21347,7 @@
         <v>4</v>
       </c>
       <c r="H561" s="7" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I561" s="4" t="n">
         <v>7.5</v>
@@ -21357,7 +21369,7 @@
         <v>27</v>
       </c>
       <c r="D562" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E562" s="4" t="n">
         <v>59</v>
@@ -21369,7 +21381,7 @@
         <v>2</v>
       </c>
       <c r="H562" s="7" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="I562" s="4"/>
       <c r="J562" s="4"/>
@@ -21435,7 +21447,7 @@
         <v>3</v>
       </c>
       <c r="H564" s="7" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I564" s="4"/>
       <c r="J564" s="4" t="n">
@@ -21457,7 +21469,7 @@
         <v>27</v>
       </c>
       <c r="D565" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E565" s="4" t="n">
         <v>83</v>
@@ -21469,7 +21481,7 @@
         <v>5</v>
       </c>
       <c r="H565" s="7" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I565" s="4"/>
       <c r="J565" s="4"/>
@@ -21489,7 +21501,7 @@
         <v>7</v>
       </c>
       <c r="D566" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E566" s="4" t="n">
         <v>86</v>
@@ -21501,7 +21513,7 @@
         <v>6</v>
       </c>
       <c r="H566" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I566" s="4" t="n">
         <v>14</v>
@@ -21523,7 +21535,7 @@
         <v>11</v>
       </c>
       <c r="D567" s="6" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E567" s="4" t="n">
         <v>107</v>
@@ -21535,7 +21547,7 @@
         <v>6</v>
       </c>
       <c r="H567" s="7" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I567" s="4"/>
       <c r="J567" s="4" t="n">
@@ -21573,7 +21585,7 @@
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="27" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B569" s="27"/>
       <c r="C569" s="27"/>
@@ -21598,7 +21610,7 @@
         <v>2</v>
       </c>
       <c r="D570" s="6" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E570" s="4" t="s">
         <v>4</v>
@@ -21622,7 +21634,7 @@
         <v>11</v>
       </c>
       <c r="D571" s="6" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E571" s="4" t="n">
         <v>43</v>
@@ -21634,7 +21646,7 @@
         <v>2</v>
       </c>
       <c r="H571" s="7" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I571" s="4"/>
       <c r="J571" s="4" t="n">
@@ -21666,7 +21678,7 @@
         <v>2</v>
       </c>
       <c r="H572" s="7" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="I572" s="4" t="n">
         <v>2.5</v>
@@ -21686,7 +21698,7 @@
         <v>11</v>
       </c>
       <c r="D573" s="6" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E573" s="4" t="n">
         <v>37</v>
@@ -21698,7 +21710,7 @@
         <v>2</v>
       </c>
       <c r="H573" s="7" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I573" s="4"/>
       <c r="J573" s="4" t="n">
@@ -21718,7 +21730,7 @@
         <v>27</v>
       </c>
       <c r="D574" s="6" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E574" s="4" t="n">
         <v>44</v>
@@ -21730,7 +21742,7 @@
         <v>3</v>
       </c>
       <c r="H574" s="7" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I574" s="4"/>
       <c r="J574" s="4"/>
@@ -21750,7 +21762,7 @@
         <v>11</v>
       </c>
       <c r="D575" s="6" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E575" s="4" t="n">
         <v>27</v>
@@ -21762,7 +21774,7 @@
         <v>2</v>
       </c>
       <c r="H575" s="7" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I575" s="4"/>
       <c r="J575" s="4" t="n">
@@ -21782,7 +21794,7 @@
         <v>7</v>
       </c>
       <c r="D576" s="6" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E576" s="4" t="n">
         <v>15</v>
@@ -21794,7 +21806,7 @@
         <v>2</v>
       </c>
       <c r="H576" s="7" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I576" s="4" t="n">
         <v>2.5</v>
@@ -21814,7 +21826,7 @@
         <v>27</v>
       </c>
       <c r="D577" s="6" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E577" s="4" t="n">
         <v>29</v>
@@ -21826,7 +21838,7 @@
         <v>2</v>
       </c>
       <c r="H577" s="7" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I577" s="4"/>
       <c r="J577" s="4"/>
@@ -21846,7 +21858,7 @@
         <v>7</v>
       </c>
       <c r="D578" s="6" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E578" s="4" t="n">
         <v>15</v>
@@ -21858,7 +21870,7 @@
         <v>2</v>
       </c>
       <c r="H578" s="7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I578" s="4" t="n">
         <v>2.5</v>
@@ -21878,7 +21890,7 @@
         <v>11</v>
       </c>
       <c r="D579" s="6" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E579" s="4" t="n">
         <v>17</v>
@@ -21890,7 +21902,7 @@
         <v>2</v>
       </c>
       <c r="H579" s="7" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I579" s="4"/>
       <c r="J579" s="4" t="n">
@@ -21910,7 +21922,7 @@
         <v>7</v>
       </c>
       <c r="D580" s="19" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E580" s="19" t="s">
         <v>4</v>
@@ -21922,7 +21934,7 @@
         <v>3</v>
       </c>
       <c r="H580" s="24" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="I580" s="19" t="n">
         <v>42</v>
@@ -22034,231 +22046,231 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="29" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E13" s="31" t="s">
+        <v>630</v>
+      </c>
+      <c r="F13" s="31" t="s">
         <v>628</v>
       </c>
-      <c r="F13" s="31" t="s">
-        <v>626</v>
-      </c>
       <c r="G13" s="31" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E14" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="F14" s="31" t="s">
         <v>634</v>
       </c>
-      <c r="F14" s="31" t="s">
-        <v>632</v>
-      </c>
       <c r="G14" s="31" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E15" s="31" t="s">
+        <v>642</v>
+      </c>
+      <c r="F15" s="31" t="s">
         <v>640</v>
       </c>
-      <c r="F15" s="31" t="s">
-        <v>638</v>
-      </c>
       <c r="G15" s="31" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32"/>
@@ -22269,15 +22281,15 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
@@ -22287,10 +22299,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
@@ -22300,10 +22312,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -22313,10 +22325,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
@@ -22326,10 +22338,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C27" s="32"/>
       <c r="D27" s="32"/>
@@ -22339,10 +22351,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
@@ -22352,10 +22364,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
@@ -22399,110 +22411,110 @@
   <sheetData>
     <row r="1" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="29" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="32"/>

--- a/Marathon_programme.xlsx
+++ b/Marathon_programme.xlsx
@@ -1882,9 +1882,11 @@
       <c r="G4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="6">
-        <f>"29' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29' Z2 très facile (127-140 bpm / 100-120 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n">
@@ -1922,9 +1924,12 @@
       <c r="G5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="6">
-        <f>"20' EF Z2 | 2x22' @ 91% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*91/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5' | 10' RC"&amp;CHAR(10)&amp;"FC bloc cible : ~165 bpm (85% FC max) | Cadence : 87-93 rpm"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"</f>
-        <v/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20' EF Z2 | 2x22' @ 91% FTP (180 W) — r=5' | 10' RC
+FC bloc cible : ~165 bpm (85% FC max) | Cadence : 87-93 rpm
+NUTRITION : 40g glucides/h si &gt;90'</t>
+        </is>
       </c>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n">
@@ -2045,9 +2050,11 @@
       <c r="G8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="6">
-        <f>"10' EF | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3' | 10' RC"&amp;CHAR(10)&amp;"FC : 131-155 bpm"</f>
-        <v/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10' EF | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3' | 10' RC
+FC : 131-155 bpm</t>
+        </is>
       </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n">
@@ -2335,9 +2342,11 @@
       <c r="G16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="6">
-        <f>"38' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38' Z2 très facile (127-140 bpm / 100-120 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n">
@@ -2375,9 +2384,14 @@
       <c r="G17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="6">
-        <f>"20' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x10' @ 89% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*89/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~161 bpm (83% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20' EF Z2 (127-140 bpm / 120-140 W) | 2x10' @ 89% FTP (180 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~161 bpm (83% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n">
@@ -2457,9 +2471,13 @@
       <c r="G19" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="6">
-        <f>"10' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n">
@@ -2582,9 +2600,12 @@
       <c r="G22" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="6">
-        <f>"92' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 40g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n">
@@ -2785,9 +2806,11 @@
       <c r="G28" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="6">
-        <f>"24' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24' Z2 très facile (127-140 bpm / 100-120 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n">
@@ -2825,9 +2848,14 @@
       <c r="G29" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="6">
-        <f>"20' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x9' @ 88% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20' EF Z2 (127-140 bpm / 120-140 W) | 2x9' @ 88% FTP (175 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n">
@@ -2950,9 +2978,13 @@
       <c r="G32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="6">
-        <f>"10' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n">
@@ -3199,9 +3231,11 @@
       <c r="G39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="6">
-        <f>"33' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33' Z2 très facile (127-140 bpm / 100-120 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n">
@@ -3239,9 +3273,14 @@
       <c r="G40" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H40" s="6">
-        <f>"20' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x9' @ 92% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*92/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~167 bpm (86% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20' EF Z2 (127-140 bpm / 120-140 W) | 3x9' @ 92% FTP (185 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~167 bpm (86% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n">
@@ -3365,9 +3404,13 @@
       <c r="G43" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="6">
-        <f>"10' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n">
@@ -3490,9 +3533,12 @@
       <c r="G46" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H46" s="6">
-        <f>"94' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 40g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n">
@@ -3694,9 +3740,11 @@
       <c r="G52" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H52" s="6">
-        <f>"52' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52' Z2 très facile (127-140 bpm / 100-120 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n">
@@ -3734,9 +3782,14 @@
       <c r="G53" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H53" s="6">
-        <f>"89' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x7' @ 88% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89' EF Z2 (127-140 bpm / 120-140 W) | 2x7' @ 88% FTP (175 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n">
@@ -3861,9 +3914,13 @@
       <c r="G56" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="6">
-        <f>"39' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n">
@@ -4107,9 +4164,11 @@
       <c r="G63" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H63" s="6">
-        <f>"43' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43' Z2 très facile (127-140 bpm / 100-120 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I63" s="3" t="n"/>
       <c r="J63" s="3" t="n">
@@ -4147,9 +4206,14 @@
       <c r="G64" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H64" s="6">
-        <f>"45' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x12' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : travailler juste sous le seuil lactique (sweet spot)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45' EF Z2 (127-140 bpm / 120-140 W) | 3x12' @ 90% FTP (180 W) — r=5'
+Objectif : travailler juste sous le seuil lactique (sweet spot)
+FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I64" s="3" t="n"/>
       <c r="J64" s="3" t="n">
@@ -4278,9 +4342,13 @@
       <c r="G67" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H67" s="6">
-        <f>"50' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I67" s="3" t="n"/>
       <c r="J67" s="3" t="n">
@@ -4406,9 +4474,12 @@
       <c r="G70" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H70" s="6">
-        <f>"236' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 40g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I70" s="3" t="n"/>
       <c r="J70" s="3" t="n">
@@ -4610,9 +4681,11 @@
       <c r="G76" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H76" s="6">
-        <f>"43' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43' Z2 très facile (127-140 bpm / 100-120 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I76" s="3" t="n"/>
       <c r="J76" s="3" t="n">
@@ -4650,9 +4723,14 @@
       <c r="G77" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H77" s="6">
-        <f>"51' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x12' over-unders : 3 x (3' @ 80% (155 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*93/500,0)*5,"0"),"?")&amp;" W"&amp;") + 1' @ 88% (171 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*107/500,0)*5,"0"),"?")&amp;" W"&amp;")) — r=5'"&amp;CHAR(10)&amp;"Objectif : tolérance au lactate et relances, alternance sous / au-dessus du seuil"&amp;CHAR(10)&amp;"FC : 155 bpm (80% FC max) sous le seuil | 171 bpm (88%) au-dessus (seuil lactique 163 bpm) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51' EF Z2 (127-140 bpm / 120-140 W) | 3x12' over-unders : 3 x (3' @ 80% (155 bpm / 185 W) + 1' @ 88% (171 bpm / 215 W)) — r=5'
+Objectif : tolérance au lactate et relances, alternance sous / au-dessus du seuil
+FC : 155 bpm (80% FC max) sous le seuil | 171 bpm (88%) au-dessus (seuil lactique 163 bpm) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I77" s="3" t="n"/>
       <c r="J77" s="3" t="n">
@@ -4778,9 +4856,14 @@
       <c r="G80" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H80" s="6">
-        <f>"61' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="n">
@@ -4906,9 +4989,12 @@
       <c r="G83" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H83" s="6">
-        <f>"246' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 40g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I83" s="3" t="n"/>
       <c r="J83" s="3" t="n">
@@ -5110,9 +5196,11 @@
       <c r="G89" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H89" s="6">
-        <f>"43' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I89" s="3" t="n"/>
       <c r="J89" s="3" t="n">
@@ -5150,9 +5238,14 @@
       <c r="G90" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H90" s="6">
-        <f>"40' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3 ouvertures de 30'' à 90% FC max ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*120/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x3' @ 115% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*115/500,0)*5,"0"),"?")&amp;" W"&amp;" — 186 bpm en fin de répétition) — r=3' Z1 | 34' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Objectif : puissance aérobie maximale (VO2max), intervalles courts"&amp;CHAR(10)&amp;"FC fin de répétition : 184-194 bpm (95-100% FC max) | Cadence : 90-100 rpm | RPE 8-9/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40' EF Z2 (127-140 bpm / 120-140 W) dont 3 ouvertures de 30'' à 90% FC max (240 W) | 5x3' @ 115% FTP (230 W — 186 bpm en fin de répétition) — r=3' Z1 | 34' EF Z2 (127-140 bpm / 120-140 W)
+Objectif : puissance aérobie maximale (VO2max), intervalles courts
+FC fin de répétition : 184-194 bpm (95-100% FC max) | Cadence : 90-100 rpm | RPE 8-9/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I90" s="3" t="n"/>
       <c r="J90" s="3" t="n">
@@ -5278,9 +5371,14 @@
       <c r="G93" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H93" s="6">
-        <f>"72' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 40g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I93" s="3" t="n"/>
       <c r="J93" s="3" t="n">
@@ -5406,9 +5504,12 @@
       <c r="G96" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H96" s="6">
-        <f>"257' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 40g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 40g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I96" s="3" t="n"/>
       <c r="J96" s="3" t="n">
@@ -5610,9 +5711,11 @@
       <c r="G102" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H102" s="6">
-        <f>"32' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I102" s="3" t="n"/>
       <c r="J102" s="3" t="n">
@@ -5650,9 +5753,14 @@
       <c r="G103" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H103" s="6">
-        <f>"32' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x15' @ 88% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32' EF Z2 (127-140 bpm / 120-140 W) | 2x15' @ 88% FTP (175 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 50g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I103" s="3" t="n"/>
       <c r="J103" s="3" t="n">
@@ -5777,9 +5885,13 @@
       <c r="G106" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H106" s="6">
-        <f>"35' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I106" s="3" t="n"/>
       <c r="J106" s="3" t="n">
@@ -5905,9 +6017,13 @@
       <c r="G109" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H109" s="6">
-        <f>"167' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"Semaine deload — volume réduit"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+Semaine deload — volume réduit
+NUTRITION : 50g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I109" s="3" t="n"/>
       <c r="J109" s="3" t="n">
@@ -6071,9 +6187,11 @@
       <c r="G114" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H114" s="6">
-        <f>"43' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I114" s="3" t="n"/>
       <c r="J114" s="3" t="n">
@@ -6111,9 +6229,16 @@
       <c r="G115" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H115" s="6">
-        <f>"25' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3x1' rapide (110 rpm) | 5' très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") | 20' test — effort maximal régulier"&amp;CHAR(10)&amp;"Objectif : mesurer ta FTP (frais, après la semaine de décharge)"&amp;CHAR(10)&amp;"Départ : 5 premières minutes @ 100% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*100/500,0)*5,"0"),"?")&amp;" W"&amp;"), puis augmente de 5 W toutes les 5' si tu te sens bien — note la puissance moyenne des 20' et la FC moyenne des 10 dernières minutes | Cadence : 85-95 rpm | RPE 9/10"&amp;CHAR(10)&amp;"Calcul : FTP = 0,95 × puissance moyenne des 20' — à reporter dans la case FTP de l'onglet Repères vélo"&amp;CHAR(10)&amp;"56' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25' EF Z2 (127-140 bpm / 120-140 W) dont 3x1' rapide (110 rpm) | 5' très facile (127-140 bpm / 100-120 W) | 20' test — effort maximal régulier
+Objectif : mesurer ta FTP (frais, après la semaine de décharge)
+Départ : 5 premières minutes @ 100% FTP (200 W), puis augmente de 5 W toutes les 5' si tu te sens bien — note la puissance moyenne des 20' et la FC moyenne des 10 dernières minutes | Cadence : 85-95 rpm | RPE 9/10
+Calcul : FTP = 0,95 × puissance moyenne des 20' — à reporter dans la case FTP de l'onglet Repères vélo
+56' EF Z2 (127-140 bpm / 120-140 W)
+NUTRITION : 50g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I115" s="3" t="n"/>
       <c r="J115" s="3" t="n">
@@ -6240,9 +6365,14 @@
       <c r="G118" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H118" s="6">
-        <f>"70' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 50g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="3" t="n">
@@ -6368,9 +6498,12 @@
       <c r="G121" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H121" s="6">
-        <f>"261' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 50g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I121" s="3" t="n"/>
       <c r="J121" s="3" t="n">
@@ -6579,9 +6712,11 @@
       <c r="G127" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H127" s="6">
-        <f>"43' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="3" t="n">
@@ -6619,9 +6754,14 @@
       <c r="G128" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H128" s="6">
-        <f>"64' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x9' @ 102% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*102/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=4'"&amp;CHAR(10)&amp;"Objectif : élever le seuil (blocs courts à intensité haute)"&amp;CHAR(10)&amp;"FC bloc cible : ~169 bpm (87% FC max, 6 bpm au-dessus de ton seuil lactique de 163) | Cadence : 88-95 rpm | RPE 8/10"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64' EF Z2 (127-140 bpm / 120-140 W) | 4x9' @ 102% FTP (205 W) — r=4'
+Objectif : élever le seuil (blocs courts à intensité haute)
+FC bloc cible : ~169 bpm (87% FC max, 6 bpm au-dessus de ton seuil lactique de 163) | Cadence : 88-95 rpm | RPE 8/10
+NUTRITION : 50g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I128" s="3" t="n"/>
       <c r="J128" s="3" t="n">
@@ -6747,9 +6887,14 @@
       <c r="G131" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H131" s="6">
-        <f>"72' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 50g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="3" t="n">
@@ -6875,9 +7020,12 @@
       <c r="G134" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H134" s="6">
-        <f>"268' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 50g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="3" t="n">
@@ -7081,9 +7229,11 @@
       <c r="G140" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H140" s="6">
-        <f>"47' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n">
@@ -7121,9 +7271,14 @@
       <c r="G141" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H141" s="6">
-        <f>"71' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x20' over-unders : 5 x (3' @ 93% FTP (~155 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*93/500,0)*5,"0"),"?")&amp;" W"&amp;") + 1' @ 107% FTP (~171 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*107/500,0)*5,"0"),"?")&amp;" W"&amp;")) — r=5'"&amp;CHAR(10)&amp;"Objectif : tolérance au lactate et relances, alternance sous / au-dessus du seuil"&amp;CHAR(10)&amp;"FC : 155 bpm (80% FC max) sous le seuil | 171 bpm (88%) au-dessus (seuil lactique 163 bpm) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71' EF Z2 (127-140 bpm / 120-140 W) | 2x20' over-unders : 5 x (3' @ 93% FTP (~155 bpm / 185 W) + 1' @ 107% FTP (~171 bpm / 215 W)) — r=5'
+Objectif : tolérance au lactate et relances, alternance sous / au-dessus du seuil
+FC : 155 bpm (80% FC max) sous le seuil | 171 bpm (88%) au-dessus (seuil lactique 163 bpm) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 50g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n">
@@ -7249,9 +7404,14 @@
       <c r="G144" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H144" s="6">
-        <f>"74' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 50g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="n">
@@ -7378,9 +7538,12 @@
       <c r="G147" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H147" s="6">
-        <f>"274' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 50g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 50g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I147" s="3" t="n"/>
       <c r="J147" s="3" t="n">
@@ -7584,9 +7747,11 @@
       <c r="G153" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H153" s="6">
-        <f>"32' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="n">
@@ -7624,9 +7789,14 @@
       <c r="G154" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H154" s="6">
-        <f>"30' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x18' @ 88% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30' EF Z2 (127-140 bpm / 120-140 W) | 2x18' @ 88% FTP (175 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 60g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I154" s="3" t="n"/>
       <c r="J154" s="3" t="n">
@@ -7752,9 +7922,13 @@
       <c r="G157" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H157" s="6">
-        <f>"42' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42' EF (127-140 bpm / 120-140 W) | 4x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I157" s="3" t="n"/>
       <c r="J157" s="3" t="n">
@@ -7879,9 +8053,13 @@
       <c r="G160" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H160" s="6">
-        <f>"182' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"Semaine deload — volume réduit"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+Semaine deload — volume réduit
+NUTRITION : 60g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I160" s="3" t="n"/>
       <c r="J160" s="3" t="n">
@@ -8040,9 +8218,11 @@
       <c r="G165" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H165" s="6">
-        <f>"47' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I165" s="3" t="n"/>
       <c r="J165" s="3" t="n">
@@ -8080,9 +8260,14 @@
       <c r="G166" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H166" s="6">
-        <f>"61' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x25' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : travailler juste sous le seuil lactique (sweet spot)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61' EF Z2 (127-140 bpm / 120-140 W) | 2x25' @ 90% FTP (180 W) — r=5'
+Objectif : travailler juste sous le seuil lactique (sweet spot)
+FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10
+NUTRITION : 60g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I166" s="3" t="n"/>
       <c r="J166" s="3" t="n">
@@ -8251,9 +8436,14 @@
       <c r="G170" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H170" s="6">
-        <f>"74' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 60g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I170" s="3" t="n"/>
       <c r="J170" s="3" t="n">
@@ -8380,9 +8570,12 @@
       <c r="G173" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H173" s="6">
-        <f>"279' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 60g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I173" s="3" t="n"/>
       <c r="J173" s="3" t="n">
@@ -8591,9 +8784,11 @@
       <c r="G179" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H179" s="6">
-        <f>"47' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I179" s="3" t="n"/>
       <c r="J179" s="3" t="n">
@@ -8631,9 +8826,14 @@
       <c r="G180" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H180" s="6">
-        <f>"40' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3 ouvertures de 30'' à 90% FC max ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*120/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x4' @ 112% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*112/500,0)*5,"0"),"?")&amp;" W"&amp;" — 186 bpm en fin de répétition) — r=4' Z1 | 51' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Objectif : puissance aérobie maximale (VO2max), intervalles courts"&amp;CHAR(10)&amp;"FC fin de répétition : 184-194 bpm (95-100% FC max) | Cadence : 90-100 rpm | RPE 8-9/10"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40' EF Z2 (127-140 bpm / 120-140 W) dont 3 ouvertures de 30'' à 90% FC max (240 W) | 5x4' @ 112% FTP (225 W — 186 bpm en fin de répétition) — r=4' Z1 | 51' EF Z2 (127-140 bpm / 120-140 W)
+Objectif : puissance aérobie maximale (VO2max), intervalles courts
+FC fin de répétition : 184-194 bpm (95-100% FC max) | Cadence : 90-100 rpm | RPE 8-9/10
+NUTRITION : 60g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I180" s="3" t="n"/>
       <c r="J180" s="3" t="n">
@@ -8801,9 +9001,14 @@
       <c r="G184" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H184" s="6">
-        <f>"79' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 60g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I184" s="3" t="n"/>
       <c r="J184" s="3" t="n">
@@ -8930,9 +9135,12 @@
       <c r="G187" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H187" s="6">
-        <f>"285' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 60g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I187" s="3" t="n"/>
       <c r="J187" s="3" t="n">
@@ -9137,9 +9345,11 @@
       <c r="G193" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H193" s="6">
-        <f>"51' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I193" s="3" t="n"/>
       <c r="J193" s="3" t="n">
@@ -9177,9 +9387,14 @@
       <c r="G194" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H194" s="6">
-        <f>"66' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x20' à 147-159 bpm (76-82% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*82/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*87/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : endurance de tempo, pont vers l'allure IM"&amp;CHAR(10)&amp;"FC bloc cible : 147-159 bpm (76-82% FC max) | Cadence : 85-92 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66' EF Z2 (127-140 bpm / 120-140 W) | 3x20' à 147-159 bpm (76-82% FC max / 165-175 W) — r=5'
+Objectif : endurance de tempo, pont vers l'allure IM
+FC bloc cible : 147-159 bpm (76-82% FC max) | Cadence : 85-92 rpm | RPE 6-7/10
+NUTRITION : 60g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I194" s="3" t="n"/>
       <c r="J194" s="3" t="n">
@@ -9347,9 +9562,14 @@
       <c r="G198" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H198" s="6">
-        <f>"83' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 60g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I198" s="3" t="n"/>
       <c r="J198" s="3" t="n">
@@ -9476,9 +9696,12 @@
       <c r="G201" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H201" s="6">
-        <f>"289' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 60g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I201" s="3" t="n"/>
       <c r="J201" s="3" t="n">
@@ -9635,9 +9858,14 @@
       <c r="G206" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H206" s="6">
-        <f>"70' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x12' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70' EF Z2 (127-140 bpm / 120-140 W) | 2x12' @ 90% FTP (180 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~163 bpm (84% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 60g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I206" s="3" t="n"/>
       <c r="J206" s="3" t="n">
@@ -9721,9 +9949,12 @@
       <c r="G208" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H208" s="6">
-        <f>"100' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") — parcours Paris, terrain plat"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;90'"</f>
-        <v/>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100' Z2 (127-140 bpm / 120-140 W) — parcours Paris, terrain plat
+Cadence souple 85-90 rpm
+NUTRITION : 60g glucides/h si &gt;90'</t>
+        </is>
       </c>
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="3" t="n">
@@ -10361,9 +10592,11 @@
       <c r="G224" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H224" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I224" s="3" t="n"/>
       <c r="J224" s="3" t="n">
@@ -10401,9 +10634,12 @@
       <c r="G225" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H225" s="6">
-        <f>"193' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 60g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 60g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I225" s="3" t="n"/>
       <c r="J225" s="3" t="n">
@@ -10647,9 +10883,11 @@
       <c r="G232" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H232" s="6">
-        <f>"51' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H232" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I232" s="3" t="n"/>
       <c r="J232" s="3" t="n">
@@ -10687,9 +10925,14 @@
       <c r="G233" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H233" s="6">
-        <f>"53' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x28' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : travailler juste sous le seuil lactique (sweet spot)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H233" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53' EF Z2 (127-140 bpm / 120-140 W) | 2x28' @ 90% FTP (180 W) — r=5'
+Objectif : travailler juste sous le seuil lactique (sweet spot)
+FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I233" s="3" t="n"/>
       <c r="J233" s="3" t="n">
@@ -10859,9 +11102,14 @@
       <c r="G237" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H237" s="6">
-        <f>"61' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H237" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61' EF (127-140 bpm / 120-140 W) | 5x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I237" s="3" t="n"/>
       <c r="J237" s="3" t="n">
@@ -10988,9 +11236,12 @@
       <c r="G240" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H240" s="6">
-        <f>"257' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H240" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 70g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I240" s="3" t="n"/>
       <c r="J240" s="3" t="n">
@@ -11237,9 +11488,11 @@
       <c r="G247" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H247" s="6">
-        <f>"51' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H247" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I247" s="3" t="n"/>
       <c r="J247" s="3" t="n">
@@ -11277,9 +11530,14 @@
       <c r="G248" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H248" s="6">
-        <f>"56' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x30' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement"&amp;CHAR(10)&amp;"FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H248" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56' EF Z2 (127-140 bpm / 120-140 W) | 2x30' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=5'
+Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
+FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I248" s="3" t="n"/>
       <c r="J248" s="3" t="n">
@@ -11446,9 +11704,14 @@
       <c r="G252" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H252" s="6">
-        <f>"65' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H252" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65' EF (127-140 bpm / 120-140 W) | 5x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I252" s="3" t="n"/>
       <c r="J252" s="3" t="n">
@@ -11575,9 +11838,12 @@
       <c r="G255" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H255" s="6">
-        <f>"279' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H255" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 70g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I255" s="3" t="n"/>
       <c r="J255" s="3" t="n">
@@ -11824,9 +12090,11 @@
       <c r="G262" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H262" s="6">
-        <f>"54' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H262" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I262" s="3" t="n"/>
       <c r="J262" s="3" t="n">
@@ -11864,9 +12132,14 @@
       <c r="G263" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H263" s="6">
-        <f>"62' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x30' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : travailler juste sous le seuil lactique (sweet spot)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H263" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62' EF Z2 (127-140 bpm / 120-140 W) | 2x30' @ 90% FTP (180 W) — r=5'
+Objectif : travailler juste sous le seuil lactique (sweet spot)
+FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I263" s="3" t="n"/>
       <c r="J263" s="3" t="n">
@@ -12034,9 +12307,14 @@
       <c r="G267" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H267" s="6">
-        <f>"72' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H267" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72' EF (127-140 bpm / 120-140 W) | 5x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I267" s="3" t="n"/>
       <c r="J267" s="3" t="n">
@@ -12163,9 +12441,12 @@
       <c r="G270" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H270" s="6">
-        <f>"296' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H270" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 70g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I270" s="3" t="n"/>
       <c r="J270" s="3" t="n">
@@ -12413,9 +12694,11 @@
       <c r="G277" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H277" s="6">
-        <f>"39' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H277" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I277" s="3" t="n"/>
       <c r="J277" s="3" t="n">
@@ -12453,9 +12736,14 @@
       <c r="G278" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H278" s="6">
-        <f>"35' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x20' @ 88% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H278" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35' EF Z2 (127-140 bpm / 120-140 W) | 2x20' @ 88% FTP (175 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I278" s="3" t="n"/>
       <c r="J278" s="3" t="n">
@@ -12622,9 +12910,13 @@
       <c r="G282" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H282" s="6">
-        <f>"40' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H282" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I282" s="3" t="n"/>
       <c r="J282" s="3" t="n">
@@ -12750,9 +13042,13 @@
       <c r="G285" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H285" s="6">
-        <f>"193' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"Semaine deload — volume réduit"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H285" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+Semaine deload — volume réduit
+NUTRITION : 70g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I285" s="3" t="n"/>
       <c r="J285" s="3" t="n">
@@ -12951,9 +13247,11 @@
       <c r="G291" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H291" s="6">
-        <f>"54' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H291" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I291" s="3" t="n"/>
       <c r="J291" s="3" t="n">
@@ -12991,9 +13289,16 @@
       <c r="G292" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H292" s="6">
-        <f>"25' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3x1' rapide (110 rpm) | 5' très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") | 20' test — effort maximal régulier"&amp;CHAR(10)&amp;"Objectif : mesurer ta FTP (frais, après la semaine de décharge)"&amp;CHAR(10)&amp;"Départ : 5 premières minutes @ 100% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*100/500,0)*5,"0"),"?")&amp;" W"&amp;"), puis augmente de 5 W toutes les 5' si tu te sens bien — note la puissance moyenne des 20' et la FC moyenne des 10 dernières minutes | Cadence : 85-95 rpm | RPE 9/10"&amp;CHAR(10)&amp;"Calcul : FTP = 0,95 × puissance moyenne des 20' — à reporter dans la case FTP de l'onglet Repères vélo"&amp;CHAR(10)&amp;"81' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H292" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25' EF Z2 (127-140 bpm / 120-140 W) dont 3x1' rapide (110 rpm) | 5' très facile (127-140 bpm / 100-120 W) | 20' test — effort maximal régulier
+Objectif : mesurer ta FTP (frais, après la semaine de décharge)
+Départ : 5 premières minutes @ 100% FTP (200 W), puis augmente de 5 W toutes les 5' si tu te sens bien — note la puissance moyenne des 20' et la FC moyenne des 10 dernières minutes | Cadence : 85-95 rpm | RPE 9/10
+Calcul : FTP = 0,95 × puissance moyenne des 20' — à reporter dans la case FTP de l'onglet Repères vélo
+81' EF Z2 (127-140 bpm / 120-140 W)
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I292" s="3" t="n"/>
       <c r="J292" s="3" t="n">
@@ -13160,9 +13465,14 @@
       <c r="G296" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H296" s="6">
-        <f>"74' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H296" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74' EF (127-140 bpm / 120-140 W) | 5x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I296" s="3" t="n"/>
       <c r="J296" s="3" t="n">
@@ -13289,9 +13599,12 @@
       <c r="G299" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H299" s="6">
-        <f>"300' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H299" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 70g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I299" s="3" t="n"/>
       <c r="J299" s="3" t="n">
@@ -13535,9 +13848,11 @@
       <c r="G306" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H306" s="6">
-        <f>"56' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I306" s="3" t="n"/>
       <c r="J306" s="3" t="n">
@@ -13620,9 +13935,14 @@
       <c r="G308" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H308" s="6">
-        <f>"40' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3 ouvertures de 30'' à 90% FC max ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*120/500,0)*5,"0"),"?")&amp;" W"&amp;") | 6x4' @ 112% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*112/500,0)*5,"0"),"?")&amp;" W"&amp;" — 186 bpm en fin de répétition) — r=4' Z1 | 56' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Objectif : puissance aérobie maximale (VO2max), intervalles courts"&amp;CHAR(10)&amp;"FC fin de répétition : 184-194 bpm (95-100% FC max) | Cadence : 90-100 rpm | RPE 8-9/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H308" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40' EF Z2 (127-140 bpm / 120-140 W) dont 3 ouvertures de 30'' à 90% FC max (240 W) | 6x4' @ 112% FTP (225 W — 186 bpm en fin de répétition) — r=4' Z1 | 56' EF Z2 (127-140 bpm / 120-140 W)
+Objectif : puissance aérobie maximale (VO2max), intervalles courts
+FC fin de répétition : 184-194 bpm (95-100% FC max) | Cadence : 90-100 rpm | RPE 8-9/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I308" s="3" t="n"/>
       <c r="J308" s="3" t="n">
@@ -13789,9 +14109,14 @@
       <c r="G312" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H312" s="6">
-        <f>"80' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H312" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80' EF (127-140 bpm / 120-140 W) | 5x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 70g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I312" s="3" t="n"/>
       <c r="J312" s="3" t="n">
@@ -13872,9 +14197,12 @@
       <c r="G314" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H314" s="6">
-        <f>"311' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 70g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H314" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 70g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I314" s="3" t="n"/>
       <c r="J314" s="3" t="n">
@@ -14034,9 +14362,11 @@
       <c r="G319" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H319" s="6">
-        <f>"58' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H319" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I319" s="3" t="n"/>
       <c r="J319" s="3" t="n">
@@ -14074,9 +14404,14 @@
       <c r="G320" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H320" s="6">
-        <f>"78' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x33' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : travailler juste sous le seuil lactique (sweet spot)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H320" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78' EF Z2 (127-140 bpm / 120-140 W) | 2x33' @ 90% FTP (180 W) — r=5'
+Objectif : travailler juste sous le seuil lactique (sweet spot)
+FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I320" s="3" t="n"/>
       <c r="J320" s="3" t="n">
@@ -14244,9 +14579,14 @@
       <c r="G324" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H324" s="6">
-        <f>"89' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H324" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89' EF (127-140 bpm / 120-140 W) | 5x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I324" s="3" t="n"/>
       <c r="J324" s="3" t="n">
@@ -14373,9 +14713,12 @@
       <c r="G327" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H327" s="6">
-        <f>"321' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H327" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 80g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I327" s="3" t="n"/>
       <c r="J327" s="3" t="n">
@@ -14623,9 +14966,11 @@
       <c r="G334" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H334" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H334" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I334" s="3" t="n"/>
       <c r="J334" s="3" t="n">
@@ -14663,9 +15008,14 @@
       <c r="G335" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H335" s="6">
-        <f>"72' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x40' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement"&amp;CHAR(10)&amp;"FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H335" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72' EF Z2 (127-140 bpm / 120-140 W) | 2x40' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=5'
+Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
+FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I335" s="3" t="n"/>
       <c r="J335" s="3" t="n">
@@ -14833,9 +15183,14 @@
       <c r="G339" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H339" s="6">
-        <f>"95' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H339" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95' EF (127-140 bpm / 120-140 W) | 5x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I339" s="3" t="n"/>
       <c r="J339" s="3" t="n">
@@ -14962,9 +15317,12 @@
       <c r="G342" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H342" s="6">
-        <f>"332' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H342" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 80g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I342" s="3" t="n"/>
       <c r="J342" s="3" t="n">
@@ -15529,9 +15887,11 @@
       <c r="G358" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H358" s="6">
-        <f>"51' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H358" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I358" s="3" t="n"/>
       <c r="J358" s="3" t="n">
@@ -15569,9 +15929,12 @@
       <c r="G359" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H359" s="6">
-        <f>"120' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") — pas de bloc FTP cette semaine (reprise post-ski)"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"</f>
-        <v/>
+      <c r="H359" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120' Z2 (127-140 bpm / 120-140 W) — pas de bloc FTP cette semaine (reprise post-ski)
+Cadence souple 85-90 rpm
+NUTRITION : 80g glucides/h si &gt;90'</t>
+        </is>
       </c>
       <c r="I359" s="3" t="n"/>
       <c r="J359" s="3" t="n">
@@ -15738,9 +16101,12 @@
       <c r="G363" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H363" s="6">
-        <f>"96' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — pas de travail de force cette semaine"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"</f>
-        <v/>
+      <c r="H363" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96' Z2 très facile (127-140 bpm / 100-120 W) — pas de travail de force cette semaine
+Cadence souple 85-90 rpm
+NUTRITION : 80g glucides/h si &gt;90'</t>
+        </is>
       </c>
       <c r="I363" s="3" t="n"/>
       <c r="J363" s="3" t="n">
@@ -15867,9 +16233,12 @@
       <c r="G366" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H366" s="6">
-        <f>"246' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H366" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 80g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I366" s="3" t="n"/>
       <c r="J366" s="3" t="n">
@@ -16116,9 +16485,11 @@
       <c r="G373" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H373" s="6">
-        <f>"56' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H373" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I373" s="3" t="n"/>
       <c r="J373" s="3" t="n">
@@ -16156,9 +16527,14 @@
       <c r="G374" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H374" s="6">
-        <f>"66' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x30' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : travailler juste sous le seuil lactique (sweet spot)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H374" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66' EF Z2 (127-140 bpm / 120-140 W) | 2x30' @ 90% FTP (180 W) — r=5'
+Objectif : travailler juste sous le seuil lactique (sweet spot)
+FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I374" s="3" t="n"/>
       <c r="J374" s="3" t="n">
@@ -16328,9 +16704,14 @@
       <c r="G378" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H378" s="6">
-        <f>"77' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x5' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H378" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77' EF (127-140 bpm / 120-140 W) | 5x5' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I378" s="3" t="n"/>
       <c r="J378" s="3" t="n">
@@ -16457,9 +16838,12 @@
       <c r="G381" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H381" s="6">
-        <f>"300' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H381" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 80g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I381" s="3" t="n"/>
       <c r="J381" s="3" t="n">
@@ -16707,9 +17091,11 @@
       <c r="G388" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H388" s="6">
-        <f>"47' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H388" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I388" s="3" t="n"/>
       <c r="J388" s="3" t="n">
@@ -16747,9 +17133,14 @@
       <c r="G389" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H389" s="6">
-        <f>"52' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x20' @ 88% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H389" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52' EF Z2 (127-140 bpm / 120-140 W) | 2x20' @ 88% FTP (175 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I389" s="3" t="n"/>
       <c r="J389" s="3" t="n">
@@ -16916,9 +17307,13 @@
       <c r="G393" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H393" s="6">
-        <f>"46' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H393" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I393" s="3" t="n"/>
       <c r="J393" s="3" t="n">
@@ -17045,9 +17440,13 @@
       <c r="G396" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H396" s="6">
-        <f>"236' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"Semaine deload — volume réduit"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H396" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+Semaine deload — volume réduit
+NUTRITION : 80g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I396" s="3" t="n"/>
       <c r="J396" s="3" t="n">
@@ -17249,9 +17648,11 @@
       <c r="G402" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H402" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H402" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I402" s="3" t="n"/>
       <c r="J402" s="3" t="n">
@@ -17289,9 +17690,14 @@
       <c r="G403" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H403" s="6">
-        <f>"61' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x25' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement"&amp;CHAR(10)&amp;"FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H403" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61' EF Z2 (127-140 bpm / 120-140 W) | 3x25' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=5'
+Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
+FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I403" s="3" t="n"/>
       <c r="J403" s="3" t="n">
@@ -17459,9 +17865,14 @@
       <c r="G407" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H407" s="6">
-        <f>"79' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x5' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H407" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79' EF (127-140 bpm / 120-140 W) | 5x5' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 80g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I407" s="3" t="n"/>
       <c r="J407" s="3" t="n">
@@ -17588,9 +17999,12 @@
       <c r="G410" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H410" s="6">
-        <f>"321' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 80g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H410" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 80g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I410" s="3" t="n"/>
       <c r="J410" s="3" t="n">
@@ -17837,9 +18251,11 @@
       <c r="G417" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H417" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H417" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I417" s="3" t="n"/>
       <c r="J417" s="3" t="n">
@@ -17877,9 +18293,14 @@
       <c r="G418" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H418" s="6">
-        <f>"106' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x25' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : travailler juste sous le seuil lactique (sweet spot)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H418" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106' EF Z2 (127-140 bpm / 120-140 W) | 2x25' @ 90% FTP (180 W) — r=5'
+Objectif : travailler juste sous le seuil lactique (sweet spot)
+FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I418" s="3" t="n"/>
       <c r="J418" s="3" t="n">
@@ -18047,9 +18468,14 @@
       <c r="G422" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H422" s="6">
-        <f>"86' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x5' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H422" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86' EF (127-140 bpm / 120-140 W) | 5x5' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I422" s="3" t="n"/>
       <c r="J422" s="3" t="n">
@@ -18176,9 +18602,12 @@
       <c r="G425" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H425" s="6">
-        <f>"343' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H425" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">343' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I425" s="3" t="n"/>
       <c r="J425" s="3" t="n">
@@ -18425,9 +18854,11 @@
       <c r="G432" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H432" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H432" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I432" s="3" t="n"/>
       <c r="J432" s="3" t="n">
@@ -18465,9 +18896,14 @@
       <c r="G433" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H433" s="6">
-        <f>"100' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x20' à 147-159 bpm (76-82% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*82/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*87/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : endurance de tempo, pont vers l'allure IM"&amp;CHAR(10)&amp;"FC bloc cible : 147-159 bpm (76-82% FC max) | Cadence : 85-92 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H433" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100' EF Z2 (127-140 bpm / 120-140 W) | 3x20' à 147-159 bpm (76-82% FC max / 165-175 W) — r=5'
+Objectif : endurance de tempo, pont vers l'allure IM
+FC bloc cible : 147-159 bpm (76-82% FC max) | Cadence : 85-92 rpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I433" s="3" t="n"/>
       <c r="J433" s="3" t="n">
@@ -18635,9 +19071,14 @@
       <c r="G437" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H437" s="6">
-        <f>"99' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 5x5' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H437" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99' EF (127-140 bpm / 120-140 W) | 5x5' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I437" s="3" t="n"/>
       <c r="J437" s="3" t="n">
@@ -18764,9 +19205,12 @@
       <c r="G440" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H440" s="6">
-        <f>"364' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H440" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">364' Z2 (127-140 bpm / 120-140 W)
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I440" s="3" t="n"/>
       <c r="J440" s="3" t="n">
@@ -19010,9 +19454,11 @@
       <c r="G447" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H447" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H447" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I447" s="3" t="n"/>
       <c r="J447" s="3" t="n">
@@ -19050,9 +19496,14 @@
       <c r="G448" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H448" s="6">
-        <f>"67' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x25' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : rester juste sous le seuil lactique, séance complète — Lacanau est une course en Z3, pas d'affûtage"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H448" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67' EF Z2 (127-140 bpm / 120-140 W) | 2x25' @ 90% FTP (180 W) — r=5'
+Objectif : rester juste sous le seuil lactique, séance complète — Lacanau est une course en Z3, pas d'affûtage
+FC bloc cible : ~163 bpm (84% FC max = ton seuil lactique) | Cadence : 87-93 rpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I448" s="3" t="n"/>
       <c r="J448" s="3" t="n">
@@ -19219,9 +19670,13 @@
       <c r="G452" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H452" s="6">
-        <f>"26' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H452" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26' EF (127-140 bpm / 120-140 W) | 3x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I452" s="3" t="n"/>
       <c r="J452" s="3" t="n">
@@ -19345,9 +19800,10 @@
       <c r="G455" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H455" s="6">
-        <f>"15' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — vérification matériel / dépôt sac T1-T2"</f>
-        <v/>
+      <c r="H455" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15' Z2 très facile (127-140 bpm / 100-120 W) — vérification matériel / dépôt sac T1-T2</t>
+        </is>
       </c>
       <c r="I455" s="3" t="n"/>
       <c r="J455" s="3" t="n">
@@ -19560,9 +20016,11 @@
       <c r="G461" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H461" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H461" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I461" s="3" t="n"/>
       <c r="J461" s="3" t="n">
@@ -19600,9 +20058,12 @@
       <c r="G462" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H462" s="6">
-        <f>"118' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") — Z2 facile, pas de bloc FTP (reprise post-Lacanau)"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"</f>
-        <v/>
+      <c r="H462" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118' Z2 (127-140 bpm / 120-140 W) — Z2 facile, pas de bloc FTP (reprise post-Lacanau)
+Cadence souple 85-90 rpm
+NUTRITION : 90g glucides/h si &gt;90'</t>
+        </is>
       </c>
       <c r="I462" s="3" t="n"/>
       <c r="J462" s="3" t="n">
@@ -19769,9 +20230,11 @@
       <c r="G466" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H466" s="6">
-        <f>"75' Z2 facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H466" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75' Z2 facile (127-140 bpm / 120-140 W)
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I466" s="3" t="n"/>
       <c r="J466" s="3" t="n">
@@ -19855,9 +20318,11 @@
       <c r="G468" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H468" s="6">
-        <f>"214' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — Z2 léger, reprise du volume"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"</f>
-        <v/>
+      <c r="H468" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214' Z2 (127-140 bpm / 100-120 W) — Z2 léger, reprise du volume
+NUTRITION : 90g glucides/h si &gt;90'</t>
+        </is>
       </c>
       <c r="I468" s="3" t="n"/>
       <c r="J468" s="3" t="n">
@@ -20112,9 +20577,11 @@
       <c r="G475" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H475" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H475" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I475" s="3" t="n"/>
       <c r="J475" s="3" t="n">
@@ -20152,9 +20619,14 @@
       <c r="G476" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H476" s="6">
-        <f>"85' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x25' @ 90% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*90/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : reprendre le développement du seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~163 bpm (84% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H476" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85' EF Z2 (127-140 bpm / 120-140 W) | 2x25' @ 90% FTP (180 W) — r=5'
+Objectif : reprendre le développement du seuil (FTP)
+FC bloc cible : ~163 bpm (84% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I476" s="3" t="n"/>
       <c r="J476" s="3" t="n">
@@ -20322,9 +20794,14 @@
       <c r="G480" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H480" s="6">
-        <f>"87' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H480" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I480" s="3" t="n"/>
       <c r="J480" s="3" t="n">
@@ -20451,9 +20928,12 @@
       <c r="G483" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H483" s="6">
-        <f>"321' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 2x30' allure IM (136-146 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") dans la seconde moitié — r=10' Z2"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H483" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321' Z2 (127-140 bpm / 120-140 W) dont 2x30' allure IM (136-146 bpm / 140-150 W) dans la seconde moitié — r=10' Z2
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I483" s="3" t="n"/>
       <c r="J483" s="3" t="n">
@@ -20707,9 +21187,11 @@
       <c r="G490" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H490" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H490" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I490" s="3" t="n"/>
       <c r="J490" s="3" t="n">
@@ -20747,9 +21229,14 @@
       <c r="G491" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H491" s="6">
-        <f>"69' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x35' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement"&amp;CHAR(10)&amp;"FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H491" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69' EF Z2 (127-140 bpm / 120-140 W) | 2x35' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=5'
+Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
+FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I491" s="3" t="n"/>
       <c r="J491" s="3" t="n">
@@ -20916,9 +21403,14 @@
       <c r="G495" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H495" s="6">
-        <f>"74' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 6x5' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H495" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74' EF (127-140 bpm / 120-140 W) | 6x5' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I495" s="3" t="n"/>
       <c r="J495" s="3" t="n">
@@ -21045,9 +21537,12 @@
       <c r="G498" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H498" s="6">
-        <f>"343' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3x30' allure IM (136-146 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") dans la seconde moitié — r=10' Z2"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H498" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">343' Z2 (127-140 bpm / 120-140 W) dont 3x30' allure IM (136-146 bpm / 140-150 W) dans la seconde moitié — r=10' Z2
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I498" s="3" t="n"/>
       <c r="J498" s="3" t="n">
@@ -21302,9 +21797,11 @@
       <c r="G505" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H505" s="6">
-        <f>"43' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H505" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I505" s="3" t="n"/>
       <c r="J505" s="3" t="n">
@@ -21342,9 +21839,14 @@
       <c r="G506" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H506" s="6">
-        <f>"33' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x22' @ 88% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : développer la puissance au seuil (FTP)"&amp;CHAR(10)&amp;"FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H506" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33' EF Z2 (127-140 bpm / 120-140 W) | 2x22' @ 88% FTP (175 W) — r=5'
+Objectif : développer la puissance au seuil (FTP)
+FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I506" s="3" t="n"/>
       <c r="J506" s="3" t="n">
@@ -21511,9 +22013,13 @@
       <c r="G510" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H510" s="6">
-        <f>"42' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 4x4' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H510" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42' EF (127-140 bpm / 120-140 W) | 4x4' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I510" s="3" t="n"/>
       <c r="J510" s="3" t="n">
@@ -21595,9 +22101,12 @@
       <c r="G512" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H512" s="6">
-        <f>"300' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3x40' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;")"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h — stratégie course complète"</f>
-        <v/>
+      <c r="H512" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300' Z2 (127-140 bpm / 120-140 W) dont 3x40' allure IM (136-146 bpm, 70-75% FC max / 140-150 W)
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h — stratégie course complète</t>
+        </is>
       </c>
       <c r="I512" s="3" t="n"/>
       <c r="J512" s="3" t="n">
@@ -21844,9 +22353,11 @@
       <c r="G519" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H519" s="6">
-        <f>"64' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H519" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I519" s="3" t="n"/>
       <c r="J519" s="3" t="n">
@@ -21929,9 +22440,14 @@
       <c r="G521" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H521" s="6">
-        <f>"53' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x30' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement"&amp;CHAR(10)&amp;"FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H521" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53' EF Z2 (127-140 bpm / 120-140 W) | 3x30' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=5'
+Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
+FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I521" s="3" t="n"/>
       <c r="J521" s="3" t="n">
@@ -22098,9 +22614,14 @@
       <c r="G525" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H525" s="6">
-        <f>"78' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 6x5' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H525" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78' EF (127-140 bpm / 120-140 W) | 6x5' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I525" s="3" t="n"/>
       <c r="J525" s="3" t="n">
@@ -22226,9 +22747,12 @@
       <c r="G528" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H528" s="6">
-        <f>"354' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3x40' allure IM (136-146 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") dans la seconde moitié — r=10' Z2"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H528" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354' Z2 (127-140 bpm / 120-140 W) dont 3x40' allure IM (136-146 bpm / 140-150 W) dans la seconde moitié — r=10' Z2
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I528" s="3" t="n"/>
       <c r="J528" s="3" t="n">
@@ -22431,9 +22955,11 @@
       <c r="G534" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H534" s="6">
-        <f>"69' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H534" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I534" s="3" t="n"/>
       <c r="J534" s="3" t="n">
@@ -22471,9 +22997,14 @@
       <c r="G535" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H535" s="6">
-        <f>"62' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x45' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement"&amp;CHAR(10)&amp;"FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H535" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62' EF Z2 (127-140 bpm / 120-140 W) | 2x45' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=5'
+Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
+FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I535" s="3" t="n"/>
       <c r="J535" s="3" t="n">
@@ -22641,9 +23172,14 @@
       <c r="G539" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H539" s="6">
-        <f>"84' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 6x5' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H539" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84' EF (127-140 bpm / 120-140 W) | 6x5' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I539" s="3" t="n"/>
       <c r="J539" s="3" t="n">
@@ -22770,9 +23306,12 @@
       <c r="G542" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H542" s="6">
-        <f>"369' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3x45' allure IM (136-146 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") dans la seconde moitié — r=10' Z2"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H542" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">369' Z2 (127-140 bpm / 120-140 W) dont 3x45' allure IM (136-146 bpm / 140-150 W) dans la seconde moitié — r=10' Z2
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I542" s="3" t="n"/>
       <c r="J542" s="3" t="n">
@@ -22976,9 +23515,11 @@
       <c r="G548" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H548" s="6">
-        <f>"69' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H548" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I548" s="3" t="n"/>
       <c r="J548" s="3" t="n">
@@ -23016,9 +23557,14 @@
       <c r="G549" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H549" s="6">
-        <f>"59' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x50' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement"&amp;CHAR(10)&amp;"FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H549" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59' EF Z2 (127-140 bpm / 120-140 W) | 2x50' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=5'
+Objectif : spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
+FC bloc cible : 136-146 bpm (70-75% FC max) | Cadence : 85-92 rpm | RPE 5-6/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I549" s="3" t="n"/>
       <c r="J549" s="3" t="n">
@@ -23186,9 +23732,14 @@
       <c r="G553" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H553" s="6">
-        <f>"89' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 6x5' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H553" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89' EF (127-140 bpm / 120-140 W) | 6x5' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I553" s="3" t="n"/>
       <c r="J553" s="3" t="n">
@@ -23315,9 +23866,12 @@
       <c r="G556" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H556" s="6">
-        <f>"386' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 3x50' allure IM (136-146 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") dans la seconde moitié — r=10' Z2"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H556" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">386' Z2 (127-140 bpm / 120-140 W) dont 3x50' allure IM (136-146 bpm / 140-150 W) dans la seconde moitié — r=10' Z2
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I556" s="3" t="n"/>
       <c r="J556" s="3" t="n">
@@ -23517,9 +24071,11 @@
       <c r="G562" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H562" s="6">
-        <f>"60' Z1 très facile (&lt; 127 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"&amp;") — récupération active"&amp;CHAR(10)&amp;"Cadence souple 85-90 rpm"</f>
-        <v/>
+      <c r="H562" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60' Z1 très facile (&lt; 127 bpm / 100-110 W) — récupération active
+Cadence souple 85-90 rpm</t>
+        </is>
       </c>
       <c r="I562" s="3" t="n"/>
       <c r="J562" s="3" t="n">
@@ -23557,9 +24113,14 @@
       <c r="G563" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H563" s="6">
-        <f>"35' EF Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 2x20' @ 88% FTP ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=5'"&amp;CHAR(10)&amp;"Objectif : garder du rythme pendant l'affûtage"&amp;CHAR(10)&amp;"FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H563" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35' EF Z2 (127-140 bpm / 120-140 W) | 2x20' @ 88% FTP (175 W) — r=5'
+Objectif : garder du rythme pendant l'affûtage
+FC bloc cible : ~159 bpm (82% FC max) | Cadence : 87-93 rpm | RPE 7-8/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I563" s="3" t="n"/>
       <c r="J563" s="3" t="n">
@@ -23726,9 +24287,14 @@
       <c r="G567" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H567" s="6">
-        <f>"35' EF (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x3' basse cadence (55-62 rpm) @ Z2 ("&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*85/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : force musculaire spécifique, économie de pédalage"&amp;CHAR(10)&amp;"FC : 131-155 bpm | RPE 6-7/10"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;90'"&amp;CHAR(10)&amp;"10' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H567" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35' EF (127-140 bpm / 120-140 W) | 3x3' basse cadence (55-62 rpm) @ Z2 (150-170 W) — r=3'
+Objectif : force musculaire spécifique, économie de pédalage
+FC : 131-155 bpm | RPE 6-7/10
+NUTRITION : 90g glucides/h si &gt;90'
+10' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I567" s="3" t="n"/>
       <c r="J567" s="3" t="n">
@@ -23856,9 +24422,12 @@
       <c r="G570" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H570" s="6">
-        <f>"120' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") dont 2x15' allure IM (136-146 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") dans la seconde moitié — r=10' Z2"&amp;CHAR(10)&amp;"Cadence 85-92 rpm"&amp;CHAR(10)&amp;"NUTRITION : 90g glucides/h si &gt;60'"</f>
-        <v/>
+      <c r="H570" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120' Z2 (127-140 bpm / 120-140 W) dont 2x15' allure IM (136-146 bpm / 140-150 W) dans la seconde moitié — r=10' Z2
+Cadence 85-92 rpm
+NUTRITION : 90g glucides/h si &gt;60'</t>
+        </is>
       </c>
       <c r="I570" s="3" t="n"/>
       <c r="J570" s="3" t="n">
@@ -23970,9 +24539,12 @@
       <c r="G574" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H574" s="6">
-        <f>"36' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x5' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=3'"&amp;CHAR(10)&amp;"Objectif : activation + vérification matériel (réglages, pression des pneus, ravitaillement de course)"&amp;CHAR(10)&amp;"3' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H574" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36' Z2 (127-140 bpm / 120-140 W) | 3x5' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=3'
+Objectif : activation + vérification matériel (réglages, pression des pneus, ravitaillement de course)
+3' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I574" s="3" t="n"/>
       <c r="J574" s="3" t="n">
@@ -24052,9 +24624,10 @@
       <c r="G576" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H576" s="6">
-        <f>"35' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — activation/vérification matériel"</f>
-        <v/>
+      <c r="H576" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35' Z2 très facile (127-140 bpm / 100-120 W) — activation/vérification matériel</t>
+        </is>
       </c>
       <c r="I576" s="3" t="n"/>
       <c r="J576" s="3" t="n">
@@ -24137,9 +24710,12 @@
       <c r="G578" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H578" s="6">
-        <f>"30' Z2 (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;") | 3x2' allure IM (136-146 bpm, 70-75% FC max / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"&amp;") — r=2'"&amp;CHAR(10)&amp;"Objectif : activation, retrouver les sensations de course"&amp;CHAR(10)&amp;"5' RC (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W"&amp;")"</f>
-        <v/>
+      <c r="H578" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30' Z2 (127-140 bpm / 120-140 W) | 3x2' allure IM (136-146 bpm, 70-75% FC max / 140-150 W) — r=2'
+Objectif : activation, retrouver les sensations de course
+5' RC (127-140 bpm / 120-140 W)</t>
+        </is>
       </c>
       <c r="I578" s="3" t="n"/>
       <c r="J578" s="3" t="n">
@@ -24305,9 +24881,10 @@
       <c r="G582" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H582" s="6">
-        <f>"25' Z2 très facile (127-140 bpm / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*50/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;" W"&amp;") — activation/vérification matériel"</f>
-        <v/>
+      <c r="H582" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25' Z2 très facile (127-140 bpm / 100-120 W) — activation/vérification matériel</t>
+        </is>
       </c>
       <c r="I582" s="3" t="n"/>
       <c r="J582" s="3" t="n">

--- a/Marathon_programme.xlsx
+++ b/Marathon_programme.xlsx
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="FTP">'Repères vélo'!$B$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -86,7 +86,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 29' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 29' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -97,13 +97,13 @@
   </si>
   <si>
     <t>🎯 Sweet spot : travailler juste sous le seuil
-ÉCHAUFFEMENT — 20' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 20' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 22' à 180 W (91 % FTP) · 87-93 rpm · FC fin ≈165
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 22' à 190 W (91 % FTP) · 87-93 rpm · FC fin ≈165
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 🍌 40 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>Jeudi</t>
@@ -132,11 +132,11 @@
   </si>
   <si>
     <t>🎯 Force très légère, reprise
-ÉCHAUFFEMENT — 10' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 10' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -214,7 +214,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 38' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 38' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -225,13 +225,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 20' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 20' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 10' à 180 W (89 % FTP) · 87-93 rpm · FC fin ≈161
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 10' à 190 W (89 % FTP) · 87-93 rpm · FC fin ≈161
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 40 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>26' EF Z2 (127-140 bpm) | 4x20'' strides
@@ -245,11 +245,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 10' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 10' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -276,10 +276,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 156' (71.5 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 156' (71.5 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 40 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -318,7 +318,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 24' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 24' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -326,13 +326,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 20' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 20' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 9' à 175 W (88 % FTP) · 87-93 rpm · FC fin ≈159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 9' à 185 W (88 % FTP) · 87-93 rpm · FC fin ≈159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 40 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 175 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>Natation technique pré-course</t>
@@ -375,7 +375,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 33' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 33' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -383,13 +383,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 20' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 20' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 3 x :
-  • 9' à 185 W (92 % FTP) · 87-93 rpm · FC fin ≈167
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 9' à 195 W (92 % FTP) · 87-93 rpm · FC fin ≈167
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 40 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 195 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -431,10 +431,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 230' (106 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 230' (106 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 40 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -465,7 +465,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 52' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 52' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -473,13 +473,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 89' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 89' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 7' à 175 W (88 % FTP) · 87-93 rpm · FC fin ≈159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 7' à 185 W (88 % FTP) · 87-93 rpm · FC fin ≈159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 40 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 175 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -497,11 +497,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 39' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 39' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -539,7 +539,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 43' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 43' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -547,13 +547,13 @@
   </si>
   <si>
     <t>🎯 Travailler juste sous le seuil lactique (sweet spot)
-ÉCHAUFFEMENT — 45' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 45' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 3 x :
-  • 12' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 12' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 40 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>Natation test CSS 400/200</t>
@@ -578,11 +578,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 50' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 50' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -615,10 +615,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 236' (110 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 236' (110 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 40 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -652,12 +652,12 @@
   </si>
   <si>
     <t>🎯 Tolérance au lactate et relances, alternance sous / au-dessus du seuil
-ÉCHAUFFEMENT — 51' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 51' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 3 blocs de 12', chacun = 3 x (3' sous + 1' sur) enchaînés :
-  • 3' sous le seuil · 185 W (93 % FTP) · 87-93 rpm · FC ≈155
-  • 1' au-dessus · 215 W (107 % FTP) · FC ≈171
-  → 5' récup Z1 entre blocs · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 3' sous le seuil · 195 W (93 % FTP) · 87-93 rpm · FC ≈155
+  • 1' au-dessus · 225 W (107 % FTP) · FC ≈171
+  → 5' récup Z1 entre blocs · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 40 g glucides/h si &gt; 90'
 ⚠ Pilotage aux watts : sur le 1', la FC n'a pas le temps de suivre. Relance assise, sans à-coup</t>
   </si>
@@ -678,11 +678,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 61' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 61' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 40 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -713,10 +713,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 246' (115 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 246' (115 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 40 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -751,7 +751,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 43' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 43' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -762,14 +762,14 @@
   </si>
   <si>
     <t>🎯 Puissance aérobie maximale (VO2max), intervalles courts
-ÉCHAUFFEMENT — 40' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 3 ouvertures de 30'' à 240 W
+ÉCHAUFFEMENT — 40' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 3 ouvertures de 30'' à 250 W
 CORPS — 5 x :
-  • 3' à 230 W (115 % FTP) · 90-100 rpm · FC fin 184-194
-  • 3' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 34' Z2 · 120-140 W (60-70 % FTP), puis 10' souple &lt;110 W
+  • 3' à 240 W (115 % FTP) · 90-100 rpm · FC fin 184-194
+  • 3' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 34' Z2 · 125-145 W (60-70 % FTP), puis 10' souple &lt;115 W
 ⚡ RPE 8-9/10 · 🍌 40 g glucides/h si &gt; 90'
-⚠ Mode ERG. Si tu ne tiens plus 230 W sur la dernière, arrête une rép plus tôt : c'est la qualité qui compte</t>
+⚠ Mode ERG. Si tu ne tiens plus 240 W sur la dernière, arrête une rép plus tôt : c'est la qualité qui compte</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -789,11 +789,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 72' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 72' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 40 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -823,10 +823,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 257' (120 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 257' (120 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 40 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -844,7 +844,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 32' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 32' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -852,13 +852,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 32' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 32' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 15' à 175 W (88 % FTP) · 87-93 rpm · FC fin ≈159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 15' à 185 W (88 % FTP) · 87-93 rpm · FC fin ≈159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 50 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 175 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -877,11 +877,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 35' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 35' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -912,11 +912,11 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 167' (78 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 167' (78 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 📝 Semaine de décharge : volume réduit
 🍌 50 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t xml:space="preserve">  S10 — 02/11/2026 → 08/11/2026   |     Phase 1 — Base</t>
@@ -948,15 +948,15 @@
   </si>
   <si>
     <t>🎯 Mesurer ta FTP (frais, après la semaine de décharge)
-ÉCHAUFFEMENT — 25' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 25' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
   dont 3 x 1' rapide à 110 rpm
-  puis 5' très facile · 100-120 W (50-60 % FTP)
+  puis 5' très facile · 105-125 W (50-60 % FTP)
 TEST — 20' effort maximal régulier · 85-95 rpm
-  • 5 premières minutes à 200 W (100 % FTP)
+  • 5 premières minutes à 210 W (100 % FTP)
   • puis +5 W toutes les 5' si tu te sens bien
   • note la puissance moyenne des 20' et la FC moyenne des 10 dernières minutes
-APRÈS LE TEST — 56' Z2 · 120-140 W (60-70 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+APRÈS LE TEST — 56' Z2 · 125-145 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 🧮 FTP = 0,95 × puissance moyenne des 20' → à reporter dans l'onglet Repères vélo (je recale ensuite les watts du plan)
 ⚡ RPE 9/10 · 🍌 50 g glucides/h si &gt; 90'
 ⚠ Mode libre (pas d'ERG) : pars prudent, c'est la régularité qui fait le bon test</t>
@@ -979,11 +979,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 70' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 70' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 50 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1013,10 +1013,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 261' (122 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 261' (122 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 50 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -1056,13 +1056,13 @@
   </si>
   <si>
     <t>🎯 Élever le seuil (blocs courts à intensité haute)
-ÉCHAUFFEMENT — 64' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 64' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 4 x :
-  • 9' à 205 W (102 % FTP) · 88-95 rpm · FC fin ≈169
-  • 4' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 9' à 215 W (102 % FTP) · 88-95 rpm · FC fin ≈169
+  • 4' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 8/10 · 🍌 50 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 205 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 215 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -1081,11 +1081,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 72' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 72' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 50 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1116,10 +1116,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 268' (125 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 268' (125 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 50 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -1150,7 +1150,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 47' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 47' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -1158,12 +1158,12 @@
   </si>
   <si>
     <t>🎯 Tolérance au lactate et relances, alternance sous / au-dessus du seuil
-ÉCHAUFFEMENT — 71' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 71' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 blocs de 20', chacun = 5 x (3' sous + 1' sur) enchaînés :
-  • 3' sous le seuil · 185 W (93 % FTP) · 87-93 rpm · FC ≈155
-  • 1' au-dessus · 215 W (107 % FTP) · FC ≈171
-  → 5' récup Z1 entre blocs · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 3' sous le seuil · 195 W (93 % FTP) · 87-93 rpm · FC ≈155
+  • 1' au-dessus · 225 W (107 % FTP) · FC ≈171
+  → 5' récup Z1 entre blocs · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 50 g glucides/h si &gt; 90'
 ⚠ Pilotage aux watts : sur le 1', la FC n'a pas le temps de suivre. Relance assise, sans à-coup</t>
   </si>
@@ -1185,11 +1185,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 74' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 74' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 50 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1221,10 +1221,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 274' (128 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 274' (128 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 50 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -1258,13 +1258,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 30' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 30' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 18' à 175 W (88 % FTP) · 87-93 rpm · FC fin ≈159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 18' à 185 W (88 % FTP) · 87-93 rpm · FC fin ≈159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 60 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 175 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Technique, puis allure IM en continu
@@ -1287,11 +1287,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 42' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 42' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1315,11 +1315,11 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 182' (85 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 182' (85 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 📝 Semaine de décharge : volume réduit
 🍌 60 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t xml:space="preserve">  S14 — 30/11/2026 → 06/12/2026   |     Phase 2 — Build</t>
@@ -1343,13 +1343,13 @@
   </si>
   <si>
     <t>🎯 Travailler juste sous le seuil lactique (sweet spot)
-ÉCHAUFFEMENT — 61' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 61' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 25' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 25' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 60 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Seuil (CSS) puis allure soutenue
@@ -1375,11 +1375,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 74' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 74' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 60 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1411,10 +1411,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 279' (130 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 279' (130 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 60 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -1451,14 +1451,14 @@
   </si>
   <si>
     <t>🎯 Puissance aérobie maximale (VO2max), intervalles courts
-ÉCHAUFFEMENT — 40' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 3 ouvertures de 30'' à 240 W
+ÉCHAUFFEMENT — 40' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 3 ouvertures de 30'' à 250 W
 CORPS — 5 x :
-  • 4' à 225 W (112 % FTP) · 90-100 rpm · FC fin 184-194
-  • 4' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 51' Z2 · 120-140 W (60-70 % FTP), puis 10' souple &lt;110 W
+  • 4' à 235 W (112 % FTP) · 90-100 rpm · FC fin 184-194
+  • 4' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 51' Z2 · 125-145 W (60-70 % FTP), puis 10' souple &lt;115 W
 ⚡ RPE 8-9/10 · 🍌 60 g glucides/h si &gt; 90'
-⚠ Mode ERG. Si tu ne tiens plus 225 W sur la dernière, arrête une rép plus tôt : c'est la qualité qui compte</t>
+⚠ Mode ERG. Si tu ne tiens plus 235 W sur la dernière, arrête une rép plus tôt : c'est la qualité qui compte</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -1478,11 +1478,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 79' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 79' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 60 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1514,10 +1514,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 285' (133 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 285' (133 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 60 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -1551,7 +1551,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 51' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 51' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -1559,11 +1559,11 @@
   </si>
   <si>
     <t>🎯 Endurance de tempo, pont vers l'allure IM
-ÉCHAUFFEMENT — 66' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 66' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 3 x :
-  • 20' tempo · 165-175 W (82-87 % FTP) · 85-92 rpm · FC 147-159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 20' tempo · 175-185 W (82-87 % FTP) · 85-92 rpm · FC 147-159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 60 g glucides/h si &gt; 90'
 ⚠ Mode ERG. Bloc régulier : si la FC dépasse 159, baisse de 5 W</t>
   </si>
@@ -1585,11 +1585,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 83' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 83' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 60 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1621,10 +1621,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 289' (135 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 289' (135 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 60 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -1647,13 +1647,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 70' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 70' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 12' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 12' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 60 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Technique, puis allure IM en continu
@@ -1674,10 +1674,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale
-CORPS — 100' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 100' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-90 rpm
 📝 Parcours Paris, terrain plat
 🍌 60 g glucides/h si &gt; 90'
-⚠ Plafond 140 bpm ; dans les bosses, max 170 W</t>
+⚠ Plafond 140 bpm ; dans les bosses, max 180 W</t>
   </si>
   <si>
     <t>🎯 Progression SV1 → SV2, endurance de seuil
@@ -1780,7 +1780,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 60' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 60' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -1788,10 +1788,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 193' (90 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 193' (90 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 60 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>CAP en Brick — 15'</t>
@@ -1830,13 +1830,13 @@
   </si>
   <si>
     <t>🎯 Travailler juste sous le seuil lactique (sweet spot)
-ÉCHAUFFEMENT — 53' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 53' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 28' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 28' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 70 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>EF Z2</t>
@@ -1865,11 +1865,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 61' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 61' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 70 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1898,10 +1898,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 257' (120 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 257' (120 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 70 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>Natation récupération</t>
@@ -1924,11 +1924,11 @@
   </si>
   <si>
     <t>🎯 Spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
-ÉCHAUFFEMENT — 56' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 56' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 30' allure IM · 140-150 W (70-75 % FTP) · 85-92 rpm · FC 136-146
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 30' allure IM · 145-160 W (70-75 % FTP) · 85-92 rpm · FC 136-146
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 5-6/10 · 🍌 70 g glucides/h si &gt; 90'
 ⚠ Position aéro tenue tout le bloc, et ravitaillement pris comme en course : c'est la répétition du jour J</t>
   </si>
@@ -1949,11 +1949,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 65' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 65' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 70 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -1981,10 +1981,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 279' (130 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 279' (130 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 70 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>CAP en Brick — 20'</t>
@@ -2023,7 +2023,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 54' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 54' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -2031,13 +2031,13 @@
   </si>
   <si>
     <t>🎯 Travailler juste sous le seuil lactique (sweet spot)
-ÉCHAUFFEMENT — 62' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 62' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 30' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 30' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 70 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>71' EF Z2 (127-140 bpm)
@@ -2058,11 +2058,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 72' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 72' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 70 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2094,10 +2094,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 296' (138 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 296' (138 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 70 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Récupération : relâchement et amplitude
@@ -2131,7 +2131,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 39' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 39' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -2139,13 +2139,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 35' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 35' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 20' à 175 W (88 % FTP) · 87-93 rpm · FC fin ≈159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 20' à 185 W (88 % FTP) · 87-93 rpm · FC fin ≈159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 70 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 175 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>46' EF Z2 (127-140 bpm) | 4x20'' strides
@@ -2163,11 +2163,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 40' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 40' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2191,11 +2191,11 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 193' (90 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 193' (90 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 📝 Semaine de décharge : volume réduit
 🍌 70 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t xml:space="preserve">  S23 — 01/02/2027 → 07/02/2027   |     Phase 3 — Pré-IM</t>
@@ -2214,15 +2214,15 @@
   </si>
   <si>
     <t>🎯 Mesurer ta FTP (frais, après la semaine de décharge)
-ÉCHAUFFEMENT — 25' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 25' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
   dont 3 x 1' rapide à 110 rpm
-  puis 5' très facile · 100-120 W (50-60 % FTP)
+  puis 5' très facile · 105-125 W (50-60 % FTP)
 TEST — 20' effort maximal régulier · 85-95 rpm
-  • 5 premières minutes à 200 W (100 % FTP)
+  • 5 premières minutes à 210 W (100 % FTP)
   • puis +5 W toutes les 5' si tu te sens bien
   • note la puissance moyenne des 20' et la FC moyenne des 10 dernières minutes
-APRÈS LE TEST — 81' Z2 · 120-140 W (60-70 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+APRÈS LE TEST — 81' Z2 · 125-145 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 🧮 FTP = 0,95 × puissance moyenne des 20' → à reporter dans l'onglet Repères vélo (je recale ensuite les watts du plan)
 ⚡ RPE 9/10 · 🍌 70 g glucides/h si &gt; 90'
 ⚠ Mode libre (pas d'ERG) : pars prudent, c'est la régularité qui fait le bon test</t>
@@ -2244,11 +2244,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 74' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 74' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 70 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2280,10 +2280,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 300' (140 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 300' (140 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 70 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t xml:space="preserve">  S24 — 08/02/2027 → 14/02/2027   |     Phase 3 — WE Paris 13/02</t>
@@ -2302,7 +2302,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 56' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 56' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -2324,14 +2324,14 @@
   </si>
   <si>
     <t>🎯 Puissance aérobie maximale (VO2max), intervalles courts
-ÉCHAUFFEMENT — 40' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 3 ouvertures de 30'' à 240 W
+ÉCHAUFFEMENT — 40' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 3 ouvertures de 30'' à 250 W
 CORPS — 6 x :
-  • 4' à 225 W (112 % FTP) · 90-100 rpm · FC fin 184-194
-  • 4' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 56' Z2 · 120-140 W (60-70 % FTP), puis 10' souple &lt;110 W
+  • 4' à 235 W (112 % FTP) · 90-100 rpm · FC fin 184-194
+  • 4' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 56' Z2 · 125-145 W (60-70 % FTP), puis 10' souple &lt;115 W
 ⚡ RPE 8-9/10 · 🍌 70 g glucides/h si &gt; 90'
-⚠ Mode ERG. Si tu ne tiens plus 225 W sur la dernière, arrête une rép plus tôt : c'est la qualité qui compte</t>
+⚠ Mode ERG. Si tu ne tiens plus 235 W sur la dernière, arrête une rép plus tôt : c'est la qualité qui compte</t>
   </si>
   <si>
     <t>89' EF Z2 (127-140 bpm)
@@ -2349,11 +2349,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 80' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 80' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 70 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2370,10 +2370,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 311' (145 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 311' (145 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 70 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t xml:space="preserve">  S25 — 15/02/2027 → 21/02/2027   |     Phase 4 — Spécifique IM</t>
@@ -2396,7 +2396,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 58' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 58' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -2404,13 +2404,13 @@
   </si>
   <si>
     <t>🎯 Travailler juste sous le seuil lactique (sweet spot)
-ÉCHAUFFEMENT — 78' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 78' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 33' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 33' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 80 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>83' EF Z2 (127-140 bpm)
@@ -2431,11 +2431,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 89' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 89' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 80 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2466,10 +2466,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 321' (150 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 321' (150 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 80 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>CAP en Brick — 25'</t>
@@ -2510,11 +2510,11 @@
   </si>
   <si>
     <t>🎯 Spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
-ÉCHAUFFEMENT — 72' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 72' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 40' allure IM · 140-150 W (70-75 % FTP) · 85-92 rpm · FC 136-146
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 40' allure IM · 145-160 W (70-75 % FTP) · 85-92 rpm · FC 136-146
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 5-6/10 · 🍌 80 g glucides/h si &gt; 90'
 ⚠ Position aéro tenue tout le bloc, et ravitaillement pris comme en course : c'est la répétition du jour J</t>
   </si>
@@ -2535,11 +2535,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 95' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 95' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 80 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2571,10 +2571,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 332' (155 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 332' (155 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 80 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Récupération : relâchement et amplitude
@@ -2635,10 +2635,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale
-CORPS — 120' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 120' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-90 rpm
 📝 Pas de bloc FTP cette semaine (reprise post-ski)
 🍌 80 g glucides/h si &gt; 90'
-⚠ Plafond 140 bpm ; dans les bosses, max 170 W</t>
+⚠ Plafond 140 bpm ; dans les bosses, max 180 W</t>
   </si>
   <si>
     <t>68' EF Z2 (127-140 bpm)
@@ -2660,10 +2660,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale
-CORPS — 96' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 96' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 📝 Pas de travail de force cette semaine
 🍌 80 g glucides/h si &gt; 90'
-⚠ Plafond 140 bpm ; dans les bosses, max 170 W</t>
+⚠ Plafond 140 bpm ; dans les bosses, max 180 W</t>
   </si>
   <si>
     <t>🎯 Technique, puis allure IM en continu
@@ -2686,10 +2686,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 246' (115 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 246' (115 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 80 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Récupération : relâchement et amplitude
@@ -2705,13 +2705,13 @@
   </si>
   <si>
     <t>🎯 Travailler juste sous le seuil lactique (sweet spot)
-ÉCHAUFFEMENT — 66' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 66' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 30' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 30' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 80 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Test CSS : mesurer ton allure seuil
@@ -2732,11 +2732,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 77' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 77' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 5' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 5' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 80 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2764,10 +2764,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 300' (140 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 300' (140 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 80 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Récupération : relâchement et amplitude
@@ -2801,13 +2801,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 52' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 52' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 20' à 175 W (88 % FTP) · 87-93 rpm · FC fin ≈159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 20' à 185 W (88 % FTP) · 87-93 rpm · FC fin ≈159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 80 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 175 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>65' EF Z2 (127-140 bpm) | 4x20'' strides
@@ -2826,11 +2826,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 46' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 46' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2855,11 +2855,11 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 236' (110 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 236' (110 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 📝 Semaine de décharge : volume réduit
 🍌 80 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Récupération : relâchement et amplitude
@@ -2887,11 +2887,11 @@
   </si>
   <si>
     <t>🎯 Spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
-ÉCHAUFFEMENT — 61' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 61' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 3 x :
-  • 25' allure IM · 140-150 W (70-75 % FTP) · 85-92 rpm · FC 136-146
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 25' allure IM · 145-160 W (70-75 % FTP) · 85-92 rpm · FC 136-146
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 5-6/10 · 🍌 80 g glucides/h si &gt; 90'
 ⚠ Position aéro tenue tout le bloc, et ravitaillement pris comme en course : c'est la répétition du jour J</t>
   </si>
@@ -2913,11 +2913,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 79' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 79' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 5' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 5' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 80 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -2955,13 +2955,13 @@
   </si>
   <si>
     <t>🎯 Travailler juste sous le seuil lactique (sweet spot)
-ÉCHAUFFEMENT — 106' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 106' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 25' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 25' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 90 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -2976,11 +2976,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 86' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 86' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 5' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 5' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3011,10 +3011,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 343' (160 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 343' (160 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 90 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>CAP en Brick — 30'</t>
@@ -3038,11 +3038,11 @@
   </si>
   <si>
     <t>🎯 Endurance de tempo, pont vers l'allure IM
-ÉCHAUFFEMENT — 100' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 100' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 3 x :
-  • 20' tempo · 165-175 W (82-87 % FTP) · 85-92 rpm · FC 147-159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 20' tempo · 175-185 W (82-87 % FTP) · 85-92 rpm · FC 147-159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Mode ERG. Bloc régulier : si la FC dépasse 159, baisse de 5 W</t>
   </si>
@@ -3064,11 +3064,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 99' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 99' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 5 x :
-  • 5' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 5' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3099,10 +3099,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 364' (170 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  Puissance normalisée visée ≤ 140 W (IF ≤ 0,70)
+CORPS — 364' (170 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  Puissance normalisée visée ≤ 145 W (IF ≤ 0,70)
 🍌 90 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>CAP en Brick — 35'</t>
@@ -3135,13 +3135,13 @@
   </si>
   <si>
     <t>🎯 Rester juste sous le seuil lactique, séance complète — Lacanau est une course en Z3, pas d'affûtage
-ÉCHAUFFEMENT — 67' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 67' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 25' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 25' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · 🍌 90 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>🎯 Récupération : relâchement et amplitude
@@ -3159,11 +3159,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 26' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 26' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 3 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3192,7 +3192,7 @@
   </si>
   <si>
     <t>🎯 Vérification matériel / dépôt sac T1-T2
-CORPS — 15' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 15' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Aucun effort : on vérifie le vélo, pas la forme</t>
   </si>
   <si>
@@ -3221,10 +3221,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale
-CORPS — 118' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 118' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-90 rpm
 📝 Z2 facile, pas de bloc FTP (reprise post-Lacanau)
 🍌 90 g glucides/h si &gt; 90'
-⚠ Plafond 140 bpm ; dans les bosses, max 170 W</t>
+⚠ Plafond 140 bpm ; dans les bosses, max 180 W</t>
   </si>
   <si>
     <t>🎯 Endurance aérobie, allure régulière
@@ -3246,8 +3246,8 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale
-CORPS — 75' Z2 facile · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-90 rpm
-⚠ Plafond 140 bpm ; dans les bosses, max 170 W</t>
+CORPS — 75' Z2 facile · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-90 rpm
+⚠ Plafond 140 bpm ; dans les bosses, max 180 W</t>
   </si>
   <si>
     <t>🎯 Technique, puis allure IM en continu
@@ -3268,10 +3268,10 @@
   </si>
   <si>
     <t>🎯 Endurance fondamentale, tenir la durée
-CORPS — 214' (100 km) en Z2 · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-92 rpm
+CORPS — 214' (100 km) en Z2 · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-92 rpm
 📝 Z2 léger, reprise du volume
 🍌 90 g glucides/h si &gt; 90'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>Z2 92' — allure conversationnelle
@@ -3304,13 +3304,13 @@
   </si>
   <si>
     <t>🎯 Reprendre le développement du seuil (FTP)
-ÉCHAUFFEMENT — 85' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 85' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 25' à 180 W (90 % FTP) · 87-93 rpm · FC fin ≈163
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 25' à 190 W (90 % FTP) · 87-93 rpm · FC fin ≈163
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 90 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 180 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 190 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>47' EF Z1-Z2 (120-135 bpm) — COURT
@@ -3318,11 +3318,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 87' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 87' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3345,11 +3345,11 @@
   </si>
   <si>
     <t>🎯 Spécificité IM : allure de course dans la fatigue
-CORPS — 321' (150 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 2 x 30' allure IM · 140-150 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
-  Puissance normalisée visée ≤ 145 W (IF ≤ 0,72)
+CORPS — 321' (150 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 2 x 30' allure IM · 145-160 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
+  Puissance normalisée visée ≤ 150 W (IF ≤ 0,72)
 🍌 90 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>🎯 Récupération : relâchement et amplitude
@@ -3383,11 +3383,11 @@
   </si>
   <si>
     <t>🎯 Spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
-ÉCHAUFFEMENT — 69' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 69' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 35' allure IM · 140-150 W (70-75 % FTP) · 85-92 rpm · FC 136-146
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 35' allure IM · 145-160 W (70-75 % FTP) · 85-92 rpm · FC 136-146
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 5-6/10 · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Position aéro tenue tout le bloc, et ravitaillement pris comme en course : c'est la répétition du jour J</t>
   </si>
@@ -3401,11 +3401,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 74' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 74' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 6 x :
-  • 5' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 5' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3433,11 +3433,11 @@
   </si>
   <si>
     <t>🎯 Spécificité IM : allure de course dans la fatigue
-CORPS — 343' (160 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 3 x 30' allure IM · 140-150 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
-  Puissance normalisée visée ≤ 145 W (IF ≤ 0,72)
+CORPS — 343' (160 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 3 x 30' allure IM · 145-160 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
+  Puissance normalisée visée ≤ 150 W (IF ≤ 0,72)
 🍌 90 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t xml:space="preserve">  S38 — 17/05/2027 → 23/05/2027   |     Phase 4 — Spécifique IM (Deload + Grand Brick)</t>
@@ -3462,13 +3462,13 @@
   </si>
   <si>
     <t>🎯 Développer la puissance au seuil (FTP)
-ÉCHAUFFEMENT — 33' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 33' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 22' à 175 W (88 % FTP) · 87-93 rpm · FC fin ≈159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 22' à 185 W (88 % FTP) · 87-93 rpm · FC fin ≈159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 90 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 175 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>52' EF Z2 (127-140 bpm) | 4x20'' strides
@@ -3487,11 +3487,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 42' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 42' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 4 x :
-  • 4' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 4' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3514,9 +3514,9 @@
   </si>
   <si>
     <t>🎯 Grand Brick : répétition générale du jour J (vélo, 2/3)
-CORPS — 300' en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 3 x 40' allure IM · 140-150 W (70-75 % FTP) · FC 136-146
-  Puissance normalisée visée ≤ 145 W (IF ≤ 0,72)
+CORPS — 300' en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 3 x 40' allure IM · 145-160 W (70-75 % FTP) · FC 136-146
+  Puissance normalisée visée ≤ 150 W (IF ≤ 0,72)
 🍌 90 g glucides/h
 ⚠ Stratégie course complète : nutrition, position, tenue et matériel du jour J</t>
   </si>
@@ -3541,7 +3541,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 64' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 64' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -3559,21 +3559,21 @@
   </si>
   <si>
     <t>🎯 Spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
-ÉCHAUFFEMENT — 53' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 53' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 3 x :
-  • 30' allure IM · 140-150 W (70-75 % FTP) · 85-92 rpm · FC 136-146
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 30' allure IM · 145-160 W (70-75 % FTP) · 85-92 rpm · FC 136-146
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 5-6/10 · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Position aéro tenue tout le bloc, et ravitaillement pris comme en course : c'est la répétition du jour J</t>
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 78' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 78' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 6 x :
-  • 5' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 5' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3603,11 +3603,11 @@
   </si>
   <si>
     <t>🎯 Spécificité IM : allure de course dans la fatigue
-CORPS — 354' (165 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 3 x 40' allure IM · 140-150 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
-  Puissance normalisée visée ≤ 145 W (IF ≤ 0,72)
+CORPS — 354' (165 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 3 x 40' allure IM · 145-160 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
+  Puissance normalisée visée ≤ 150 W (IF ≤ 0,72)
 🍌 90 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t xml:space="preserve">  S40 — 31/05/2027 → 06/06/2027   |     Phase 4 — Bloc Final IM</t>
@@ -3634,7 +3634,7 @@
   </si>
   <si>
     <t>🎯 Récupération active
-CORPS — 69' Z1 très facile · 100-110 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
+CORPS — 69' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
 ⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
@@ -3642,21 +3642,21 @@
   </si>
   <si>
     <t>🎯 Spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
-ÉCHAUFFEMENT — 62' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 62' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 45' allure IM · 140-150 W (70-75 % FTP) · 85-92 rpm · FC 136-146
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 45' allure IM · 145-160 W (70-75 % FTP) · 85-92 rpm · FC 136-146
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 5-6/10 · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Position aéro tenue tout le bloc, et ravitaillement pris comme en course : c'est la répétition du jour J</t>
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 84' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 84' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 6 x :
-  • 5' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 5' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3687,11 +3687,11 @@
   </si>
   <si>
     <t>🎯 Spécificité IM : allure de course dans la fatigue
-CORPS — 369' (172 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 3 x 45' allure IM · 140-150 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
-  Puissance normalisée visée ≤ 145 W (IF ≤ 0,72)
+CORPS — 369' (172 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 3 x 45' allure IM · 145-160 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
+  Puissance normalisée visée ≤ 150 W (IF ≤ 0,72)
 🍌 90 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>CAP en Brick — 40'</t>
@@ -3729,11 +3729,11 @@
   </si>
   <si>
     <t>🎯 Spécificité Ironman : rouler à l'effort de course et répéter le ravitaillement
-ÉCHAUFFEMENT — 59' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 59' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 50' allure IM · 140-150 W (70-75 % FTP) · 85-92 rpm · FC 136-146
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 50' allure IM · 145-160 W (70-75 % FTP) · 85-92 rpm · FC 136-146
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 5-6/10 · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Position aéro tenue tout le bloc, et ravitaillement pris comme en course : c'est la répétition du jour J</t>
   </si>
@@ -3754,11 +3754,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 89' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 89' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 6 x :
-  • 5' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 5' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3789,11 +3789,11 @@
   </si>
   <si>
     <t>🎯 Spécificité IM : allure de course dans la fatigue
-CORPS — 386' (180 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 3 x 50' allure IM · 140-150 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
-  Puissance normalisée visée ≤ 145 W (IF ≤ 0,72)
+CORPS — 386' (180 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 3 x 50' allure IM · 145-160 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
+  Puissance normalisée visée ≤ 150 W (IF ≤ 0,72)
 🍌 90 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t>CAP en Brick — 45'</t>
@@ -3819,13 +3819,13 @@
   </si>
   <si>
     <t>🎯 Garder du rythme pendant l'affûtage
-ÉCHAUFFEMENT — 35' Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+ÉCHAUFFEMENT — 35' Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
 CORPS — 2 x :
-  • 20' à 175 W (88 % FTP) · 87-93 rpm · FC fin ≈159
-  • 5' récup Z1 · &lt;110 W (&lt;55 % FTP)
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+  • 20' à 185 W (88 % FTP) · 87-93 rpm · FC fin ≈159
+  • 5' récup Z1 · &lt;115 W (&lt;55 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 7-8/10 · 🍌 90 g glucides/h si &gt; 90'
-⚠ Mode ERG. Ne pars jamais au-dessus de 175 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
+⚠ Mode ERG. Ne pars jamais au-dessus de 185 W ; la FC qui dérive en fin de bloc est normale, ce sont les watts qui commandent</t>
   </si>
   <si>
     <t>60' EF Z2 (127-140 bpm)
@@ -3843,11 +3843,11 @@
   </si>
   <si>
     <t>🎯 Force musculaire spécifique, économie de pédalage
-ÉCHAUFFEMENT — 35' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 35' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 3 x :
-  • 3' basse cadence · 150-170 W (75-85 % FTP) · 55-62 rpm
+  • 3' basse cadence · 160-180 W (75-85 % FTP) · 55-62 rpm
   • 3' récup Z2 souple · 90 rpm
-RETOUR AU CALME — 10' Z2 souple · 120-140 W (60-70 % FTP)
+RETOUR AU CALME — 10' Z2 souple · 125-145 W (60-70 % FTP)
 ⚡ RPE 6-7/10 · FC 131-155 normale sur les blocs · 🍌 90 g glucides/h si &gt; 90'
 ⚠ Assis, buste immobile, genou dans l'axe : c'est la jambe qui pousse, pas le dos</t>
   </si>
@@ -3879,11 +3879,11 @@
   </si>
   <si>
     <t>🎯 Spécificité IM : allure de course dans la fatigue
-CORPS — 120' (56 km) en Z2 · 120-140 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
-  dont 2 x 15' allure IM · 140-150 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
-  Puissance normalisée visée ≤ 145 W (IF ≤ 0,72)
+CORPS — 120' (56 km) en Z2 · 125-145 W (60-70 % FTP) · &lt;140 bpm · 85-92 rpm
+  dont 2 x 15' allure IM · 145-160 W (70-75 % FTP) · FC 136-146 dans la seconde moitié — 10' Z2 entre les blocs
+  Puissance normalisée visée ≤ 150 W (IF ≤ 0,72)
 🍌 90 g glucides/h si &gt; 60'
-⚠ Dans les bosses, plafond 170 W : on monte en Z2-Z3, jamais au seuil</t>
+⚠ Dans les bosses, plafond 180 W : on monte en Z2-Z3, jamais au seuil</t>
   </si>
   <si>
     <t xml:space="preserve">  S43 — 21/06/2027 → 27/06/2027   |     COMPETITION — IRONMAN LES SABLES D'OLONNE 27/06</t>
@@ -3899,12 +3899,12 @@
   </si>
   <si>
     <t>🎯 Activation + vérification matériel (réglages, pression des pneus, ravitaillement de course)
-ÉCHAUFFEMENT — 36' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 36' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 3 x :
-  • 5' allure IM · 140-150 W (70-75 % FTP) · FC 136-146
-  • 3' souple · &lt;110 W (&lt;55 % FTP)
+  • 5' allure IM · 145-160 W (70-75 % FTP) · FC 136-146
+  • 3' souple · &lt;115 W (&lt;55 % FTP)
 RETOUR AU CALME — 3' souple
-⚠ Sensations seulement : aucun watt au-dessus de 150 W, on garde tout pour dimanche</t>
+⚠ Sensations seulement : aucun watt au-dessus de 160 W, on garde tout pour dimanche</t>
   </si>
   <si>
     <t>20' EF Z2 (127-140 bpm) | 4x20'' strides en fin
@@ -3915,7 +3915,7 @@
   </si>
   <si>
     <t>🎯 Activation/vérification matériel
-CORPS — 35' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 35' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Aucun effort : on vérifie le vélo, pas la forme</t>
   </si>
   <si>
@@ -3938,12 +3938,12 @@
   </si>
   <si>
     <t>🎯 Activation, retrouver les sensations de course
-ÉCHAUFFEMENT — 30' Z2 · 120-140 W (60-70 % FTP) · 85-92 rpm
+ÉCHAUFFEMENT — 30' Z2 · 125-145 W (60-70 % FTP) · 85-92 rpm
 CORPS — 3 x :
-  • 2' allure IM · 140-150 W (70-75 % FTP) · FC 136-146
-  • 2' souple · &lt;110 W (&lt;55 % FTP)
+  • 2' allure IM · 145-160 W (70-75 % FTP) · FC 136-146
+  • 2' souple · &lt;115 W (&lt;55 % FTP)
 RETOUR AU CALME — 5' souple
-⚠ Sensations seulement : aucun watt au-dessus de 150 W, on garde tout pour dimanche</t>
+⚠ Sensations seulement : aucun watt au-dessus de 160 W, on garde tout pour dimanche</t>
   </si>
   <si>
     <t>EF + 3x1' allure IM + visualisation</t>
@@ -3974,7 +3974,7 @@
   </si>
   <si>
     <t>🎯 Activation/vérification matériel
-CORPS — 25' Z2 très facile · 100-120 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
+CORPS — 25' Z2 très facile · 105-125 W (50-60 % FTP) · &lt;140 bpm · 85-90 rpm
 ⚠ Aucun effort : on vérifie le vélo, pas la forme</t>
   </si>
   <si>
@@ -4985,7 +4985,7 @@
     <t>FTP actuelle (W)</t>
   </si>
   <si>
-    <t>← à modifier après les tests FTP de S10 et S23 : ce tableau se recalcule. Dans les séances du plan, les watts sont écrits pour 200 W ; le % FTP indiqué à côté reste la référence (watts à recaler après chaque test)</t>
+    <t>← à modifier après les tests FTP de S10 et S23 : ce tableau se recalcule. Dans les séances du plan, les watts sont écrits pour 210 W (FTP de travail estimée au ressenti le 22/10/2026, à remplacer par la FTP mesurée au test de S10) ; le % FTP indiqué à côté reste la référence (watts à recaler après chaque test)</t>
   </si>
   <si>
     <t>% FTP</t>
@@ -26444,7 +26444,7 @@
         <v>922</v>
       </c>
       <c r="B2" s="144">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C2" s="176" t="s">
         <v>923</v>
@@ -26484,7 +26484,7 @@
       </c>
       <c r="E4" s="143" t="str">
         <f>"&lt; "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"</f>
-        <v>&lt; 110 W</v>
+        <v>&lt; 115 W</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -26502,7 +26502,7 @@
       </c>
       <c r="E5" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*56/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W (cible "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W)"</f>
-        <v>110-150 W (cible 120-140 W)</v>
+        <v>120-160 W (cible 125-145 W)</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="E6" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"</f>
-        <v>140-150 W</v>
+        <v>145-160 W</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="E7" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*76/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*87/500,0)*5,"0"),"?")&amp;" W"</f>
-        <v>150-175 W</v>
+        <v>160-185 W</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="E8" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*94/500,0)*5,"0"),"?")&amp;" W"</f>
-        <v>175-190 W</v>
+        <v>185-195 W</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -26574,7 +26574,7 @@
       </c>
       <c r="E9" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*95/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*105/500,0)*5,"0"),"?")&amp;" W"</f>
-        <v>190-210 W</v>
+        <v>200-220 W</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -26592,7 +26592,7 @@
       </c>
       <c r="E10" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*93/500,0)*5,"0"),"?")&amp;" / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*107/500,0)*5,"0"),"?")&amp;" W"</f>
-        <v>185 / 215 W</v>
+        <v>195 / 225 W</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="E11" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*106/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*120/500,0)*5,"0"),"?")&amp;" W"</f>
-        <v>210-240 W</v>
+        <v>225-250 W</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">

--- a/Marathon_programme.xlsx
+++ b/Marathon_programme.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhernand\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herna\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_45B3EF83F92D373BFF46D3059687EE9CE902096E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640F4F8E-B7BD-4D9A-90E6-EC8A5B42AFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="4185" windowWidth="36240" windowHeight="14940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan IM Final" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="FTP">'Repères vélo'!$B$2</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,12 +36,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="963">
   <si>
     <t xml:space="preserve">  S01 — 31/08/2026 → 06/09/2026   |     S1 — Transition post-vacances (Z2 pur 70%)</t>
   </si>
@@ -1149,11 +1152,6 @@
 ⚠ Chaque palier un cran au-dessus du précédent, sans à-coup</t>
   </si>
   <si>
-    <t>🎯 Récupération active
-CORPS — 47' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
-  </si>
-  <si>
     <t>Vélo clé — Over-unders 2x20' — r=5'</t>
   </si>
   <si>
@@ -1550,11 +1548,6 @@
 ⚠ Bloc IM final jamais sous 4'55 : c'est l'exercice de retenue du jour J</t>
   </si>
   <si>
-    <t>🎯 Récupération active
-CORPS — 51' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
-  </si>
-  <si>
     <t>Vélo clé — Tempo 3x20' (147-159 bpm) — r=5'</t>
   </si>
   <si>
@@ -1779,11 +1772,6 @@
 Semaine à gros volume CAP — bloc spécifique</t>
   </si>
   <si>
-    <t>🎯 Récupération active
-CORPS — 60' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
-  </si>
-  <si>
     <t>Sortie longue — 193' (90.0 km)</t>
   </si>
   <si>
@@ -2022,11 +2010,6 @@
 ⚠ Bloc IM final jamais sous 4'55 : c'est l'exercice de retenue du jour J</t>
   </si>
   <si>
-    <t>🎯 Récupération active
-CORPS — 54' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
-  </si>
-  <si>
     <t>Vélo clé — 2x30' @ 90% FTP — r=5'</t>
   </si>
   <si>
@@ -2130,11 +2113,6 @@
 Décharge : même type de séance que le bloc précédent, volume de qualité réduit</t>
   </si>
   <si>
-    <t>🎯 Récupération active
-CORPS — 39' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
-  </si>
-  <si>
     <t>Vélo clé — 2x20' @ 88% FTP — r=5'</t>
   </si>
   <si>
@@ -2301,11 +2279,6 @@
 ⚠ Le km allure IM se court sans s'arrêter : on récupère EN courant</t>
   </si>
   <si>
-    <t>🎯 Récupération active
-CORPS — 56' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
-  </si>
-  <si>
     <t>Natation endurance (optionnelle)</t>
   </si>
   <si>
@@ -2393,11 +2366,6 @@
 RETOUR AU CALME — 6' EF · 6'05-6'20/km
 🍌 Répéter le ravitaillement : 30 g de glucides
 ⚠ Bloc IM final jamais sous 4'55 : c'est l'exercice de retenue du jour J</t>
-  </si>
-  <si>
-    <t>🎯 Récupération active
-CORPS — 58' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
     <t>Vélo clé — 2x33' @ 90% FTP — r=5'</t>
@@ -3540,11 +3508,6 @@
     <t xml:space="preserve">  S39 — 24/05/2027 → 30/05/2027   |     Phase 4 — Bloc Final IM</t>
   </si>
   <si>
-    <t>🎯 Récupération active
-CORPS — 64' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
-  </si>
-  <si>
     <t>🎯 Endurance aérobie, allure régulière
 ÉCHAUFFEMENT — 200 m souple · 2:21/100 m
 CORPS :
@@ -3631,11 +3594,6 @@
   • 1 km allure IM · 4'55-5'10/km · FC 150-155
 RETOUR AU CALME — 10' EF · 6'05-6'20/km
 ⚠ Le km allure IM se court sans s'arrêter : on récupère EN courant</t>
-  </si>
-  <si>
-    <t>🎯 Récupération active
-CORPS — 69' Z1 très facile · 105-115 W (50-55 % FTP) · &lt;127 bpm · 85-90 rpm
-⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
   <si>
     <t>Vélo clé — Bloc allure IM 2x45' (136-146 bpm) — r=5'</t>
@@ -5097,6 +5055,61 @@
   </si>
   <si>
     <t>Sources : TrainingPeaks — Lessons from Kona (IF 0,65-0,75 âge-groupe) ; Best Bike Split — Ironman pacing (IF 0,68-0,72, 250-285 TSS) ; zones de Coggan (sweet spot 88-94 % FTP).</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 43' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 47' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 32' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 51' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 60' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 54' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 39' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 56' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 58' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 64' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
+  </si>
+  <si>
+    <t>🎯 Récupération active
+CORPS — 69' Z1-Z2 très facile · 120-130 W (60 % FTP) · FC libre ≈ 120-132 bpm (les watts commandent) · 85-90 rpm
+⚠ Zéro effort, jambes qui tournent : si tu hésites, encore plus facile</t>
   </si>
 </sst>
 </file>
@@ -6287,17 +6300,11 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6305,23 +6312,29 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6615,7 +6628,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="167" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="161"/>
@@ -6964,7 +6977,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="173" t="s">
+      <c r="A13" s="171" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="161"/>
@@ -7311,7 +7324,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="164" t="s">
+      <c r="A25" s="166" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="161"/>
@@ -8007,7 +8020,7 @@
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="164" t="s">
+      <c r="A49" s="166" t="s">
         <v>82</v>
       </c>
       <c r="B49" s="161"/>
@@ -9457,7 +9470,7 @@
       </c>
     </row>
     <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="164" t="s">
+      <c r="A99" s="166" t="s">
         <v>141</v>
       </c>
       <c r="B99" s="161"/>
@@ -9593,160 +9606,160 @@
       </c>
       <c r="K103" s="2"/>
     </row>
-    <row r="104" spans="1:11" ht="166.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46324</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="2">
+        <v>19</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104" s="2">
+        <v>2</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="I104" s="2">
+        <v>3</v>
+      </c>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+    </row>
+    <row r="105" spans="1:11" ht="153.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E105" s="2">
+        <v>66</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G105" s="2">
+        <v>3</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2">
+        <v>31</v>
+      </c>
+      <c r="K105" s="2"/>
+    </row>
+    <row r="106" spans="1:11" ht="216.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>46326</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E104" s="2">
-        <v>70</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G104" s="2">
-        <v>4</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E105" s="2">
-        <v>19</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G105" s="2">
-        <v>2</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="I105" s="2">
-        <v>3</v>
-      </c>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-    </row>
-    <row r="106" spans="1:11" ht="153.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
-        <v>46325</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="D106" s="4" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="E106" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="G106" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I106" s="2"/>
-      <c r="J106" s="2">
-        <v>31</v>
-      </c>
-      <c r="K106" s="2"/>
-    </row>
-    <row r="107" spans="1:11" ht="216.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J106" s="2"/>
+      <c r="K106" s="2">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46326</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E107" s="2">
+        <v>49</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G107" s="2">
+        <v>5</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I107" s="2">
+        <v>7</v>
+      </c>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+    </row>
+    <row r="108" spans="1:11" ht="166.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>46327</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C108" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D107" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E107" s="2">
-        <v>64</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G107" s="2">
-        <v>4</v>
-      </c>
-      <c r="H107" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
-        <v>46326</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="D108" s="4" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="E108" s="2">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G108" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="I108" s="2">
-        <v>7</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="I108" s="2"/>
       <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
+      <c r="K108" s="2">
+        <v>2550</v>
+      </c>
     </row>
     <row r="109" spans="1:11" ht="104.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
@@ -9901,7 +9914,7 @@
         <v>2</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>128</v>
+        <v>952</v>
       </c>
       <c r="I114" s="2"/>
       <c r="J114" s="2">
@@ -10279,7 +10292,7 @@
         <v>2</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>128</v>
+        <v>952</v>
       </c>
       <c r="I127" s="2"/>
       <c r="J127" s="2">
@@ -10657,7 +10670,7 @@
         <v>2</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>185</v>
+        <v>953</v>
       </c>
       <c r="I140" s="2"/>
       <c r="J140" s="2">
@@ -10676,7 +10689,7 @@
         <v>11</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E141" s="2">
         <v>126</v>
@@ -10688,7 +10701,7 @@
         <v>7</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I141" s="2"/>
       <c r="J141" s="2">
@@ -10719,7 +10732,7 @@
         <v>4</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
@@ -10750,7 +10763,7 @@
         <v>2</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I143" s="2">
         <v>7</v>
@@ -10781,7 +10794,7 @@
         <v>5</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I144" s="2"/>
       <c r="J144" s="2">
@@ -10812,7 +10825,7 @@
         <v>4</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
@@ -10831,7 +10844,7 @@
         <v>7</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E146" s="2">
         <v>92</v>
@@ -10843,7 +10856,7 @@
         <v>6</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I146" s="2">
         <v>15</v>
@@ -10862,7 +10875,7 @@
         <v>11</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E147" s="2">
         <v>274</v>
@@ -10874,7 +10887,7 @@
         <v>6</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I147" s="2"/>
       <c r="J147" s="2">
@@ -10905,7 +10918,7 @@
         <v>4</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
@@ -10938,8 +10951,8 @@
       </c>
     </row>
     <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="164" t="s">
-        <v>197</v>
+      <c r="A150" s="166" t="s">
+        <v>196</v>
       </c>
       <c r="B150" s="161"/>
       <c r="C150" s="161"/>
@@ -10992,7 +11005,7 @@
         <v>7</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E152" s="2">
         <v>46</v>
@@ -11004,7 +11017,7 @@
         <v>6</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I152" s="2">
         <v>8</v>
@@ -11035,7 +11048,7 @@
         <v>2</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>142</v>
+        <v>954</v>
       </c>
       <c r="I153" s="2"/>
       <c r="J153" s="2">
@@ -11054,7 +11067,7 @@
         <v>11</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E154" s="2">
         <v>81</v>
@@ -11066,7 +11079,7 @@
         <v>5</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I154" s="2"/>
       <c r="J154" s="2">
@@ -11097,7 +11110,7 @@
         <v>4</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
@@ -11128,7 +11141,7 @@
         <v>2</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I156" s="2">
         <v>5</v>
@@ -11159,7 +11172,7 @@
         <v>3</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I157" s="2"/>
       <c r="J157" s="2">
@@ -11190,7 +11203,7 @@
         <v>4</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
@@ -11221,7 +11234,7 @@
         <v>5</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I159" s="2">
         <v>10</v>
@@ -11240,7 +11253,7 @@
         <v>11</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E160" s="2">
         <v>182</v>
@@ -11252,7 +11265,7 @@
         <v>4</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I160" s="2"/>
       <c r="J160" s="2">
@@ -11286,7 +11299,7 @@
     </row>
     <row r="162" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="162" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B162" s="161"/>
       <c r="C162" s="161"/>
@@ -11339,7 +11352,7 @@
         <v>7</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E164" s="2">
         <v>52</v>
@@ -11351,7 +11364,7 @@
         <v>7</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I164" s="2">
         <v>8.5</v>
@@ -11382,7 +11395,7 @@
         <v>2</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>185</v>
+        <v>953</v>
       </c>
       <c r="I165" s="2"/>
       <c r="J165" s="2">
@@ -11401,7 +11414,7 @@
         <v>11</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E166" s="2">
         <v>126</v>
@@ -11413,7 +11426,7 @@
         <v>6</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I166" s="2"/>
       <c r="J166" s="2">
@@ -11444,7 +11457,7 @@
         <v>6</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
@@ -11475,7 +11488,7 @@
         <v>2</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I168" s="2">
         <v>7.5</v>
@@ -11506,7 +11519,7 @@
         <v>2</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I169" s="2">
         <v>4</v>
@@ -11537,7 +11550,7 @@
         <v>5</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I170" s="2"/>
       <c r="J170" s="2">
@@ -11568,7 +11581,7 @@
         <v>5</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
@@ -11587,7 +11600,7 @@
         <v>7</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E172" s="2">
         <v>99</v>
@@ -11599,7 +11612,7 @@
         <v>6</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I172" s="2">
         <v>16</v>
@@ -11618,7 +11631,7 @@
         <v>11</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E173" s="2">
         <v>279</v>
@@ -11630,7 +11643,7 @@
         <v>6</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I173" s="2"/>
       <c r="J173" s="2">
@@ -11661,7 +11674,7 @@
         <v>4</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
@@ -11694,8 +11707,8 @@
       </c>
     </row>
     <row r="176" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="160" t="s">
-        <v>224</v>
+      <c r="A176" s="169" t="s">
+        <v>223</v>
       </c>
       <c r="B176" s="161"/>
       <c r="C176" s="161"/>
@@ -11760,7 +11773,7 @@
         <v>7</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I178" s="2">
         <v>9.5</v>
@@ -11791,7 +11804,7 @@
         <v>2</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>185</v>
+        <v>953</v>
       </c>
       <c r="I179" s="2"/>
       <c r="J179" s="2">
@@ -11810,7 +11823,7 @@
         <v>11</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E180" s="2">
         <v>137</v>
@@ -11822,7 +11835,7 @@
         <v>8</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I180" s="2"/>
       <c r="J180" s="2">
@@ -11853,7 +11866,7 @@
         <v>4</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
@@ -11884,7 +11897,7 @@
         <v>2</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I182" s="2">
         <v>9</v>
@@ -11915,7 +11928,7 @@
         <v>2</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I183" s="2">
         <v>4</v>
@@ -11946,7 +11959,7 @@
         <v>5</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I184" s="2"/>
       <c r="J184" s="2">
@@ -11977,7 +11990,7 @@
         <v>5</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I185" s="2"/>
       <c r="J185" s="2"/>
@@ -11996,7 +12009,7 @@
         <v>7</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E186" s="2">
         <v>105</v>
@@ -12008,7 +12021,7 @@
         <v>6</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I186" s="2">
         <v>17</v>
@@ -12027,7 +12040,7 @@
         <v>11</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E187" s="2">
         <v>285</v>
@@ -12039,7 +12052,7 @@
         <v>6</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I187" s="2"/>
       <c r="J187" s="2">
@@ -12070,7 +12083,7 @@
         <v>4</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
@@ -12103,8 +12116,8 @@
       </c>
     </row>
     <row r="190" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="160" t="s">
-        <v>237</v>
+      <c r="A190" s="169" t="s">
+        <v>236</v>
       </c>
       <c r="B190" s="161"/>
       <c r="C190" s="161"/>
@@ -12157,7 +12170,7 @@
         <v>7</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E192" s="2">
         <v>65</v>
@@ -12169,7 +12182,7 @@
         <v>6</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I192" s="2">
         <v>11</v>
@@ -12200,7 +12213,7 @@
         <v>2</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>240</v>
+        <v>955</v>
       </c>
       <c r="I193" s="2"/>
       <c r="J193" s="2">
@@ -12219,7 +12232,7 @@
         <v>11</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E194" s="2">
         <v>146</v>
@@ -12231,7 +12244,7 @@
         <v>6</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I194" s="2"/>
       <c r="J194" s="2">
@@ -12262,7 +12275,7 @@
         <v>4</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
@@ -12293,7 +12306,7 @@
         <v>2</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I196" s="2">
         <v>10</v>
@@ -12324,7 +12337,7 @@
         <v>2</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I197" s="2">
         <v>4</v>
@@ -12355,7 +12368,7 @@
         <v>5</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I198" s="2"/>
       <c r="J198" s="2">
@@ -12386,7 +12399,7 @@
         <v>5</v>
       </c>
       <c r="H199" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
@@ -12405,7 +12418,7 @@
         <v>7</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E200" s="2">
         <v>111</v>
@@ -12417,7 +12430,7 @@
         <v>6</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I200" s="2">
         <v>18</v>
@@ -12436,7 +12449,7 @@
         <v>11</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E201" s="2">
         <v>289</v>
@@ -12448,7 +12461,7 @@
         <v>6</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I201" s="2"/>
       <c r="J201" s="2">
@@ -12479,7 +12492,7 @@
         <v>4</v>
       </c>
       <c r="H202" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I202" s="2"/>
       <c r="J202" s="2"/>
@@ -12512,8 +12525,8 @@
       </c>
     </row>
     <row r="204" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="164" t="s">
-        <v>252</v>
+      <c r="A204" s="166" t="s">
+        <v>250</v>
       </c>
       <c r="B204" s="161"/>
       <c r="C204" s="161"/>
@@ -12537,7 +12550,7 @@
         <v>2</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>4</v>
@@ -12566,7 +12579,7 @@
         <v>11</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E206" s="2">
         <v>109</v>
@@ -12578,7 +12591,7 @@
         <v>5</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I206" s="2"/>
       <c r="J206" s="2">
@@ -12609,7 +12622,7 @@
         <v>4</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I207" s="2"/>
       <c r="J207" s="2"/>
@@ -12628,7 +12641,7 @@
         <v>11</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E208" s="2">
         <v>100</v>
@@ -12640,7 +12653,7 @@
         <v>3</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I208" s="2"/>
       <c r="J208" s="2">
@@ -12659,7 +12672,7 @@
         <v>7</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E209" s="2">
         <v>55</v>
@@ -12671,7 +12684,7 @@
         <v>6</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I209" s="2">
         <v>9</v>
@@ -12690,7 +12703,7 @@
         <v>2</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>4</v>
@@ -12731,7 +12744,7 @@
         <v>4</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
@@ -12762,7 +12775,7 @@
         <v>2</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I212" s="2">
         <v>8</v>
@@ -12793,7 +12806,7 @@
         <v>5</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I213" s="2">
         <v>13</v>
@@ -12827,7 +12840,7 @@
     </row>
     <row r="215" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="162" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B215" s="161"/>
       <c r="C215" s="161"/>
@@ -12892,7 +12905,7 @@
         <v>6</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I217" s="2">
         <v>7.5</v>
@@ -12923,7 +12936,7 @@
         <v>2</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I218" s="2">
         <v>10</v>
@@ -12954,7 +12967,7 @@
         <v>4</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I219" s="2"/>
       <c r="J219" s="2"/>
@@ -12973,7 +12986,7 @@
         <v>7</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E220" s="2">
         <v>37</v>
@@ -12985,7 +12998,7 @@
         <v>5</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I220" s="2">
         <v>6.5</v>
@@ -13004,7 +13017,7 @@
         <v>2</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>4</v>
@@ -13045,7 +13058,7 @@
         <v>5</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
@@ -13064,7 +13077,7 @@
         <v>7</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E223" s="2">
         <v>117</v>
@@ -13076,7 +13089,7 @@
         <v>6</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I223" s="2">
         <v>19</v>
@@ -13107,7 +13120,7 @@
         <v>2</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I224" s="2"/>
       <c r="J224" s="2">
@@ -13126,7 +13139,7 @@
         <v>11</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E225" s="2">
         <v>193</v>
@@ -13138,7 +13151,7 @@
         <v>6</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I225" s="2"/>
       <c r="J225" s="2">
@@ -13157,7 +13170,7 @@
         <v>7</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E226" s="2">
         <v>15</v>
@@ -13169,7 +13182,7 @@
         <v>4</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I226" s="2">
         <v>2.5</v>
@@ -13200,7 +13213,7 @@
         <v>4</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I227" s="2"/>
       <c r="J227" s="2"/>
@@ -13234,7 +13247,7 @@
     </row>
     <row r="229" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="162" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B229" s="161"/>
       <c r="C229" s="161"/>
@@ -13299,7 +13312,7 @@
         <v>7</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I231" s="2">
         <v>10.5</v>
@@ -13330,7 +13343,7 @@
         <v>2</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>240</v>
+        <v>955</v>
       </c>
       <c r="I232" s="2"/>
       <c r="J232" s="2">
@@ -13349,7 +13362,7 @@
         <v>11</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E233" s="2">
         <v>124</v>
@@ -13361,7 +13374,7 @@
         <v>6</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I233" s="2"/>
       <c r="J233" s="2">
@@ -13380,7 +13393,7 @@
         <v>7</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E234" s="2">
         <v>62</v>
@@ -13392,7 +13405,7 @@
         <v>4</v>
       </c>
       <c r="H234" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I234" s="2">
         <v>10</v>
@@ -13423,7 +13436,7 @@
         <v>7</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I235" s="2"/>
       <c r="J235" s="2"/>
@@ -13454,7 +13467,7 @@
         <v>2</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I236" s="2">
         <v>5</v>
@@ -13485,7 +13498,7 @@
         <v>5</v>
       </c>
       <c r="H237" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I237" s="2"/>
       <c r="J237" s="2">
@@ -13516,7 +13529,7 @@
         <v>5</v>
       </c>
       <c r="H238" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
@@ -13535,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E239" s="2">
         <v>117</v>
@@ -13547,7 +13560,7 @@
         <v>6</v>
       </c>
       <c r="H239" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I239" s="2">
         <v>19</v>
@@ -13578,7 +13591,7 @@
         <v>6</v>
       </c>
       <c r="H240" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I240" s="2"/>
       <c r="J240" s="2">
@@ -13597,7 +13610,7 @@
         <v>7</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E241" s="2">
         <v>15</v>
@@ -13609,7 +13622,7 @@
         <v>4</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I241" s="2">
         <v>2.5</v>
@@ -13628,7 +13641,7 @@
         <v>27</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E242" s="2">
         <v>69</v>
@@ -13640,7 +13653,7 @@
         <v>2</v>
       </c>
       <c r="H242" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
@@ -13673,8 +13686,8 @@
       </c>
     </row>
     <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="172" t="s">
-        <v>295</v>
+      <c r="A244" s="168" t="s">
+        <v>292</v>
       </c>
       <c r="B244" s="161"/>
       <c r="C244" s="161"/>
@@ -13727,7 +13740,7 @@
         <v>7</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E246" s="2">
         <v>65</v>
@@ -13739,7 +13752,7 @@
         <v>6</v>
       </c>
       <c r="H246" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I246" s="2">
         <v>11</v>
@@ -13770,7 +13783,7 @@
         <v>2</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>240</v>
+        <v>955</v>
       </c>
       <c r="I247" s="2"/>
       <c r="J247" s="2">
@@ -13789,7 +13802,7 @@
         <v>11</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E248" s="2">
         <v>131</v>
@@ -13801,7 +13814,7 @@
         <v>6</v>
       </c>
       <c r="H248" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I248" s="2"/>
       <c r="J248" s="2">
@@ -13820,7 +13833,7 @@
         <v>7</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E249" s="2">
         <v>65</v>
@@ -13832,7 +13845,7 @@
         <v>4</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I249" s="2">
         <v>10.5</v>
@@ -13863,7 +13876,7 @@
         <v>4</v>
       </c>
       <c r="H250" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I250" s="2"/>
       <c r="J250" s="2"/>
@@ -13894,7 +13907,7 @@
         <v>2</v>
       </c>
       <c r="H251" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I251" s="2">
         <v>5</v>
@@ -13925,7 +13938,7 @@
         <v>5</v>
       </c>
       <c r="H252" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I252" s="2"/>
       <c r="J252" s="2">
@@ -13956,7 +13969,7 @@
         <v>5</v>
       </c>
       <c r="H253" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I253" s="2"/>
       <c r="J253" s="2"/>
@@ -13975,7 +13988,7 @@
         <v>7</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E254" s="2">
         <v>123</v>
@@ -13987,7 +14000,7 @@
         <v>6</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I254" s="2">
         <v>20</v>
@@ -14006,7 +14019,7 @@
         <v>11</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E255" s="2">
         <v>279</v>
@@ -14018,7 +14031,7 @@
         <v>6</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I255" s="2"/>
       <c r="J255" s="2">
@@ -14037,7 +14050,7 @@
         <v>7</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E256" s="2">
         <v>20</v>
@@ -14049,7 +14062,7 @@
         <v>4</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I256" s="2">
         <v>3.5</v>
@@ -14068,7 +14081,7 @@
         <v>27</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E257" s="2">
         <v>70</v>
@@ -14080,7 +14093,7 @@
         <v>2</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I257" s="2"/>
       <c r="J257" s="2"/>
@@ -14114,7 +14127,7 @@
     </row>
     <row r="259" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="162" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B259" s="161"/>
       <c r="C259" s="161"/>
@@ -14167,7 +14180,7 @@
         <v>7</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E261" s="2">
         <v>70</v>
@@ -14179,7 +14192,7 @@
         <v>6</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I261" s="2">
         <v>12</v>
@@ -14210,7 +14223,7 @@
         <v>2</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>311</v>
+        <v>957</v>
       </c>
       <c r="I262" s="2"/>
       <c r="J262" s="2">
@@ -14229,7 +14242,7 @@
         <v>11</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E263" s="2">
         <v>137</v>
@@ -14241,7 +14254,7 @@
         <v>6</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I263" s="2"/>
       <c r="J263" s="2">
@@ -14260,7 +14273,7 @@
         <v>7</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E264" s="2">
         <v>71</v>
@@ -14272,7 +14285,7 @@
         <v>4</v>
       </c>
       <c r="H264" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I264" s="2">
         <v>11.5</v>
@@ -14303,7 +14316,7 @@
         <v>6</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I265" s="2"/>
       <c r="J265" s="2"/>
@@ -14334,7 +14347,7 @@
         <v>2</v>
       </c>
       <c r="H266" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I266" s="2">
         <v>5</v>
@@ -14365,7 +14378,7 @@
         <v>5</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I267" s="2"/>
       <c r="J267" s="2">
@@ -14396,7 +14409,7 @@
         <v>5</v>
       </c>
       <c r="H268" s="5" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I268" s="2"/>
       <c r="J268" s="2"/>
@@ -14415,7 +14428,7 @@
         <v>7</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E269" s="2">
         <v>130</v>
@@ -14427,7 +14440,7 @@
         <v>6</v>
       </c>
       <c r="H269" s="5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I269" s="2">
         <v>21</v>
@@ -14446,7 +14459,7 @@
         <v>11</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E270" s="2">
         <v>296</v>
@@ -14458,7 +14471,7 @@
         <v>6</v>
       </c>
       <c r="H270" s="5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I270" s="2"/>
       <c r="J270" s="2">
@@ -14477,7 +14490,7 @@
         <v>7</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E271" s="2">
         <v>20</v>
@@ -14489,7 +14502,7 @@
         <v>4</v>
       </c>
       <c r="H271" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I271" s="2">
         <v>3.5</v>
@@ -14508,7 +14521,7 @@
         <v>27</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E272" s="2">
         <v>71</v>
@@ -14520,7 +14533,7 @@
         <v>2</v>
       </c>
       <c r="H272" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I272" s="2"/>
       <c r="J272" s="2"/>
@@ -14553,8 +14566,8 @@
       </c>
     </row>
     <row r="274" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="164" t="s">
-        <v>323</v>
+      <c r="A274" s="166" t="s">
+        <v>319</v>
       </c>
       <c r="B274" s="161"/>
       <c r="C274" s="161"/>
@@ -14607,7 +14620,7 @@
         <v>7</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E276" s="2">
         <v>46</v>
@@ -14619,7 +14632,7 @@
         <v>6</v>
       </c>
       <c r="H276" s="5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I276" s="2">
         <v>8</v>
@@ -14650,7 +14663,7 @@
         <v>2</v>
       </c>
       <c r="H277" s="5" t="s">
-        <v>326</v>
+        <v>958</v>
       </c>
       <c r="I277" s="2"/>
       <c r="J277" s="2">
@@ -14669,7 +14682,7 @@
         <v>11</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E278" s="2">
         <v>90</v>
@@ -14681,7 +14694,7 @@
         <v>5</v>
       </c>
       <c r="H278" s="5" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I278" s="2"/>
       <c r="J278" s="2">
@@ -14712,7 +14725,7 @@
         <v>2</v>
       </c>
       <c r="H279" s="5" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I279" s="2">
         <v>7.5</v>
@@ -14731,7 +14744,7 @@
         <v>27</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E280" s="2">
         <v>76</v>
@@ -14743,7 +14756,7 @@
         <v>2</v>
       </c>
       <c r="H280" s="5" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I280" s="2"/>
       <c r="J280" s="2"/>
@@ -14774,7 +14787,7 @@
         <v>2</v>
       </c>
       <c r="H281" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I281" s="2">
         <v>4</v>
@@ -14805,7 +14818,7 @@
         <v>3</v>
       </c>
       <c r="H282" s="5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="I282" s="2"/>
       <c r="J282" s="2">
@@ -14836,7 +14849,7 @@
         <v>5</v>
       </c>
       <c r="H283" s="5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I283" s="2"/>
       <c r="J283" s="2"/>
@@ -14867,7 +14880,7 @@
         <v>6</v>
       </c>
       <c r="H284" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I284" s="2">
         <v>14</v>
@@ -14886,7 +14899,7 @@
         <v>11</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E285" s="2">
         <v>193</v>
@@ -14898,7 +14911,7 @@
         <v>4</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I285" s="2"/>
       <c r="J285" s="2">
@@ -14917,7 +14930,7 @@
         <v>7</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E286" s="2">
         <v>15</v>
@@ -14929,7 +14942,7 @@
         <v>4</v>
       </c>
       <c r="H286" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I286" s="2">
         <v>2.5</v>
@@ -14963,7 +14976,7 @@
     </row>
     <row r="288" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="162" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B288" s="161"/>
       <c r="C288" s="161"/>
@@ -15016,7 +15029,7 @@
         <v>7</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E290" s="2">
         <v>66</v>
@@ -15028,7 +15041,7 @@
         <v>7</v>
       </c>
       <c r="H290" s="5" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I290" s="2">
         <v>12.5</v>
@@ -15059,7 +15072,7 @@
         <v>2</v>
       </c>
       <c r="H291" s="5" t="s">
-        <v>311</v>
+        <v>957</v>
       </c>
       <c r="I291" s="2"/>
       <c r="J291" s="2">
@@ -15090,7 +15103,7 @@
         <v>9</v>
       </c>
       <c r="H292" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I292" s="2"/>
       <c r="J292" s="2">
@@ -15109,7 +15122,7 @@
         <v>7</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E293" s="2">
         <v>74</v>
@@ -15121,7 +15134,7 @@
         <v>4</v>
       </c>
       <c r="H293" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I293" s="2">
         <v>12</v>
@@ -15152,7 +15165,7 @@
         <v>4</v>
       </c>
       <c r="H294" s="5" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I294" s="2"/>
       <c r="J294" s="2"/>
@@ -15183,7 +15196,7 @@
         <v>2</v>
       </c>
       <c r="H295" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I295" s="2">
         <v>5</v>
@@ -15214,7 +15227,7 @@
         <v>5</v>
       </c>
       <c r="H296" s="5" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I296" s="2"/>
       <c r="J296" s="2">
@@ -15245,7 +15258,7 @@
         <v>5</v>
       </c>
       <c r="H297" s="5" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I297" s="2"/>
       <c r="J297" s="2"/>
@@ -15264,7 +15277,7 @@
         <v>7</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E298" s="2">
         <v>136</v>
@@ -15276,7 +15289,7 @@
         <v>6</v>
       </c>
       <c r="H298" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="I298" s="2">
         <v>22</v>
@@ -15295,7 +15308,7 @@
         <v>11</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E299" s="2">
         <v>300</v>
@@ -15307,7 +15320,7 @@
         <v>6</v>
       </c>
       <c r="H299" s="5" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I299" s="2"/>
       <c r="J299" s="2">
@@ -15326,7 +15339,7 @@
         <v>7</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E300" s="2">
         <v>20</v>
@@ -15338,7 +15351,7 @@
         <v>4</v>
       </c>
       <c r="H300" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I300" s="2">
         <v>3.5</v>
@@ -15357,7 +15370,7 @@
         <v>27</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E301" s="2">
         <v>71</v>
@@ -15369,7 +15382,7 @@
         <v>2</v>
       </c>
       <c r="H301" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
@@ -15403,7 +15416,7 @@
     </row>
     <row r="303" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="162" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B303" s="161"/>
       <c r="C303" s="161"/>
@@ -15456,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E305" s="2">
         <v>81</v>
@@ -15468,7 +15481,7 @@
         <v>7</v>
       </c>
       <c r="H305" s="5" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I305" s="2">
         <v>15.5</v>
@@ -15499,7 +15512,7 @@
         <v>2</v>
       </c>
       <c r="H306" s="5" t="s">
-        <v>350</v>
+        <v>959</v>
       </c>
       <c r="I306" s="2"/>
       <c r="J306" s="2">
@@ -15518,7 +15531,7 @@
         <v>27</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E307" s="2">
         <v>69</v>
@@ -15530,7 +15543,7 @@
         <v>4</v>
       </c>
       <c r="H307" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
@@ -15549,7 +15562,7 @@
         <v>11</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E308" s="2">
         <v>150</v>
@@ -15561,7 +15574,7 @@
         <v>8</v>
       </c>
       <c r="H308" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="I308" s="2"/>
       <c r="J308" s="2">
@@ -15580,7 +15593,7 @@
         <v>7</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E309" s="2">
         <v>89</v>
@@ -15592,7 +15605,7 @@
         <v>4</v>
       </c>
       <c r="H309" s="5" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="I309" s="2">
         <v>14.5</v>
@@ -15611,7 +15624,7 @@
         <v>27</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E310" s="2">
         <v>79</v>
@@ -15623,7 +15636,7 @@
         <v>2</v>
       </c>
       <c r="H310" s="5" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="I310" s="2"/>
       <c r="J310" s="2"/>
@@ -15654,7 +15667,7 @@
         <v>2</v>
       </c>
       <c r="H311" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I311" s="2">
         <v>5</v>
@@ -15685,7 +15698,7 @@
         <v>5</v>
       </c>
       <c r="H312" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I312" s="2"/>
       <c r="J312" s="2">
@@ -15704,7 +15717,7 @@
         <v>7</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E313" s="2">
         <v>142</v>
@@ -15716,7 +15729,7 @@
         <v>6</v>
       </c>
       <c r="H313" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="I313" s="2">
         <v>23</v>
@@ -15735,7 +15748,7 @@
         <v>11</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="E314" s="2">
         <v>311</v>
@@ -15747,7 +15760,7 @@
         <v>6</v>
       </c>
       <c r="H314" s="5" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="I314" s="2"/>
       <c r="J314" s="2">
@@ -15781,7 +15794,7 @@
     </row>
     <row r="316" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="170" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B316" s="161"/>
       <c r="C316" s="161"/>
@@ -15834,7 +15847,7 @@
         <v>7</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E318" s="2">
         <v>80</v>
@@ -15846,7 +15859,7 @@
         <v>6</v>
       </c>
       <c r="H318" s="5" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="I318" s="2">
         <v>14.5</v>
@@ -15877,7 +15890,7 @@
         <v>2</v>
       </c>
       <c r="H319" s="5" t="s">
-        <v>365</v>
+        <v>960</v>
       </c>
       <c r="I319" s="2"/>
       <c r="J319" s="2">
@@ -15896,7 +15909,7 @@
         <v>11</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="E320" s="2">
         <v>159</v>
@@ -15908,7 +15921,7 @@
         <v>6</v>
       </c>
       <c r="H320" s="5" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="I320" s="2"/>
       <c r="J320" s="2">
@@ -15927,7 +15940,7 @@
         <v>7</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E321" s="2">
         <v>83</v>
@@ -15939,7 +15952,7 @@
         <v>4</v>
       </c>
       <c r="H321" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="I321" s="2">
         <v>13.5</v>
@@ -15970,7 +15983,7 @@
         <v>6</v>
       </c>
       <c r="H322" s="5" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="I322" s="2"/>
       <c r="J322" s="2"/>
@@ -16001,7 +16014,7 @@
         <v>2</v>
       </c>
       <c r="H323" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I323" s="2">
         <v>5</v>
@@ -16032,7 +16045,7 @@
         <v>5</v>
       </c>
       <c r="H324" s="5" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="I324" s="2"/>
       <c r="J324" s="2">
@@ -16063,7 +16076,7 @@
         <v>5</v>
       </c>
       <c r="H325" s="5" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="I325" s="2"/>
       <c r="J325" s="2"/>
@@ -16082,7 +16095,7 @@
         <v>7</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="E326" s="2">
         <v>148</v>
@@ -16094,7 +16107,7 @@
         <v>6</v>
       </c>
       <c r="H326" s="5" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="I326" s="2">
         <v>24</v>
@@ -16113,7 +16126,7 @@
         <v>11</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E327" s="2">
         <v>321</v>
@@ -16125,7 +16138,7 @@
         <v>6</v>
       </c>
       <c r="H327" s="5" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="I327" s="2"/>
       <c r="J327" s="2">
@@ -16144,7 +16157,7 @@
         <v>7</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E328" s="2">
         <v>25</v>
@@ -16156,7 +16169,7 @@
         <v>4</v>
       </c>
       <c r="H328" s="5" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I328" s="2">
         <v>4.5</v>
@@ -16175,7 +16188,7 @@
         <v>27</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E329" s="2">
         <v>72</v>
@@ -16187,7 +16200,7 @@
         <v>2</v>
       </c>
       <c r="H329" s="5" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="I329" s="2"/>
       <c r="J329" s="2"/>
@@ -16220,8 +16233,8 @@
       </c>
     </row>
     <row r="331" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A331" s="169" t="s">
-        <v>379</v>
+      <c r="A331" s="167" t="s">
+        <v>372</v>
       </c>
       <c r="B331" s="161"/>
       <c r="C331" s="161"/>
@@ -16274,7 +16287,7 @@
         <v>7</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E333" s="2">
         <v>92</v>
@@ -16286,7 +16299,7 @@
         <v>7</v>
       </c>
       <c r="H333" s="5" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="I333" s="2">
         <v>16.5</v>
@@ -16317,7 +16330,7 @@
         <v>2</v>
       </c>
       <c r="H334" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I334" s="2"/>
       <c r="J334" s="2">
@@ -16336,7 +16349,7 @@
         <v>11</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="E335" s="2">
         <v>167</v>
@@ -16348,7 +16361,7 @@
         <v>6</v>
       </c>
       <c r="H335" s="5" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="I335" s="2"/>
       <c r="J335" s="2">
@@ -16367,7 +16380,7 @@
         <v>7</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E336" s="2">
         <v>92</v>
@@ -16379,7 +16392,7 @@
         <v>4</v>
       </c>
       <c r="H336" s="5" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="I336" s="2">
         <v>15</v>
@@ -16410,7 +16423,7 @@
         <v>4</v>
       </c>
       <c r="H337" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="I337" s="2"/>
       <c r="J337" s="2"/>
@@ -16441,7 +16454,7 @@
         <v>2</v>
       </c>
       <c r="H338" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I338" s="2">
         <v>5</v>
@@ -16472,7 +16485,7 @@
         <v>5</v>
       </c>
       <c r="H339" s="5" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="I339" s="2"/>
       <c r="J339" s="2">
@@ -16503,7 +16516,7 @@
         <v>5</v>
       </c>
       <c r="H340" s="5" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="I340" s="2"/>
       <c r="J340" s="2"/>
@@ -16522,7 +16535,7 @@
         <v>7</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="E341" s="2">
         <v>154</v>
@@ -16534,7 +16547,7 @@
         <v>6</v>
       </c>
       <c r="H341" s="5" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="I341" s="2">
         <v>25</v>
@@ -16553,7 +16566,7 @@
         <v>11</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="E342" s="2">
         <v>332</v>
@@ -16565,7 +16578,7 @@
         <v>6</v>
       </c>
       <c r="H342" s="5" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="I342" s="2"/>
       <c r="J342" s="2">
@@ -16584,7 +16597,7 @@
         <v>7</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E343" s="2">
         <v>25</v>
@@ -16596,7 +16609,7 @@
         <v>4</v>
       </c>
       <c r="H343" s="5" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I343" s="2">
         <v>4.5</v>
@@ -16615,7 +16628,7 @@
         <v>27</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E344" s="2">
         <v>73</v>
@@ -16627,7 +16640,7 @@
         <v>2</v>
       </c>
       <c r="H344" s="5" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="I344" s="2"/>
       <c r="J344" s="2"/>
@@ -16661,7 +16674,7 @@
     </row>
     <row r="346" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="162" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B346" s="161"/>
       <c r="C346" s="161"/>
@@ -16685,7 +16698,7 @@
         <v>2</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>4</v>
@@ -16697,7 +16710,7 @@
         <v>1</v>
       </c>
       <c r="H347" s="5" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="I347" s="2"/>
       <c r="J347" s="2"/>
@@ -16711,22 +16724,22 @@
         <v>6</v>
       </c>
       <c r="C348" s="13" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E348" s="2">
         <v>360</v>
       </c>
       <c r="F348" s="4" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G348" s="2">
         <v>5</v>
       </c>
       <c r="H348" s="5" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I348" s="2"/>
       <c r="J348" s="2"/>
@@ -16740,22 +16753,22 @@
         <v>14</v>
       </c>
       <c r="C349" s="13" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E349" s="2">
         <v>360</v>
       </c>
       <c r="F349" s="4" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G349" s="2">
         <v>5</v>
       </c>
       <c r="H349" s="5" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I349" s="2"/>
       <c r="J349" s="2"/>
@@ -16769,22 +16782,22 @@
         <v>17</v>
       </c>
       <c r="C350" s="13" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E350" s="2">
         <v>360</v>
       </c>
       <c r="F350" s="4" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G350" s="2">
         <v>5</v>
       </c>
       <c r="H350" s="5" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I350" s="2"/>
       <c r="J350" s="2"/>
@@ -16798,22 +16811,22 @@
         <v>21</v>
       </c>
       <c r="C351" s="13" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E351" s="2">
         <v>360</v>
       </c>
       <c r="F351" s="4" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G351" s="2">
         <v>5</v>
       </c>
       <c r="H351" s="5" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I351" s="2"/>
       <c r="J351" s="2"/>
@@ -16827,22 +16840,22 @@
         <v>26</v>
       </c>
       <c r="C352" s="13" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E352" s="2">
         <v>360</v>
       </c>
       <c r="F352" s="4" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G352" s="2">
         <v>5</v>
       </c>
       <c r="H352" s="5" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I352" s="2"/>
       <c r="J352" s="2"/>
@@ -16859,7 +16872,7 @@
         <v>2</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>4</v>
@@ -16871,7 +16884,7 @@
         <v>1</v>
       </c>
       <c r="H353" s="5" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="I353" s="2"/>
       <c r="J353" s="2"/>
@@ -16903,7 +16916,7 @@
     </row>
     <row r="355" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="162" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B355" s="161"/>
       <c r="C355" s="161"/>
@@ -16956,7 +16969,7 @@
         <v>7</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="E357" s="2">
         <v>54</v>
@@ -16968,7 +16981,7 @@
         <v>5</v>
       </c>
       <c r="H357" s="5" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="I357" s="2">
         <v>9.5</v>
@@ -16999,7 +17012,7 @@
         <v>2</v>
       </c>
       <c r="H358" s="5" t="s">
-        <v>240</v>
+        <v>955</v>
       </c>
       <c r="I358" s="2"/>
       <c r="J358" s="2">
@@ -17018,7 +17031,7 @@
         <v>11</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E359" s="2">
         <v>120</v>
@@ -17030,7 +17043,7 @@
         <v>3</v>
       </c>
       <c r="H359" s="5" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="I359" s="2"/>
       <c r="J359" s="2">
@@ -17049,7 +17062,7 @@
         <v>7</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E360" s="2">
         <v>68</v>
@@ -17061,7 +17074,7 @@
         <v>4</v>
       </c>
       <c r="H360" s="5" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="I360" s="2">
         <v>11</v>
@@ -17092,7 +17105,7 @@
         <v>4</v>
       </c>
       <c r="H361" s="5" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="I361" s="2"/>
       <c r="J361" s="2"/>
@@ -17123,7 +17136,7 @@
         <v>2</v>
       </c>
       <c r="H362" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I362" s="2">
         <v>5</v>
@@ -17142,7 +17155,7 @@
         <v>11</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E363" s="2">
         <v>96</v>
@@ -17154,7 +17167,7 @@
         <v>2</v>
       </c>
       <c r="H363" s="5" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="I363" s="2"/>
       <c r="J363" s="2">
@@ -17185,7 +17198,7 @@
         <v>5</v>
       </c>
       <c r="H364" s="5" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="I364" s="2"/>
       <c r="J364" s="2"/>
@@ -17204,7 +17217,7 @@
         <v>7</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E365" s="2">
         <v>111</v>
@@ -17216,7 +17229,7 @@
         <v>6</v>
       </c>
       <c r="H365" s="5" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="I365" s="2">
         <v>18</v>
@@ -17247,7 +17260,7 @@
         <v>6</v>
       </c>
       <c r="H366" s="5" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="I366" s="2"/>
       <c r="J366" s="2">
@@ -17266,7 +17279,7 @@
         <v>7</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E367" s="2">
         <v>15</v>
@@ -17278,7 +17291,7 @@
         <v>4</v>
       </c>
       <c r="H367" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I367" s="2">
         <v>2.5</v>
@@ -17297,7 +17310,7 @@
         <v>27</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E368" s="2">
         <v>52</v>
@@ -17309,7 +17322,7 @@
         <v>2</v>
       </c>
       <c r="H368" s="5" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="I368" s="2"/>
       <c r="J368" s="2"/>
@@ -17343,7 +17356,7 @@
     </row>
     <row r="370" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="162" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B370" s="161"/>
       <c r="C370" s="161"/>
@@ -17396,7 +17409,7 @@
         <v>7</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E372" s="2">
         <v>80</v>
@@ -17408,7 +17421,7 @@
         <v>6</v>
       </c>
       <c r="H372" s="5" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="I372" s="2">
         <v>14.5</v>
@@ -17439,7 +17452,7 @@
         <v>2</v>
       </c>
       <c r="H373" s="5" t="s">
-        <v>350</v>
+        <v>959</v>
       </c>
       <c r="I373" s="2"/>
       <c r="J373" s="2">
@@ -17458,7 +17471,7 @@
         <v>11</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E374" s="2">
         <v>141</v>
@@ -17470,7 +17483,7 @@
         <v>6</v>
       </c>
       <c r="H374" s="5" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="I374" s="2"/>
       <c r="J374" s="2">
@@ -17489,7 +17502,7 @@
         <v>7</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E375" s="2">
         <v>74</v>
@@ -17501,7 +17514,7 @@
         <v>4</v>
       </c>
       <c r="H375" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I375" s="2">
         <v>12</v>
@@ -17532,7 +17545,7 @@
         <v>7</v>
       </c>
       <c r="H376" s="5" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="I376" s="2"/>
       <c r="J376" s="2"/>
@@ -17563,7 +17576,7 @@
         <v>2</v>
       </c>
       <c r="H377" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I377" s="2">
         <v>6</v>
@@ -17594,7 +17607,7 @@
         <v>5</v>
       </c>
       <c r="H378" s="5" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="I378" s="2"/>
       <c r="J378" s="2">
@@ -17625,7 +17638,7 @@
         <v>5</v>
       </c>
       <c r="H379" s="5" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="I379" s="2"/>
       <c r="J379" s="2"/>
@@ -17644,7 +17657,7 @@
         <v>7</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E380" s="2">
         <v>135</v>
@@ -17656,7 +17669,7 @@
         <v>7</v>
       </c>
       <c r="H380" s="5" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="I380" s="2">
         <v>22</v>
@@ -17675,7 +17688,7 @@
         <v>11</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E381" s="2">
         <v>300</v>
@@ -17687,7 +17700,7 @@
         <v>6</v>
       </c>
       <c r="H381" s="5" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="I381" s="2"/>
       <c r="J381" s="2">
@@ -17706,7 +17719,7 @@
         <v>7</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E382" s="2">
         <v>20</v>
@@ -17718,7 +17731,7 @@
         <v>4</v>
       </c>
       <c r="H382" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I382" s="2">
         <v>3.5</v>
@@ -17737,7 +17750,7 @@
         <v>27</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E383" s="2">
         <v>65</v>
@@ -17749,7 +17762,7 @@
         <v>2</v>
       </c>
       <c r="H383" s="5" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="I383" s="2"/>
       <c r="J383" s="2"/>
@@ -17782,8 +17795,8 @@
       </c>
     </row>
     <row r="385" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="164" t="s">
-        <v>425</v>
+      <c r="A385" s="166" t="s">
+        <v>418</v>
       </c>
       <c r="B385" s="161"/>
       <c r="C385" s="161"/>
@@ -17836,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="E387" s="2">
         <v>60</v>
@@ -17848,7 +17861,7 @@
         <v>6</v>
       </c>
       <c r="H387" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="I387" s="2">
         <v>10.5</v>
@@ -17879,7 +17892,7 @@
         <v>2</v>
       </c>
       <c r="H388" s="5" t="s">
-        <v>185</v>
+        <v>953</v>
       </c>
       <c r="I388" s="2"/>
       <c r="J388" s="2">
@@ -17898,7 +17911,7 @@
         <v>11</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E389" s="2">
         <v>107</v>
@@ -17910,7 +17923,7 @@
         <v>5</v>
       </c>
       <c r="H389" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="I389" s="2"/>
       <c r="J389" s="2">
@@ -17941,7 +17954,7 @@
         <v>2</v>
       </c>
       <c r="H390" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="I390" s="2">
         <v>10.5</v>
@@ -17972,7 +17985,7 @@
         <v>4</v>
       </c>
       <c r="H391" s="5" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="I391" s="2"/>
       <c r="J391" s="2"/>
@@ -18003,7 +18016,7 @@
         <v>2</v>
       </c>
       <c r="H392" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I392" s="2">
         <v>5</v>
@@ -18034,7 +18047,7 @@
         <v>3</v>
       </c>
       <c r="H393" s="5" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="I393" s="2"/>
       <c r="J393" s="2">
@@ -18065,7 +18078,7 @@
         <v>5</v>
       </c>
       <c r="H394" s="5" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="I394" s="2"/>
       <c r="J394" s="2"/>
@@ -18084,7 +18097,7 @@
         <v>7</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E395" s="2">
         <v>111</v>
@@ -18096,7 +18109,7 @@
         <v>6</v>
       </c>
       <c r="H395" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="I395" s="2">
         <v>18</v>
@@ -18127,7 +18140,7 @@
         <v>4</v>
       </c>
       <c r="H396" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="I396" s="2"/>
       <c r="J396" s="2">
@@ -18146,7 +18159,7 @@
         <v>27</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E397" s="2">
         <v>53</v>
@@ -18158,7 +18171,7 @@
         <v>2</v>
       </c>
       <c r="H397" s="5" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="I397" s="2"/>
       <c r="J397" s="2"/>
@@ -18192,7 +18205,7 @@
     </row>
     <row r="399" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="162" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="B399" s="161"/>
       <c r="C399" s="161"/>
@@ -18245,7 +18258,7 @@
         <v>7</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E401" s="2">
         <v>78</v>
@@ -18257,7 +18270,7 @@
         <v>7</v>
       </c>
       <c r="H401" s="5" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="I401" s="2">
         <v>15</v>
@@ -18288,7 +18301,7 @@
         <v>2</v>
       </c>
       <c r="H402" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I402" s="2"/>
       <c r="J402" s="2">
@@ -18307,7 +18320,7 @@
         <v>11</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="E403" s="2">
         <v>156</v>
@@ -18319,7 +18332,7 @@
         <v>6</v>
       </c>
       <c r="H403" s="5" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="I403" s="2"/>
       <c r="J403" s="2">
@@ -18338,7 +18351,7 @@
         <v>7</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E404" s="2">
         <v>77</v>
@@ -18350,7 +18363,7 @@
         <v>4</v>
       </c>
       <c r="H404" s="5" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="I404" s="2">
         <v>12.5</v>
@@ -18381,7 +18394,7 @@
         <v>6</v>
       </c>
       <c r="H405" s="5" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="I405" s="2"/>
       <c r="J405" s="2"/>
@@ -18412,7 +18425,7 @@
         <v>2</v>
       </c>
       <c r="H406" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I406" s="2">
         <v>6</v>
@@ -18443,7 +18456,7 @@
         <v>5</v>
       </c>
       <c r="H407" s="5" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="I407" s="2"/>
       <c r="J407" s="2">
@@ -18474,7 +18487,7 @@
         <v>5</v>
       </c>
       <c r="H408" s="5" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="I408" s="2"/>
       <c r="J408" s="2"/>
@@ -18493,7 +18506,7 @@
         <v>7</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="E409" s="2">
         <v>148</v>
@@ -18505,7 +18518,7 @@
         <v>7</v>
       </c>
       <c r="H409" s="5" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="I409" s="2">
         <v>24</v>
@@ -18524,7 +18537,7 @@
         <v>11</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E410" s="2">
         <v>321</v>
@@ -18536,7 +18549,7 @@
         <v>6</v>
       </c>
       <c r="H410" s="5" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="I410" s="2"/>
       <c r="J410" s="2">
@@ -18555,7 +18568,7 @@
         <v>7</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E411" s="2">
         <v>25</v>
@@ -18567,7 +18580,7 @@
         <v>4</v>
       </c>
       <c r="H411" s="5" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I411" s="2">
         <v>4.5</v>
@@ -18586,7 +18599,7 @@
         <v>27</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E412" s="2">
         <v>64</v>
@@ -18598,7 +18611,7 @@
         <v>2</v>
       </c>
       <c r="H412" s="5" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="I412" s="2"/>
       <c r="J412" s="2"/>
@@ -18632,7 +18645,7 @@
     </row>
     <row r="414" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="162" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B414" s="161"/>
       <c r="C414" s="161"/>
@@ -18685,7 +18698,7 @@
         <v>7</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E416" s="2">
         <v>80</v>
@@ -18697,7 +18710,7 @@
         <v>6</v>
       </c>
       <c r="H416" s="5" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="I416" s="2">
         <v>14</v>
@@ -18728,7 +18741,7 @@
         <v>2</v>
       </c>
       <c r="H417" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I417" s="2"/>
       <c r="J417" s="2">
@@ -18747,7 +18760,7 @@
         <v>11</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E418" s="2">
         <v>171</v>
@@ -18759,7 +18772,7 @@
         <v>6</v>
       </c>
       <c r="H418" s="5" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="I418" s="2"/>
       <c r="J418" s="2">
@@ -18778,7 +18791,7 @@
         <v>7</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E419" s="2">
         <v>92</v>
@@ -18790,7 +18803,7 @@
         <v>4</v>
       </c>
       <c r="H419" s="5" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="I419" s="2">
         <v>15</v>
@@ -18821,7 +18834,7 @@
         <v>4</v>
       </c>
       <c r="H420" s="5" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="I420" s="2"/>
       <c r="J420" s="2"/>
@@ -18852,7 +18865,7 @@
         <v>2</v>
       </c>
       <c r="H421" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I421" s="2">
         <v>6</v>
@@ -18883,7 +18896,7 @@
         <v>5</v>
       </c>
       <c r="H422" s="5" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="I422" s="2"/>
       <c r="J422" s="2">
@@ -18914,7 +18927,7 @@
         <v>5</v>
       </c>
       <c r="H423" s="5" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="I423" s="2"/>
       <c r="J423" s="2"/>
@@ -18933,7 +18946,7 @@
         <v>7</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E424" s="2">
         <v>160</v>
@@ -18945,7 +18958,7 @@
         <v>7</v>
       </c>
       <c r="H424" s="5" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="I424" s="2">
         <v>26</v>
@@ -18964,7 +18977,7 @@
         <v>11</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="E425" s="2">
         <v>343</v>
@@ -18976,7 +18989,7 @@
         <v>6</v>
       </c>
       <c r="H425" s="5" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="I425" s="2"/>
       <c r="J425" s="2">
@@ -18995,7 +19008,7 @@
         <v>7</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="E426" s="2">
         <v>30</v>
@@ -19007,7 +19020,7 @@
         <v>4</v>
       </c>
       <c r="H426" s="5" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="I426" s="2">
         <v>5</v>
@@ -19026,7 +19039,7 @@
         <v>27</v>
       </c>
       <c r="D427" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E427" s="2">
         <v>75</v>
@@ -19038,7 +19051,7 @@
         <v>2</v>
       </c>
       <c r="H427" s="5" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="I427" s="2"/>
       <c r="J427" s="2"/>
@@ -19072,7 +19085,7 @@
     </row>
     <row r="429" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="162" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B429" s="161"/>
       <c r="C429" s="161"/>
@@ -19125,7 +19138,7 @@
         <v>7</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E431" s="2">
         <v>80</v>
@@ -19137,7 +19150,7 @@
         <v>6</v>
       </c>
       <c r="H431" s="5" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="I431" s="2">
         <v>14</v>
@@ -19168,7 +19181,7 @@
         <v>2</v>
       </c>
       <c r="H432" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I432" s="2"/>
       <c r="J432" s="2">
@@ -19187,7 +19200,7 @@
         <v>11</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E433" s="2">
         <v>180</v>
@@ -19199,7 +19212,7 @@
         <v>6</v>
       </c>
       <c r="H433" s="5" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="I433" s="2"/>
       <c r="J433" s="2">
@@ -19218,7 +19231,7 @@
         <v>7</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E434" s="2">
         <v>98</v>
@@ -19230,7 +19243,7 @@
         <v>4</v>
       </c>
       <c r="H434" s="5" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="I434" s="2">
         <v>16</v>
@@ -19261,7 +19274,7 @@
         <v>4</v>
       </c>
       <c r="H435" s="5" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="I435" s="2"/>
       <c r="J435" s="2"/>
@@ -19292,7 +19305,7 @@
         <v>2</v>
       </c>
       <c r="H436" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I436" s="2">
         <v>6</v>
@@ -19323,7 +19336,7 @@
         <v>5</v>
       </c>
       <c r="H437" s="5" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="I437" s="2"/>
       <c r="J437" s="2">
@@ -19354,7 +19367,7 @@
         <v>5</v>
       </c>
       <c r="H438" s="5" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="I438" s="2"/>
       <c r="J438" s="2"/>
@@ -19373,7 +19386,7 @@
         <v>7</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="E439" s="2">
         <v>172</v>
@@ -19385,7 +19398,7 @@
         <v>6</v>
       </c>
       <c r="H439" s="5" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="I439" s="2">
         <v>28</v>
@@ -19404,7 +19417,7 @@
         <v>11</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="E440" s="2">
         <v>364</v>
@@ -19416,7 +19429,7 @@
         <v>6</v>
       </c>
       <c r="H440" s="5" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="I440" s="2"/>
       <c r="J440" s="2">
@@ -19435,7 +19448,7 @@
         <v>7</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="E441" s="2">
         <v>35</v>
@@ -19447,7 +19460,7 @@
         <v>4</v>
       </c>
       <c r="H441" s="5" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="I441" s="2">
         <v>6</v>
@@ -19466,7 +19479,7 @@
         <v>27</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E442" s="2">
         <v>81</v>
@@ -19478,7 +19491,7 @@
         <v>2</v>
       </c>
       <c r="H442" s="5" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="I442" s="2"/>
       <c r="J442" s="2"/>
@@ -19511,8 +19524,8 @@
       </c>
     </row>
     <row r="444" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A444" s="163" t="s">
-        <v>471</v>
+      <c r="A444" s="172" t="s">
+        <v>464</v>
       </c>
       <c r="B444" s="161"/>
       <c r="C444" s="161"/>
@@ -19565,7 +19578,7 @@
         <v>7</v>
       </c>
       <c r="D446" s="4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E446" s="2">
         <v>69</v>
@@ -19577,7 +19590,7 @@
         <v>7</v>
       </c>
       <c r="H446" s="5" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="I446" s="2">
         <v>13</v>
@@ -19608,7 +19621,7 @@
         <v>2</v>
       </c>
       <c r="H447" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I447" s="2"/>
       <c r="J447" s="2">
@@ -19627,7 +19640,7 @@
         <v>11</v>
       </c>
       <c r="D448" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E448" s="2">
         <v>132</v>
@@ -19639,7 +19652,7 @@
         <v>6</v>
       </c>
       <c r="H448" s="5" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="I448" s="2"/>
       <c r="J448" s="2">
@@ -19658,7 +19671,7 @@
         <v>27</v>
       </c>
       <c r="D449" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E449" s="2">
         <v>84</v>
@@ -19670,7 +19683,7 @@
         <v>2</v>
       </c>
       <c r="H449" s="5" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="I449" s="2"/>
       <c r="J449" s="2"/>
@@ -19701,7 +19714,7 @@
         <v>2</v>
       </c>
       <c r="H450" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="I450" s="2">
         <v>10.5</v>
@@ -19732,7 +19745,7 @@
         <v>2</v>
       </c>
       <c r="H451" s="5" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="I451" s="2">
         <v>3</v>
@@ -19763,7 +19776,7 @@
         <v>3</v>
       </c>
       <c r="H452" s="5" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I452" s="2"/>
       <c r="J452" s="2">
@@ -19782,7 +19795,7 @@
         <v>27</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="E453" s="2">
         <v>44</v>
@@ -19794,7 +19807,7 @@
         <v>3</v>
       </c>
       <c r="H453" s="5" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="I453" s="2"/>
       <c r="J453" s="2"/>
@@ -19813,7 +19826,7 @@
         <v>7</v>
       </c>
       <c r="D454" s="4" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E454" s="2">
         <v>15</v>
@@ -19825,7 +19838,7 @@
         <v>2</v>
       </c>
       <c r="H454" s="5" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="I454" s="2">
         <v>2.5</v>
@@ -19844,7 +19857,7 @@
         <v>11</v>
       </c>
       <c r="D455" s="4" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E455" s="2">
         <v>15</v>
@@ -19856,7 +19869,7 @@
         <v>2</v>
       </c>
       <c r="H455" s="5" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="I455" s="2"/>
       <c r="J455" s="2">
@@ -19875,7 +19888,7 @@
         <v>7</v>
       </c>
       <c r="D456" s="12" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="E456" s="12" t="s">
         <v>4</v>
@@ -19887,7 +19900,7 @@
         <v>3</v>
       </c>
       <c r="H456" s="15" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="I456" s="12">
         <v>21</v>
@@ -19924,19 +19937,19 @@
       </c>
     </row>
     <row r="458" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A458" s="165" t="s">
-        <v>485</v>
-      </c>
-      <c r="B458" s="166"/>
-      <c r="C458" s="166"/>
-      <c r="D458" s="166"/>
-      <c r="E458" s="166"/>
-      <c r="F458" s="166"/>
-      <c r="G458" s="166"/>
-      <c r="H458" s="166"/>
-      <c r="I458" s="166"/>
-      <c r="J458" s="166"/>
-      <c r="K458" s="167"/>
+      <c r="A458" s="163" t="s">
+        <v>478</v>
+      </c>
+      <c r="B458" s="164"/>
+      <c r="C458" s="164"/>
+      <c r="D458" s="164"/>
+      <c r="E458" s="164"/>
+      <c r="F458" s="164"/>
+      <c r="G458" s="164"/>
+      <c r="H458" s="164"/>
+      <c r="I458" s="164"/>
+      <c r="J458" s="164"/>
+      <c r="K458" s="165"/>
     </row>
     <row r="459" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
@@ -19961,7 +19974,7 @@
         <v>1</v>
       </c>
       <c r="H459" s="5" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="I459" s="2"/>
       <c r="J459" s="2"/>
@@ -19978,19 +19991,19 @@
         <v>7</v>
       </c>
       <c r="D460" s="4" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="E460" s="2">
         <v>30</v>
       </c>
       <c r="F460" s="4" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="G460" s="2">
         <v>2</v>
       </c>
       <c r="H460" s="5" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="I460" s="2">
         <v>5</v>
@@ -20021,7 +20034,7 @@
         <v>2</v>
       </c>
       <c r="H461" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I461" s="2"/>
       <c r="J461" s="2">
@@ -20040,7 +20053,7 @@
         <v>11</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E462" s="2">
         <v>118</v>
@@ -20052,7 +20065,7 @@
         <v>2</v>
       </c>
       <c r="H462" s="5" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="I462" s="2"/>
       <c r="J462" s="2">
@@ -20083,7 +20096,7 @@
         <v>4</v>
       </c>
       <c r="H463" s="5" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="I463" s="2"/>
       <c r="J463" s="2"/>
@@ -20114,7 +20127,7 @@
         <v>2</v>
       </c>
       <c r="H464" s="5" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="I464" s="2">
         <v>13</v>
@@ -20145,7 +20158,7 @@
         <v>2</v>
       </c>
       <c r="H465" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I465" s="2">
         <v>5</v>
@@ -20164,7 +20177,7 @@
         <v>11</v>
       </c>
       <c r="D466" s="4" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="E466" s="2">
         <v>75</v>
@@ -20176,7 +20189,7 @@
         <v>2</v>
       </c>
       <c r="H466" s="5" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="I466" s="2"/>
       <c r="J466" s="2">
@@ -20207,7 +20220,7 @@
         <v>3</v>
       </c>
       <c r="H467" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I467" s="2"/>
       <c r="J467" s="2"/>
@@ -20226,7 +20239,7 @@
         <v>11</v>
       </c>
       <c r="D468" s="4" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E468" s="2">
         <v>214</v>
@@ -20238,7 +20251,7 @@
         <v>2</v>
       </c>
       <c r="H468" s="5" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="I468" s="2"/>
       <c r="J468" s="2">
@@ -20257,7 +20270,7 @@
         <v>7</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E469" s="2">
         <v>92</v>
@@ -20269,7 +20282,7 @@
         <v>5</v>
       </c>
       <c r="H469" s="5" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="I469" s="2">
         <v>15</v>
@@ -20288,7 +20301,7 @@
         <v>27</v>
       </c>
       <c r="D470" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E470" s="2">
         <v>54</v>
@@ -20300,7 +20313,7 @@
         <v>2</v>
       </c>
       <c r="H470" s="5" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="I470" s="2"/>
       <c r="J470" s="2"/>
@@ -20333,19 +20346,19 @@
       </c>
     </row>
     <row r="472" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A472" s="165" t="s">
-        <v>500</v>
-      </c>
-      <c r="B472" s="166"/>
-      <c r="C472" s="166"/>
-      <c r="D472" s="166"/>
-      <c r="E472" s="166"/>
-      <c r="F472" s="166"/>
-      <c r="G472" s="166"/>
-      <c r="H472" s="166"/>
-      <c r="I472" s="166"/>
-      <c r="J472" s="166"/>
-      <c r="K472" s="167"/>
+      <c r="A472" s="163" t="s">
+        <v>493</v>
+      </c>
+      <c r="B472" s="164"/>
+      <c r="C472" s="164"/>
+      <c r="D472" s="164"/>
+      <c r="E472" s="164"/>
+      <c r="F472" s="164"/>
+      <c r="G472" s="164"/>
+      <c r="H472" s="164"/>
+      <c r="I472" s="164"/>
+      <c r="J472" s="164"/>
+      <c r="K472" s="165"/>
     </row>
     <row r="473" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
@@ -20387,7 +20400,7 @@
         <v>7</v>
       </c>
       <c r="D474" s="4" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="E474" s="2">
         <v>66</v>
@@ -20399,7 +20412,7 @@
         <v>5</v>
       </c>
       <c r="H474" s="5" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="I474" s="2">
         <v>11.5</v>
@@ -20430,7 +20443,7 @@
         <v>2</v>
       </c>
       <c r="H475" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I475" s="2"/>
       <c r="J475" s="2">
@@ -20449,7 +20462,7 @@
         <v>11</v>
       </c>
       <c r="D476" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E476" s="2">
         <v>150</v>
@@ -20461,7 +20474,7 @@
         <v>5</v>
       </c>
       <c r="H476" s="5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="I476" s="2"/>
       <c r="J476" s="2">
@@ -20480,7 +20493,7 @@
         <v>7</v>
       </c>
       <c r="D477" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E477" s="2">
         <v>92</v>
@@ -20492,7 +20505,7 @@
         <v>4</v>
       </c>
       <c r="H477" s="5" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="I477" s="2">
         <v>15</v>
@@ -20523,7 +20536,7 @@
         <v>4</v>
       </c>
       <c r="H478" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="I478" s="2"/>
       <c r="J478" s="2"/>
@@ -20554,7 +20567,7 @@
         <v>2</v>
       </c>
       <c r="H479" s="5" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="I479" s="2">
         <v>7</v>
@@ -20585,7 +20598,7 @@
         <v>5</v>
       </c>
       <c r="H480" s="5" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="I480" s="2"/>
       <c r="J480" s="2">
@@ -20616,7 +20629,7 @@
         <v>5</v>
       </c>
       <c r="H481" s="5" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="I481" s="2"/>
       <c r="J481" s="2"/>
@@ -20635,7 +20648,7 @@
         <v>7</v>
       </c>
       <c r="D482" s="4" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E482" s="2">
         <v>142</v>
@@ -20647,7 +20660,7 @@
         <v>6</v>
       </c>
       <c r="H482" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="I482" s="2">
         <v>23</v>
@@ -20666,7 +20679,7 @@
         <v>11</v>
       </c>
       <c r="D483" s="4" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="E483" s="2">
         <v>321</v>
@@ -20678,7 +20691,7 @@
         <v>6</v>
       </c>
       <c r="H483" s="5" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="I483" s="2"/>
       <c r="J483" s="2">
@@ -20697,7 +20710,7 @@
         <v>7</v>
       </c>
       <c r="D484" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E484" s="2">
         <v>25</v>
@@ -20709,7 +20722,7 @@
         <v>4</v>
       </c>
       <c r="H484" s="5" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I484" s="2">
         <v>4.5</v>
@@ -20728,7 +20741,7 @@
         <v>27</v>
       </c>
       <c r="D485" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E485" s="2">
         <v>78</v>
@@ -20740,7 +20753,7 @@
         <v>2</v>
       </c>
       <c r="H485" s="5" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="I485" s="2"/>
       <c r="J485" s="2"/>
@@ -20773,19 +20786,19 @@
       </c>
     </row>
     <row r="487" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A487" s="165" t="s">
-        <v>510</v>
-      </c>
-      <c r="B487" s="166"/>
-      <c r="C487" s="166"/>
-      <c r="D487" s="166"/>
-      <c r="E487" s="166"/>
-      <c r="F487" s="166"/>
-      <c r="G487" s="166"/>
-      <c r="H487" s="166"/>
-      <c r="I487" s="166"/>
-      <c r="J487" s="166"/>
-      <c r="K487" s="167"/>
+      <c r="A487" s="163" t="s">
+        <v>503</v>
+      </c>
+      <c r="B487" s="164"/>
+      <c r="C487" s="164"/>
+      <c r="D487" s="164"/>
+      <c r="E487" s="164"/>
+      <c r="F487" s="164"/>
+      <c r="G487" s="164"/>
+      <c r="H487" s="164"/>
+      <c r="I487" s="164"/>
+      <c r="J487" s="164"/>
+      <c r="K487" s="165"/>
     </row>
     <row r="488" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
@@ -20827,7 +20840,7 @@
         <v>7</v>
       </c>
       <c r="D489" s="4" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E489" s="2">
         <v>82</v>
@@ -20839,7 +20852,7 @@
         <v>7</v>
       </c>
       <c r="H489" s="5" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="I489" s="2">
         <v>14</v>
@@ -20870,7 +20883,7 @@
         <v>2</v>
       </c>
       <c r="H490" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I490" s="2"/>
       <c r="J490" s="2">
@@ -20889,7 +20902,7 @@
         <v>11</v>
       </c>
       <c r="D491" s="4" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="E491" s="2">
         <v>154</v>
@@ -20901,7 +20914,7 @@
         <v>6</v>
       </c>
       <c r="H491" s="5" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="I491" s="2"/>
       <c r="J491" s="2">
@@ -20920,7 +20933,7 @@
         <v>7</v>
       </c>
       <c r="D492" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E492" s="2">
         <v>86</v>
@@ -20932,7 +20945,7 @@
         <v>4</v>
       </c>
       <c r="H492" s="5" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="I492" s="2">
         <v>14</v>
@@ -20963,7 +20976,7 @@
         <v>4</v>
       </c>
       <c r="H493" s="5" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="I493" s="2"/>
       <c r="J493" s="2"/>
@@ -20994,7 +21007,7 @@
         <v>2</v>
       </c>
       <c r="H494" s="5" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I494" s="2">
         <v>6.5</v>
@@ -21025,7 +21038,7 @@
         <v>5</v>
       </c>
       <c r="H495" s="5" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="I495" s="2"/>
       <c r="J495" s="2">
@@ -21056,7 +21069,7 @@
         <v>5</v>
       </c>
       <c r="H496" s="5" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="I496" s="2"/>
       <c r="J496" s="2"/>
@@ -21075,7 +21088,7 @@
         <v>7</v>
       </c>
       <c r="D497" s="4" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E497" s="2">
         <v>160</v>
@@ -21087,7 +21100,7 @@
         <v>7</v>
       </c>
       <c r="H497" s="5" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="I497" s="2">
         <v>26</v>
@@ -21106,7 +21119,7 @@
         <v>11</v>
       </c>
       <c r="D498" s="4" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E498" s="2">
         <v>343</v>
@@ -21118,7 +21131,7 @@
         <v>6</v>
       </c>
       <c r="H498" s="5" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="I498" s="2"/>
       <c r="J498" s="2">
@@ -21137,7 +21150,7 @@
         <v>7</v>
       </c>
       <c r="D499" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E499" s="2">
         <v>25</v>
@@ -21149,7 +21162,7 @@
         <v>4</v>
       </c>
       <c r="H499" s="5" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I499" s="2">
         <v>4.5</v>
@@ -21168,7 +21181,7 @@
         <v>27</v>
       </c>
       <c r="D500" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E500" s="2">
         <v>75</v>
@@ -21180,7 +21193,7 @@
         <v>2</v>
       </c>
       <c r="H500" s="5" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="I500" s="2"/>
       <c r="J500" s="2"/>
@@ -21213,19 +21226,19 @@
       </c>
     </row>
     <row r="502" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A502" s="168" t="s">
-        <v>522</v>
-      </c>
-      <c r="B502" s="166"/>
-      <c r="C502" s="166"/>
-      <c r="D502" s="166"/>
-      <c r="E502" s="166"/>
-      <c r="F502" s="166"/>
-      <c r="G502" s="166"/>
-      <c r="H502" s="166"/>
-      <c r="I502" s="166"/>
-      <c r="J502" s="166"/>
-      <c r="K502" s="167"/>
+      <c r="A502" s="173" t="s">
+        <v>515</v>
+      </c>
+      <c r="B502" s="164"/>
+      <c r="C502" s="164"/>
+      <c r="D502" s="164"/>
+      <c r="E502" s="164"/>
+      <c r="F502" s="164"/>
+      <c r="G502" s="164"/>
+      <c r="H502" s="164"/>
+      <c r="I502" s="164"/>
+      <c r="J502" s="164"/>
+      <c r="K502" s="165"/>
     </row>
     <row r="503" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
@@ -21267,7 +21280,7 @@
         <v>7</v>
       </c>
       <c r="D504" s="4" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E504" s="2">
         <v>64</v>
@@ -21279,7 +21292,7 @@
         <v>7</v>
       </c>
       <c r="H504" s="5" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="I504" s="2">
         <v>11</v>
@@ -21310,7 +21323,7 @@
         <v>2</v>
       </c>
       <c r="H505" s="5" t="s">
-        <v>128</v>
+        <v>952</v>
       </c>
       <c r="I505" s="2"/>
       <c r="J505" s="2">
@@ -21329,7 +21342,7 @@
         <v>11</v>
       </c>
       <c r="D506" s="4" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="E506" s="2">
         <v>92</v>
@@ -21341,7 +21354,7 @@
         <v>5</v>
       </c>
       <c r="H506" s="5" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="I506" s="2"/>
       <c r="J506" s="2">
@@ -21372,7 +21385,7 @@
         <v>2</v>
       </c>
       <c r="H507" s="5" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="I507" s="2">
         <v>8.5</v>
@@ -21403,7 +21416,7 @@
         <v>4</v>
       </c>
       <c r="H508" s="5" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="I508" s="2"/>
       <c r="J508" s="2"/>
@@ -21434,7 +21447,7 @@
         <v>2</v>
       </c>
       <c r="H509" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I509" s="2">
         <v>4</v>
@@ -21465,7 +21478,7 @@
         <v>3</v>
       </c>
       <c r="H510" s="5" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="I510" s="2"/>
       <c r="J510" s="2">
@@ -21484,7 +21497,7 @@
         <v>27</v>
       </c>
       <c r="D511" s="4" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="E511" s="2">
         <v>70</v>
@@ -21496,7 +21509,7 @@
         <v>4</v>
       </c>
       <c r="H511" s="5" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="I511" s="2"/>
       <c r="J511" s="2"/>
@@ -21515,7 +21528,7 @@
         <v>11</v>
       </c>
       <c r="D512" s="4" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="E512" s="2">
         <v>300</v>
@@ -21527,7 +21540,7 @@
         <v>7</v>
       </c>
       <c r="H512" s="5" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="I512" s="2"/>
       <c r="J512" s="2">
@@ -21546,7 +21559,7 @@
         <v>7</v>
       </c>
       <c r="D513" s="4" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E513" s="2">
         <v>76</v>
@@ -21558,7 +21571,7 @@
         <v>6</v>
       </c>
       <c r="H513" s="5" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="I513" s="2">
         <v>13</v>
@@ -21577,7 +21590,7 @@
         <v>27</v>
       </c>
       <c r="D514" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E514" s="2">
         <v>96</v>
@@ -21589,7 +21602,7 @@
         <v>2</v>
       </c>
       <c r="H514" s="5" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="I514" s="2"/>
       <c r="J514" s="2"/>
@@ -21623,7 +21636,7 @@
     </row>
     <row r="516" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="162" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B516" s="161"/>
       <c r="C516" s="161"/>
@@ -21676,7 +21689,7 @@
         <v>7</v>
       </c>
       <c r="D518" s="4" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E518" s="2">
         <v>80</v>
@@ -21688,7 +21701,7 @@
         <v>6</v>
       </c>
       <c r="H518" s="5" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="I518" s="2">
         <v>14.5</v>
@@ -21719,7 +21732,7 @@
         <v>2</v>
       </c>
       <c r="H519" s="5" t="s">
-        <v>538</v>
+        <v>961</v>
       </c>
       <c r="I519" s="2"/>
       <c r="J519" s="2">
@@ -21750,7 +21763,7 @@
         <v>4</v>
       </c>
       <c r="H520" s="5" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="I520" s="2"/>
       <c r="J520" s="2"/>
@@ -21769,7 +21782,7 @@
         <v>11</v>
       </c>
       <c r="D521" s="4" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E521" s="2">
         <v>163</v>
@@ -21781,7 +21794,7 @@
         <v>6</v>
       </c>
       <c r="H521" s="5" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="I521" s="2"/>
       <c r="J521" s="2">
@@ -21800,7 +21813,7 @@
         <v>7</v>
       </c>
       <c r="D522" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E522" s="2">
         <v>89</v>
@@ -21812,7 +21825,7 @@
         <v>4</v>
       </c>
       <c r="H522" s="5" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="I522" s="2">
         <v>14.5</v>
@@ -21831,7 +21844,7 @@
         <v>27</v>
       </c>
       <c r="D523" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E523" s="2">
         <v>81</v>
@@ -21843,7 +21856,7 @@
         <v>2</v>
       </c>
       <c r="H523" s="5" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="I523" s="2"/>
       <c r="J523" s="2"/>
@@ -21874,7 +21887,7 @@
         <v>2</v>
       </c>
       <c r="H524" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I524" s="2">
         <v>6</v>
@@ -21905,7 +21918,7 @@
         <v>5</v>
       </c>
       <c r="H525" s="5" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="I525" s="2"/>
       <c r="J525" s="2">
@@ -21936,7 +21949,7 @@
         <v>5</v>
       </c>
       <c r="H526" s="5" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="I526" s="2"/>
       <c r="J526" s="2"/>
@@ -21955,7 +21968,7 @@
         <v>7</v>
       </c>
       <c r="D527" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="E527" s="2">
         <v>179</v>
@@ -21967,7 +21980,7 @@
         <v>6</v>
       </c>
       <c r="H527" s="5" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I527" s="2">
         <v>29</v>
@@ -21986,7 +21999,7 @@
         <v>11</v>
       </c>
       <c r="D528" s="4" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E528" s="2">
         <v>354</v>
@@ -21998,7 +22011,7 @@
         <v>6</v>
       </c>
       <c r="H528" s="5" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I528" s="2"/>
       <c r="J528" s="2">
@@ -22017,7 +22030,7 @@
         <v>7</v>
       </c>
       <c r="D529" s="4" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="E529" s="2">
         <v>35</v>
@@ -22029,7 +22042,7 @@
         <v>4</v>
       </c>
       <c r="H529" s="5" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="I529" s="2">
         <v>6</v>
@@ -22063,7 +22076,7 @@
     </row>
     <row r="531" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="162" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="B531" s="161"/>
       <c r="C531" s="161"/>
@@ -22099,7 +22112,7 @@
         <v>4</v>
       </c>
       <c r="H532" s="5" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="I532" s="2"/>
       <c r="J532" s="2"/>
@@ -22118,7 +22131,7 @@
         <v>7</v>
       </c>
       <c r="D533" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E533" s="2">
         <v>84</v>
@@ -22130,7 +22143,7 @@
         <v>7</v>
       </c>
       <c r="H533" s="5" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="I533" s="2">
         <v>16</v>
@@ -22161,7 +22174,7 @@
         <v>2</v>
       </c>
       <c r="H534" s="5" t="s">
-        <v>551</v>
+        <v>962</v>
       </c>
       <c r="I534" s="2"/>
       <c r="J534" s="2">
@@ -22180,7 +22193,7 @@
         <v>11</v>
       </c>
       <c r="D535" s="4" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="E535" s="2">
         <v>167</v>
@@ -22192,7 +22205,7 @@
         <v>6</v>
       </c>
       <c r="H535" s="5" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="I535" s="2"/>
       <c r="J535" s="2">
@@ -22211,7 +22224,7 @@
         <v>7</v>
       </c>
       <c r="D536" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E536" s="2">
         <v>92</v>
@@ -22223,7 +22236,7 @@
         <v>4</v>
       </c>
       <c r="H536" s="5" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="I536" s="2">
         <v>15</v>
@@ -22242,7 +22255,7 @@
         <v>27</v>
       </c>
       <c r="D537" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E537" s="2">
         <v>84</v>
@@ -22254,7 +22267,7 @@
         <v>2</v>
       </c>
       <c r="H537" s="5" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="I537" s="2"/>
       <c r="J537" s="2"/>
@@ -22285,7 +22298,7 @@
         <v>2</v>
       </c>
       <c r="H538" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I538" s="2">
         <v>6</v>
@@ -22316,7 +22329,7 @@
         <v>5</v>
       </c>
       <c r="H539" s="5" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="I539" s="2"/>
       <c r="J539" s="2">
@@ -22347,7 +22360,7 @@
         <v>5</v>
       </c>
       <c r="H540" s="5" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="I540" s="2"/>
       <c r="J540" s="2"/>
@@ -22366,7 +22379,7 @@
         <v>7</v>
       </c>
       <c r="D541" s="4" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E541" s="2">
         <v>185</v>
@@ -22378,7 +22391,7 @@
         <v>6</v>
       </c>
       <c r="H541" s="5" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="I541" s="2">
         <v>30</v>
@@ -22397,7 +22410,7 @@
         <v>11</v>
       </c>
       <c r="D542" s="4" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E542" s="2">
         <v>369</v>
@@ -22409,7 +22422,7 @@
         <v>6</v>
       </c>
       <c r="H542" s="5" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="I542" s="2"/>
       <c r="J542" s="2">
@@ -22428,7 +22441,7 @@
         <v>7</v>
       </c>
       <c r="D543" s="4" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="E543" s="2">
         <v>40</v>
@@ -22440,7 +22453,7 @@
         <v>4</v>
       </c>
       <c r="H543" s="5" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="I543" s="2">
         <v>7</v>
@@ -22474,7 +22487,7 @@
     </row>
     <row r="545" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="162" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="B545" s="161"/>
       <c r="C545" s="161"/>
@@ -22510,7 +22523,7 @@
         <v>4</v>
       </c>
       <c r="H546" s="5" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="I546" s="2"/>
       <c r="J546" s="2"/>
@@ -22529,7 +22542,7 @@
         <v>7</v>
       </c>
       <c r="D547" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E547" s="2">
         <v>90</v>
@@ -22541,7 +22554,7 @@
         <v>7</v>
       </c>
       <c r="H547" s="5" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="I547" s="2">
         <v>17</v>
@@ -22572,7 +22585,7 @@
         <v>2</v>
       </c>
       <c r="H548" s="5" t="s">
-        <v>551</v>
+        <v>962</v>
       </c>
       <c r="I548" s="2"/>
       <c r="J548" s="2">
@@ -22591,7 +22604,7 @@
         <v>11</v>
       </c>
       <c r="D549" s="4" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E549" s="2">
         <v>174</v>
@@ -22603,7 +22616,7 @@
         <v>6</v>
       </c>
       <c r="H549" s="5" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="I549" s="2"/>
       <c r="J549" s="2">
@@ -22622,7 +22635,7 @@
         <v>7</v>
       </c>
       <c r="D550" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E550" s="2">
         <v>96</v>
@@ -22634,7 +22647,7 @@
         <v>4</v>
       </c>
       <c r="H550" s="5" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="I550" s="2">
         <v>15.5</v>
@@ -22653,7 +22666,7 @@
         <v>27</v>
       </c>
       <c r="D551" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E551" s="2">
         <v>87</v>
@@ -22665,7 +22678,7 @@
         <v>2</v>
       </c>
       <c r="H551" s="5" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="I551" s="2"/>
       <c r="J551" s="2"/>
@@ -22696,7 +22709,7 @@
         <v>2</v>
       </c>
       <c r="H552" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I552" s="2">
         <v>6</v>
@@ -22727,7 +22740,7 @@
         <v>5</v>
       </c>
       <c r="H553" s="5" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="I553" s="2"/>
       <c r="J553" s="2">
@@ -22758,7 +22771,7 @@
         <v>5</v>
       </c>
       <c r="H554" s="5" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="I554" s="2"/>
       <c r="J554" s="2"/>
@@ -22777,7 +22790,7 @@
         <v>7</v>
       </c>
       <c r="D555" s="4" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="E555" s="2">
         <v>197</v>
@@ -22789,7 +22802,7 @@
         <v>6</v>
       </c>
       <c r="H555" s="5" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="I555" s="2">
         <v>32</v>
@@ -22808,7 +22821,7 @@
         <v>11</v>
       </c>
       <c r="D556" s="4" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E556" s="2">
         <v>386</v>
@@ -22820,7 +22833,7 @@
         <v>6</v>
       </c>
       <c r="H556" s="5" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="I556" s="2"/>
       <c r="J556" s="2">
@@ -22839,7 +22852,7 @@
         <v>7</v>
       </c>
       <c r="D557" s="4" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="E557" s="2">
         <v>45</v>
@@ -22851,7 +22864,7 @@
         <v>4</v>
       </c>
       <c r="H557" s="5" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="I557" s="2">
         <v>7.5</v>
@@ -22884,8 +22897,8 @@
       </c>
     </row>
     <row r="559" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A559" s="163" t="s">
-        <v>577</v>
+      <c r="A559" s="172" t="s">
+        <v>568</v>
       </c>
       <c r="B559" s="161"/>
       <c r="C559" s="161"/>
@@ -22938,7 +22951,7 @@
         <v>7</v>
       </c>
       <c r="D561" s="4" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="E561" s="2">
         <v>57</v>
@@ -22950,7 +22963,7 @@
         <v>5</v>
       </c>
       <c r="H561" s="5" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="I561" s="2">
         <v>10</v>
@@ -22981,7 +22994,7 @@
         <v>2</v>
       </c>
       <c r="H562" s="5" t="s">
-        <v>274</v>
+        <v>956</v>
       </c>
       <c r="I562" s="2"/>
       <c r="J562" s="2">
@@ -23000,7 +23013,7 @@
         <v>11</v>
       </c>
       <c r="D563" s="4" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E563" s="2">
         <v>90</v>
@@ -23012,7 +23025,7 @@
         <v>5</v>
       </c>
       <c r="H563" s="5" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="I563" s="2"/>
       <c r="J563" s="2">
@@ -23031,7 +23044,7 @@
         <v>7</v>
       </c>
       <c r="D564" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E564" s="2">
         <v>60</v>
@@ -23043,7 +23056,7 @@
         <v>4</v>
       </c>
       <c r="H564" s="5" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="I564" s="2">
         <v>9.5</v>
@@ -23062,7 +23075,7 @@
         <v>27</v>
       </c>
       <c r="D565" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E565" s="2">
         <v>74</v>
@@ -23074,7 +23087,7 @@
         <v>2</v>
       </c>
       <c r="H565" s="5" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="I565" s="2"/>
       <c r="J565" s="2"/>
@@ -23105,7 +23118,7 @@
         <v>2</v>
       </c>
       <c r="H566" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I566" s="2">
         <v>6</v>
@@ -23136,7 +23149,7 @@
         <v>3</v>
       </c>
       <c r="H567" s="5" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="I567" s="2"/>
       <c r="J567" s="2">
@@ -23167,7 +23180,7 @@
         <v>5</v>
       </c>
       <c r="H568" s="5" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="I568" s="2"/>
       <c r="J568" s="2"/>
@@ -23186,7 +23199,7 @@
         <v>7</v>
       </c>
       <c r="D569" s="4" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E569" s="2">
         <v>75</v>
@@ -23198,7 +23211,7 @@
         <v>6</v>
       </c>
       <c r="H569" s="5" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="I569" s="2">
         <v>12</v>
@@ -23217,7 +23230,7 @@
         <v>11</v>
       </c>
       <c r="D570" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E570" s="2">
         <v>120</v>
@@ -23229,7 +23242,7 @@
         <v>6</v>
       </c>
       <c r="H570" s="5" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="I570" s="2"/>
       <c r="J570" s="2">
@@ -23262,8 +23275,8 @@
       </c>
     </row>
     <row r="572" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A572" s="171" t="s">
-        <v>589</v>
+      <c r="A572" s="160" t="s">
+        <v>580</v>
       </c>
       <c r="B572" s="161"/>
       <c r="C572" s="161"/>
@@ -23287,7 +23300,7 @@
         <v>2</v>
       </c>
       <c r="D573" s="4" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="E573" s="2" t="s">
         <v>4</v>
@@ -23299,7 +23312,7 @@
         <v>1</v>
       </c>
       <c r="H573" s="5" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="I573" s="2"/>
       <c r="J573" s="2"/>
@@ -23316,7 +23329,7 @@
         <v>11</v>
       </c>
       <c r="D574" s="4" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="E574" s="2">
         <v>60</v>
@@ -23328,7 +23341,7 @@
         <v>2</v>
       </c>
       <c r="H574" s="5" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="I574" s="2"/>
       <c r="J574" s="2">
@@ -23359,7 +23372,7 @@
         <v>2</v>
       </c>
       <c r="H575" s="5" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="I575" s="2">
         <v>3</v>
@@ -23378,7 +23391,7 @@
         <v>11</v>
       </c>
       <c r="D576" s="4" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="E576" s="2">
         <v>35</v>
@@ -23390,7 +23403,7 @@
         <v>2</v>
       </c>
       <c r="H576" s="5" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="I576" s="2"/>
       <c r="J576" s="2">
@@ -23409,7 +23422,7 @@
         <v>27</v>
       </c>
       <c r="D577" s="4" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="E577" s="2">
         <v>45</v>
@@ -23421,7 +23434,7 @@
         <v>3</v>
       </c>
       <c r="H577" s="5" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="I577" s="2"/>
       <c r="J577" s="2"/>
@@ -23440,7 +23453,7 @@
         <v>11</v>
       </c>
       <c r="D578" s="4" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="E578" s="2">
         <v>45</v>
@@ -23452,7 +23465,7 @@
         <v>2</v>
       </c>
       <c r="H578" s="5" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="I578" s="2"/>
       <c r="J578" s="2">
@@ -23471,7 +23484,7 @@
         <v>7</v>
       </c>
       <c r="D579" s="4" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="E579" s="2">
         <v>25</v>
@@ -23483,7 +23496,7 @@
         <v>2</v>
       </c>
       <c r="H579" s="5" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="I579" s="2">
         <v>4</v>
@@ -23502,7 +23515,7 @@
         <v>27</v>
       </c>
       <c r="D580" s="4" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E580" s="2">
         <v>30</v>
@@ -23514,7 +23527,7 @@
         <v>2</v>
       </c>
       <c r="H580" s="5" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="I580" s="2"/>
       <c r="J580" s="2"/>
@@ -23533,7 +23546,7 @@
         <v>7</v>
       </c>
       <c r="D581" s="4" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="E581" s="2">
         <v>15</v>
@@ -23545,7 +23558,7 @@
         <v>2</v>
       </c>
       <c r="H581" s="5" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="I581" s="2">
         <v>2.5</v>
@@ -23564,7 +23577,7 @@
         <v>11</v>
       </c>
       <c r="D582" s="4" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="E582" s="2">
         <v>25</v>
@@ -23576,7 +23589,7 @@
         <v>2</v>
       </c>
       <c r="H582" s="5" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="I582" s="2"/>
       <c r="J582" s="2">
@@ -23595,7 +23608,7 @@
         <v>7</v>
       </c>
       <c r="D583" s="4" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="E583" s="2">
         <v>10</v>
@@ -23607,7 +23620,7 @@
         <v>2</v>
       </c>
       <c r="H583" s="5" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="I583" s="2">
         <v>1.5</v>
@@ -23626,7 +23639,7 @@
         <v>27</v>
       </c>
       <c r="D584" s="4" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="E584" s="2">
         <v>10</v>
@@ -23638,7 +23651,7 @@
         <v>2</v>
       </c>
       <c r="H584" s="5" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="I584" s="2"/>
       <c r="J584" s="2"/>
@@ -23657,7 +23670,7 @@
         <v>7</v>
       </c>
       <c r="D585" s="12" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E585" s="12" t="s">
         <v>4</v>
@@ -23669,7 +23682,7 @@
         <v>3</v>
       </c>
       <c r="H585" s="15" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="I585" s="12">
         <v>42</v>
@@ -23707,6 +23720,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A288:K288"/>
+    <mergeCell ref="A559:K559"/>
+    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="A458:K458"/>
+    <mergeCell ref="A502:K502"/>
+    <mergeCell ref="A516:K516"/>
+    <mergeCell ref="A429:K429"/>
+    <mergeCell ref="A472:K472"/>
+    <mergeCell ref="A444:K444"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A370:K370"/>
+    <mergeCell ref="A399:K399"/>
+    <mergeCell ref="A355:K355"/>
+    <mergeCell ref="A124:K124"/>
+    <mergeCell ref="A162:K162"/>
+    <mergeCell ref="A346:K346"/>
+    <mergeCell ref="A316:K316"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A99:K99"/>
+    <mergeCell ref="A137:K137"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A229:K229"/>
+    <mergeCell ref="A111:K111"/>
+    <mergeCell ref="A176:K176"/>
     <mergeCell ref="A572:K572"/>
     <mergeCell ref="A531:K531"/>
     <mergeCell ref="A487:K487"/>
@@ -23723,33 +23763,6 @@
     <mergeCell ref="A244:K244"/>
     <mergeCell ref="A190:K190"/>
     <mergeCell ref="A274:K274"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A370:K370"/>
-    <mergeCell ref="A399:K399"/>
-    <mergeCell ref="A355:K355"/>
-    <mergeCell ref="A124:K124"/>
-    <mergeCell ref="A162:K162"/>
-    <mergeCell ref="A346:K346"/>
-    <mergeCell ref="A316:K316"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A99:K99"/>
-    <mergeCell ref="A137:K137"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A229:K229"/>
-    <mergeCell ref="A111:K111"/>
-    <mergeCell ref="A176:K176"/>
-    <mergeCell ref="A288:K288"/>
-    <mergeCell ref="A559:K559"/>
-    <mergeCell ref="A73:K73"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="A458:K458"/>
-    <mergeCell ref="A502:K502"/>
-    <mergeCell ref="A516:K516"/>
-    <mergeCell ref="A429:K429"/>
-    <mergeCell ref="A472:K472"/>
-    <mergeCell ref="A444:K444"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23781,64 +23794,64 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D3" s="146" t="s">
+        <v>607</v>
+      </c>
+      <c r="E3" t="s">
+        <v>608</v>
+      </c>
+      <c r="F3" t="s">
+        <v>609</v>
+      </c>
+      <c r="G3" t="s">
+        <v>610</v>
+      </c>
+      <c r="H3" t="s">
+        <v>611</v>
+      </c>
+      <c r="I3" t="s">
+        <v>612</v>
+      </c>
+      <c r="J3" t="s">
+        <v>613</v>
+      </c>
+      <c r="M3" s="174" t="s">
         <v>614</v>
-      </c>
-      <c r="C3" t="s">
-        <v>615</v>
-      </c>
-      <c r="D3" s="146" t="s">
-        <v>616</v>
-      </c>
-      <c r="E3" t="s">
-        <v>617</v>
-      </c>
-      <c r="F3" t="s">
-        <v>618</v>
-      </c>
-      <c r="G3" t="s">
-        <v>619</v>
-      </c>
-      <c r="H3" t="s">
-        <v>620</v>
-      </c>
-      <c r="I3" t="s">
-        <v>621</v>
-      </c>
-      <c r="J3" t="s">
-        <v>622</v>
-      </c>
-      <c r="M3" s="174" t="s">
-        <v>623</v>
       </c>
       <c r="N3" s="175"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B4" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="C4" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="D4" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="E4" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="F4" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="G4" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="H4" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="I4" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="M4" s="147">
         <f t="shared" ref="M4:M12" si="0">+N4*M5/N5</f>
@@ -23850,34 +23863,34 @@
     </row>
     <row r="5" spans="1:14" s="149" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="149" t="s">
+        <v>620</v>
+      </c>
+      <c r="B5" s="149" t="s">
+        <v>621</v>
+      </c>
+      <c r="C5" s="149" t="s">
+        <v>622</v>
+      </c>
+      <c r="D5" s="150" t="s">
+        <v>623</v>
+      </c>
+      <c r="E5" s="149" t="s">
+        <v>624</v>
+      </c>
+      <c r="F5" s="143" t="s">
+        <v>625</v>
+      </c>
+      <c r="G5" s="143" t="s">
+        <v>626</v>
+      </c>
+      <c r="H5" s="143" t="s">
+        <v>627</v>
+      </c>
+      <c r="I5" s="143" t="s">
+        <v>628</v>
+      </c>
+      <c r="J5" s="143" t="s">
         <v>629</v>
-      </c>
-      <c r="B5" s="149" t="s">
-        <v>630</v>
-      </c>
-      <c r="C5" s="149" t="s">
-        <v>631</v>
-      </c>
-      <c r="D5" s="150" t="s">
-        <v>632</v>
-      </c>
-      <c r="E5" s="149" t="s">
-        <v>633</v>
-      </c>
-      <c r="F5" s="143" t="s">
-        <v>634</v>
-      </c>
-      <c r="G5" s="143" t="s">
-        <v>635</v>
-      </c>
-      <c r="H5" s="143" t="s">
-        <v>636</v>
-      </c>
-      <c r="I5" s="143" t="s">
-        <v>637</v>
-      </c>
-      <c r="J5" s="143" t="s">
-        <v>638</v>
       </c>
       <c r="M5" s="151">
         <f t="shared" si="0"/>
@@ -23889,34 +23902,34 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="B6" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="C6" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="D6" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="E6" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="F6" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="G6" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="H6" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="I6" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="J6" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="M6" s="147">
         <f t="shared" si="0"/>
@@ -23928,7 +23941,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="B7">
         <v>155.19999999999999</v>
@@ -23967,34 +23980,34 @@
     </row>
     <row r="8" spans="1:14" s="155" customFormat="1" ht="225" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="155" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="B8" s="155" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="156" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="D8" s="156" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="E8" s="156" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="F8" s="156" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="G8" s="156" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="H8" s="156" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="I8" s="156" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="J8" s="156" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="M8" s="147">
         <f t="shared" si="0"/>
@@ -24115,25 +24128,25 @@
     <row r="2" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18"/>
       <c r="B2" s="19" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="I2" s="21"/>
       <c r="J2" s="18"/>
@@ -24144,25 +24157,25 @@
     <row r="3" spans="1:33" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="23" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="I3" s="25"/>
       <c r="J3" s="22"/>
@@ -24173,25 +24186,25 @@
     <row r="4" spans="1:33" s="26" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="27" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" s="22"/>
@@ -24214,29 +24227,29 @@
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
       <c r="W5" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="29" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -24244,37 +24257,37 @@
       <c r="M6" s="33"/>
       <c r="S6" s="34"/>
       <c r="W6" s="35" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="X6" s="36"/>
     </row>
     <row r="7" spans="1:33" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="37" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H7" s="43" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="I7" s="44"/>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="45" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="M7" s="33"/>
       <c r="N7" s="26"/>
@@ -24283,53 +24296,53 @@
       <c r="S7" s="26"/>
       <c r="U7" s="46"/>
       <c r="V7" s="43" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="W7" s="45" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="37" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="I8" s="44"/>
       <c r="L8" s="53" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="N8" s="54" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="O8" s="26"/>
       <c r="R8" s="26"/>
       <c r="V8" s="54" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="W8" s="53" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="B9" s="55"/>
       <c r="C9" s="56">
@@ -24426,7 +24439,7 @@
     </row>
     <row r="10" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="B10" s="61"/>
       <c r="C10" s="57">
@@ -24449,7 +24462,7 @@
       </c>
       <c r="I10" s="44"/>
       <c r="J10" s="62" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="K10" s="28"/>
       <c r="L10" s="28"/>
@@ -24459,7 +24472,7 @@
       <c r="P10" s="28"/>
       <c r="Q10" s="28"/>
       <c r="R10" s="17" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="S10" s="28"/>
       <c r="T10" s="28"/>
@@ -24478,7 +24491,7 @@
     </row>
     <row r="11" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="B11" s="64">
         <f>SUM(C11:G11)</f>
@@ -24507,7 +24520,7 @@
       </c>
       <c r="I11" s="44"/>
       <c r="J11" s="66" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="K11" s="67"/>
       <c r="L11" s="68"/>
@@ -24517,7 +24530,7 @@
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="17" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="S11" s="69"/>
       <c r="T11" s="69"/>
@@ -24538,7 +24551,7 @@
     </row>
     <row r="12" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="72">
@@ -24567,7 +24580,7 @@
       </c>
       <c r="I12" s="44"/>
       <c r="J12" s="66" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="K12" s="73"/>
       <c r="L12" s="74"/>
@@ -24577,7 +24590,7 @@
       <c r="P12" s="74"/>
       <c r="Q12" s="74"/>
       <c r="R12" s="17" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="S12" s="74"/>
       <c r="T12" s="74"/>
@@ -24596,7 +24609,7 @@
     </row>
     <row r="13" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="B13" s="55"/>
       <c r="C13" s="57">
@@ -24625,7 +24638,7 @@
       </c>
       <c r="I13" s="44"/>
       <c r="J13" s="66" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="K13" s="76"/>
       <c r="L13" s="76"/>
@@ -24635,7 +24648,7 @@
       <c r="P13" s="76"/>
       <c r="Q13" s="76"/>
       <c r="R13" s="17" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="S13" s="76"/>
       <c r="T13" s="76"/>
@@ -24654,7 +24667,7 @@
     </row>
     <row r="14" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="B14" s="65">
         <f>+SUM(C14:G14)</f>
@@ -24685,7 +24698,7 @@
         <v>0.69444444444444442</v>
       </c>
       <c r="J14" s="78" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="K14" s="79"/>
       <c r="L14" s="79"/>
@@ -24695,7 +24708,7 @@
       <c r="P14" s="79"/>
       <c r="Q14" s="79"/>
       <c r="R14" s="17" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="S14" s="79"/>
       <c r="T14" s="79"/>
@@ -24714,7 +24727,7 @@
     </row>
     <row r="15" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="B15" s="65">
         <f>+SUM(C15:G15)</f>
@@ -24745,7 +24758,7 @@
         <v>13.888888888888889</v>
       </c>
       <c r="J15" s="83" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="K15" s="84"/>
       <c r="L15" s="85"/>
@@ -24755,7 +24768,7 @@
       <c r="P15" s="85"/>
       <c r="Q15" s="86"/>
       <c r="R15" s="17" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="S15" s="85"/>
       <c r="T15" s="85"/>
@@ -24783,14 +24796,14 @@
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
       <c r="J16" s="88" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="K16" s="89">
         <f>G11+279.37+H11</f>
         <v>566.34300000000007</v>
       </c>
       <c r="L16" s="36" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="N16" s="71">
         <f>129</f>
@@ -24820,32 +24833,32 @@
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="92" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="B18" s="93" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="C18" s="94" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="D18" s="95" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="E18" s="96" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="F18" s="97" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G18" s="98" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="H18" s="99" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="I18" s="44"/>
       <c r="K18" s="100" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="L18" s="101">
         <f>SUM(K16:AD16)</f>
@@ -24854,7 +24867,7 @@
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="102" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="B19" s="103">
         <f>SUM(C19:H19)</f>
@@ -24870,19 +24883,19 @@
       <c r="H19" s="107"/>
       <c r="I19" s="106"/>
       <c r="K19" s="17" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="L19" s="36">
         <f>+G11*4</f>
         <v>647.89200000000005</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="108" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="B20" s="109">
         <f>SUM(C20:H20)</f>
@@ -24898,19 +24911,19 @@
       <c r="H20" s="111"/>
       <c r="I20" s="110"/>
       <c r="K20" s="17" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="L20" s="90">
         <f>L18-L19</f>
         <v>544.42399999999998</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="108" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="B21" s="112">
         <f t="shared" ref="B21:B27" si="3">SUM(C21:G21)</f>
@@ -24929,7 +24942,7 @@
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="108" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="B22" s="112">
         <f t="shared" si="3"/>
@@ -24948,7 +24961,7 @@
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="108" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="B23" s="112">
         <f t="shared" si="3"/>
@@ -24967,7 +24980,7 @@
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="108" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="B24" s="112">
         <f t="shared" si="3"/>
@@ -24986,7 +24999,7 @@
     </row>
     <row r="25" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="108" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="B25" s="112">
         <f t="shared" si="3"/>
@@ -25005,7 +25018,7 @@
     </row>
     <row r="26" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="108" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="B26" s="112">
         <f t="shared" si="3"/>
@@ -25024,7 +25037,7 @@
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="108" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="B27" s="116">
         <f t="shared" si="3"/>
@@ -25044,7 +25057,7 @@
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="108" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="B28" s="116">
         <f>SUM(C28:H28)</f>
@@ -25066,7 +25079,7 @@
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="108" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="B29" s="116">
         <f>SUM(C29:H29)</f>
@@ -25087,7 +25100,7 @@
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="108" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="B30" s="112">
         <f>SUM(C30:H30)</f>
@@ -25109,7 +25122,7 @@
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="108" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="B31" s="116">
         <f>SUM(C31:G31)</f>
@@ -25130,7 +25143,7 @@
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="108" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="B32" s="116">
         <f>SUM(C32:G32)</f>
@@ -25151,7 +25164,7 @@
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="108" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="B33" s="121">
         <f>SUM(C33:G33)</f>
@@ -25170,7 +25183,7 @@
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="108" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="B34" s="116">
         <f t="shared" ref="B34:B50" si="4">SUM(C34:H34)</f>
@@ -25187,7 +25200,7 @@
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="108" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="B35" s="116">
         <f t="shared" si="4"/>
@@ -25206,7 +25219,7 @@
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="108" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="B36" s="116">
         <f t="shared" si="4"/>
@@ -25225,7 +25238,7 @@
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="108" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="B37" s="116">
         <f t="shared" si="4"/>
@@ -25244,7 +25257,7 @@
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="108" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="B38" s="127">
         <f t="shared" si="4"/>
@@ -25266,7 +25279,7 @@
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="108" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="B39" s="116">
         <f t="shared" si="4"/>
@@ -25288,7 +25301,7 @@
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="108" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="B40" s="127">
         <f t="shared" si="4"/>
@@ -25309,7 +25322,7 @@
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="108" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="B41" s="116">
         <f t="shared" si="4"/>
@@ -25330,7 +25343,7 @@
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="108" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="B42" s="116">
         <f t="shared" si="4"/>
@@ -25351,7 +25364,7 @@
     </row>
     <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="108" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="B43" s="116">
         <f t="shared" si="4"/>
@@ -25372,7 +25385,7 @@
     </row>
     <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="108" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="B44" s="127">
         <f t="shared" si="4"/>
@@ -25393,7 +25406,7 @@
     </row>
     <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="108" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="B45" s="127">
         <f t="shared" si="4"/>
@@ -25414,7 +25427,7 @@
     </row>
     <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="108" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="B46" s="116">
         <f t="shared" si="4"/>
@@ -25435,7 +25448,7 @@
     </row>
     <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="108" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="B47" s="127">
         <f t="shared" si="4"/>
@@ -25456,7 +25469,7 @@
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="108" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="B48" s="127">
         <f t="shared" si="4"/>
@@ -25477,7 +25490,7 @@
     </row>
     <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="108" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="B49" s="127">
         <f t="shared" si="4"/>
@@ -25496,7 +25509,7 @@
     </row>
     <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="108" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="B50" s="116">
         <f t="shared" si="4"/>
@@ -25515,15 +25528,15 @@
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="108" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="B51" s="116" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="C51" s="104"/>
       <c r="D51" s="105"/>
       <c r="E51" s="120" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="F51" s="129"/>
       <c r="G51" s="129"/>
@@ -25535,14 +25548,14 @@
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="108" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="B52" s="116" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="C52" s="104"/>
       <c r="E52" s="120" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="H52" s="131"/>
       <c r="K52" s="18"/>
@@ -25551,14 +25564,14 @@
     </row>
     <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="108" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="B53" s="116" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="C53" s="104"/>
       <c r="E53" s="120" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="H53" s="131"/>
       <c r="K53" s="18"/>
@@ -25567,15 +25580,15 @@
     </row>
     <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="132" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="B54" s="133" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="C54" s="134"/>
       <c r="D54" s="135"/>
       <c r="E54" s="136" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="F54" s="135"/>
       <c r="G54" s="135"/>
@@ -25661,231 +25674,231 @@
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="141" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="141" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="B4" s="142" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="C4" s="142" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="143" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="B5" s="143" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="C5" s="143" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="143" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="B6" s="143" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="C6" s="143" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="143" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="C7" s="143" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="143" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="B8" s="143" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="C8" s="143" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="143" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="B9" s="143" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="C9" s="143" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="141" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="142" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="B12" s="142" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="C12" s="142" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="D12" s="142" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="E12" s="142" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="F12" s="142" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="G12" s="142" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="143" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="B13" s="143" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="C13" s="143" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="D13" s="143" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="E13" s="143" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="F13" s="143" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="G13" s="143" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="143" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="B14" s="143" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="C14" s="143" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="D14" s="143" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="E14" s="143" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="F14" s="143" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="G14" s="143" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="143" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="B15" s="143" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="C15" s="143" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="D15" s="143" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="F15" s="143" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="G15" s="143" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="143" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="B16" s="143" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="C16" s="143" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="D16" s="143" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="E16" s="143" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="F16" s="143" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="G16" s="143" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="143" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="B17" s="143" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="C17" s="143" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="D17" s="143" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="E17" s="143" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="F17" s="143" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="G17" s="143" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="141" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="176" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="B20" s="161"/>
       <c r="C20" s="161"/>
@@ -25896,15 +25909,15 @@
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="141" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="141" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="B23" s="176" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="C23" s="161"/>
       <c r="D23" s="161"/>
@@ -25914,10 +25927,10 @@
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="141" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="B24" s="176" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="C24" s="161"/>
       <c r="D24" s="161"/>
@@ -25927,10 +25940,10 @@
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="141" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="B25" s="176" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="C25" s="161"/>
       <c r="D25" s="161"/>
@@ -25940,10 +25953,10 @@
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="141" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="B26" s="176" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="C26" s="161"/>
       <c r="D26" s="161"/>
@@ -25953,10 +25966,10 @@
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="141" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="B27" s="176" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="C27" s="161"/>
       <c r="D27" s="161"/>
@@ -25966,10 +25979,10 @@
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="141" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="B28" s="176" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="C28" s="161"/>
       <c r="D28" s="161"/>
@@ -25979,10 +25992,10 @@
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="141" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="B29" s="176" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="C29" s="161"/>
       <c r="D29" s="161"/>
@@ -25992,14 +26005,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="B29:G29"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B28:G28"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B27:G27"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="B26:G26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -26018,7 +26031,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="177" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="B1" s="161"/>
       <c r="C1" s="161"/>
@@ -26026,105 +26039,105 @@
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="143" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="B3" s="143" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="C3" s="143" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="D3" s="143" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="B4" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="C4" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="D4" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="B5" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="C5" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="D5" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="B6" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="C6" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="D6" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="B7" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="C7" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="D7" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="B8" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="C8" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="D8" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="B9" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="C9" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="D9" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="161" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="B11" s="161"/>
       <c r="C11" s="161"/>
@@ -26132,7 +26145,7 @@
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="161" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="B12" s="161"/>
       <c r="C12" s="161"/>
@@ -26140,7 +26153,7 @@
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="161" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="B13" s="161"/>
       <c r="C13" s="161"/>
@@ -26148,264 +26161,264 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="157" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="158" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="159" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="B17" s="159" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="C17" s="159" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="D17" s="159" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="158" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="B18" s="158" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="C18" s="158" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="D18" s="158" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="158" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="B19" s="158" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C19" s="158" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="D19" s="158" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="158" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="B20" s="158" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="C20" s="158" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="D20" s="158" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="158" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="B21" s="158" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C21" s="158" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="D21" s="158" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="158" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="B22" s="158" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C22" s="158" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="D22" s="158" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="158" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="B23" s="158" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="C23" s="158" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="D23" s="158" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="158" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="B24" s="158" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="C24" s="158" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="D24" s="158" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="158" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="B25" s="158" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="C25" s="158" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="D25" s="158" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="158" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="B26" s="158" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="C26" s="158" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="D26" s="158" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="158" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="C27" s="158" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="D27" s="158" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="158" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="B28" s="158" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="C28" s="158" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="D28" s="158" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="158" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="B29" s="158" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="C29" s="158" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="D29" s="158" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="158" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="B30" s="158" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="C30" s="158" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="D30" s="158" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="158" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="B31" s="158" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="C31" s="158" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="D31" s="158" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="158" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="B32" s="158" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="C32" s="158" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="D32" s="158" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="158" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="B33" s="158" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="C33" s="158" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="D33" s="158" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="158" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="B34" s="158" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="C34" s="158" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="D34" s="158" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
     </row>
   </sheetData>
@@ -26433,7 +26446,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="177" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="B1" s="161"/>
       <c r="C1" s="161"/>
@@ -26441,46 +26454,46 @@
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="142" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="B2" s="144">
         <v>210</v>
       </c>
       <c r="C2" s="176" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="D2" s="161"/>
       <c r="E2" s="161"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="142" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="B3" s="142" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C3" s="142" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D3" s="142" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="E3" s="142" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="143" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="B4" s="143" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="C4" s="143" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="D4" s="143" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="E4" s="143" t="str">
         <f>"&lt; "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*55/500,0)*5,"0"),"?")&amp;" W"</f>
@@ -26489,16 +26502,16 @@
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="143" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="B5" s="143" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="C5" s="143" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="D5" s="143" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="E5" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*56/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W (cible "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*60/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;" W)"</f>
@@ -26507,16 +26520,16 @@
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="143" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="B6" s="143" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="C6" s="143" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="D6" s="143" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="E6" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*70/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*75/500,0)*5,"0"),"?")&amp;" W"</f>
@@ -26525,16 +26538,16 @@
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="143" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="C7" s="143" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="E7" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*76/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*87/500,0)*5,"0"),"?")&amp;" W"</f>
@@ -26543,16 +26556,16 @@
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="143" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="B8" s="143" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="C8" s="143" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="D8" s="143" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="E8" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*88/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*94/500,0)*5,"0"),"?")&amp;" W"</f>
@@ -26561,16 +26574,16 @@
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="143" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="B9" s="143" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="C9" s="143" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="D9" s="143" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="E9" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*95/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*105/500,0)*5,"0"),"?")&amp;" W"</f>
@@ -26579,16 +26592,16 @@
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="143" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="B10" s="143" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="C10" s="143" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="D10" s="143" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="E10" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*93/500,0)*5,"0"),"?")&amp;" / "&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*107/500,0)*5,"0"),"?")&amp;" W"</f>
@@ -26597,16 +26610,16 @@
     </row>
     <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="B11" s="143" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="C11" s="143" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="D11" s="143" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="E11" s="143" t="str">
         <f>IF(FTP&gt;0,TEXT(ROUND(FTP*106/500,0)*5,"0"),"?")&amp;"-"&amp;IF(FTP&gt;0,TEXT(ROUND(FTP*120/500,0)*5,"0"),"?")&amp;" W"</f>
@@ -26615,7 +26628,7 @@
     </row>
     <row r="13" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="176" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="B13" s="161"/>
       <c r="C13" s="161"/>
@@ -26623,7 +26636,7 @@
     </row>
     <row r="14" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="176" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="B14" s="161"/>
       <c r="C14" s="161"/>
@@ -26631,7 +26644,7 @@
     </row>
     <row r="15" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="176" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="B15" s="161"/>
       <c r="C15" s="161"/>
@@ -26639,7 +26652,7 @@
     </row>
     <row r="16" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="176" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="B16" s="161"/>
       <c r="C16" s="161"/>
@@ -26647,7 +26660,7 @@
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="176" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="B17" s="161"/>
       <c r="C17" s="161"/>
